--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="F14" t="n">
-        <v>12.88</v>
+        <v>12.45</v>
       </c>
       <c r="G14" t="n">
-        <v>238.9</v>
+        <v>254.5</v>
       </c>
       <c r="H14" t="n">
-        <v>54</v>
+        <v>58.6</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>91.25</v>
+        <v>-50.95</v>
       </c>
       <c r="K14" t="n">
-        <v>60.81</v>
+        <v>191.24</v>
       </c>
       <c r="L14" t="n">
-        <v>109.66</v>
+        <v>197.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:15:13</t>
+          <t>05:15:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.23</v>
+        <v>3.87</v>
       </c>
       <c r="F15" t="n">
-        <v>12.55</v>
+        <v>12.42</v>
       </c>
       <c r="G15" t="n">
-        <v>251.8</v>
+        <v>230.4</v>
       </c>
       <c r="H15" t="n">
-        <v>41.1</v>
+        <v>46.3</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-57.98</v>
+        <v>-105.7</v>
       </c>
       <c r="K15" t="n">
-        <v>21.11</v>
+        <v>-87.56</v>
       </c>
       <c r="L15" t="n">
-        <v>61.7</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:16:58</t>
+          <t>05:16:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="F16" t="n">
-        <v>12.36</v>
+        <v>12.43</v>
       </c>
       <c r="G16" t="n">
-        <v>238.3</v>
+        <v>240</v>
       </c>
       <c r="H16" t="n">
-        <v>49.6</v>
+        <v>56.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-48.07</v>
+        <v>-183.91</v>
       </c>
       <c r="K16" t="n">
-        <v>229.75</v>
+        <v>-278.57</v>
       </c>
       <c r="L16" t="n">
-        <v>234.73</v>
+        <v>333.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:20:25</t>
+          <t>05:21:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="F17" t="n">
-        <v>12.98</v>
+        <v>13.17</v>
       </c>
       <c r="G17" t="n">
-        <v>240.2</v>
+        <v>227.3</v>
       </c>
       <c r="H17" t="n">
-        <v>53.7</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>205.27</v>
+        <v>60.18</v>
       </c>
       <c r="K17" t="n">
-        <v>-74.56999999999999</v>
+        <v>-8.59</v>
       </c>
       <c r="L17" t="n">
-        <v>218.4</v>
+        <v>60.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:22:09</t>
+          <t>05:22:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.05</v>
+        <v>3.37</v>
       </c>
       <c r="F18" t="n">
-        <v>13.01</v>
+        <v>12.53</v>
       </c>
       <c r="G18" t="n">
-        <v>231.6</v>
+        <v>233.7</v>
       </c>
       <c r="H18" t="n">
-        <v>49.7</v>
+        <v>52.6</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.01</v>
+        <v>94.37</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.32</v>
+        <v>-12.19</v>
       </c>
       <c r="L18" t="n">
-        <v>61.81</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:23:36</t>
+          <t>05:24:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.26</v>
+        <v>2.57</v>
       </c>
       <c r="F19" t="n">
-        <v>12.58</v>
+        <v>12.87</v>
       </c>
       <c r="G19" t="n">
-        <v>250.6</v>
+        <v>226.6</v>
       </c>
       <c r="H19" t="n">
         <v>51</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>25.59</v>
+        <v>-67.09</v>
       </c>
       <c r="K19" t="n">
-        <v>45.15</v>
+        <v>17.21</v>
       </c>
       <c r="L19" t="n">
-        <v>51.9</v>
+        <v>69.26000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:28:17</t>
+          <t>05:28:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="F20" t="n">
-        <v>13.29</v>
+        <v>12.84</v>
       </c>
       <c r="G20" t="n">
-        <v>233</v>
+        <v>237.8</v>
       </c>
       <c r="H20" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>131.94</v>
+        <v>215.14</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.44</v>
+        <v>-121.21</v>
       </c>
       <c r="L20" t="n">
-        <v>141.25</v>
+        <v>246.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:30:37</t>
+          <t>05:29:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.01</v>
+        <v>3.68</v>
       </c>
       <c r="F21" t="n">
-        <v>11.98</v>
+        <v>12.19</v>
       </c>
       <c r="G21" t="n">
-        <v>249.5</v>
+        <v>238</v>
       </c>
       <c r="H21" t="n">
-        <v>54</v>
+        <v>51.8</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>178.31</v>
+        <v>-45.84</v>
       </c>
       <c r="K21" t="n">
-        <v>103.42</v>
+        <v>121.47</v>
       </c>
       <c r="L21" t="n">
-        <v>206.13</v>
+        <v>129.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:32:42</t>
+          <t>05:30:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="F22" t="n">
-        <v>13.21</v>
+        <v>12.9</v>
       </c>
       <c r="G22" t="n">
-        <v>242.1</v>
+        <v>230</v>
       </c>
       <c r="H22" t="n">
-        <v>48.1</v>
+        <v>54.8</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>357.76</v>
+        <v>15.31</v>
       </c>
       <c r="K22" t="n">
-        <v>160.86</v>
+        <v>-123.94</v>
       </c>
       <c r="L22" t="n">
-        <v>392.26</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:38:39</t>
+          <t>05:35:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="F23" t="n">
-        <v>12.65</v>
+        <v>12.69</v>
       </c>
       <c r="G23" t="n">
-        <v>243.4</v>
+        <v>237</v>
       </c>
       <c r="H23" t="n">
-        <v>49.2</v>
+        <v>53.6</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>246.51</v>
+        <v>135.15</v>
       </c>
       <c r="K23" t="n">
-        <v>-76.52</v>
+        <v>-1.38</v>
       </c>
       <c r="L23" t="n">
-        <v>258.12</v>
+        <v>135.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:40:34</t>
+          <t>05:37:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="F24" t="n">
-        <v>12.43</v>
+        <v>12.72</v>
       </c>
       <c r="G24" t="n">
-        <v>247.3</v>
+        <v>225.7</v>
       </c>
       <c r="H24" t="n">
-        <v>51.3</v>
+        <v>54.2</v>
       </c>
       <c r="I24" t="n">
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>423.73</v>
+        <v>12.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-299.64</v>
+        <v>-872.83</v>
       </c>
       <c r="L24" t="n">
-        <v>518.97</v>
+        <v>872.9299999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:41:56</t>
+          <t>05:38:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="F25" t="n">
-        <v>13.26</v>
+        <v>13.16</v>
       </c>
       <c r="G25" t="n">
-        <v>226.6</v>
+        <v>253.7</v>
       </c>
       <c r="H25" t="n">
-        <v>53.7</v>
+        <v>46.9</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>483.11</v>
+        <v>-117.17</v>
       </c>
       <c r="K25" t="n">
-        <v>-188.82</v>
+        <v>-603.35</v>
       </c>
       <c r="L25" t="n">
-        <v>518.7</v>
+        <v>614.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:46:55</t>
+          <t>05:41:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="F26" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="G26" t="n">
-        <v>239.2</v>
+        <v>246.2</v>
       </c>
       <c r="H26" t="n">
-        <v>51.8</v>
+        <v>54.3</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>221.37</v>
+        <v>462.15</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.36</v>
+        <v>-31.73</v>
       </c>
       <c r="L26" t="n">
-        <v>241.03</v>
+        <v>463.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:49:29</t>
+          <t>05:44:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="F27" t="n">
-        <v>12.03</v>
+        <v>13.24</v>
       </c>
       <c r="G27" t="n">
-        <v>226.6</v>
+        <v>227.4</v>
       </c>
       <c r="H27" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-325.11</v>
+        <v>358.6</v>
       </c>
       <c r="K27" t="n">
-        <v>128.61</v>
+        <v>302.41</v>
       </c>
       <c r="L27" t="n">
-        <v>349.62</v>
+        <v>469.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:50:08</t>
+          <t>05:46:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.66</v>
+        <v>4.37</v>
       </c>
       <c r="F28" t="n">
-        <v>12.96</v>
+        <v>12.82</v>
       </c>
       <c r="G28" t="n">
-        <v>240.5</v>
+        <v>234.7</v>
       </c>
       <c r="H28" t="n">
-        <v>46.5</v>
+        <v>47.4</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>109.76</v>
+        <v>-550.22</v>
       </c>
       <c r="K28" t="n">
-        <v>65.03</v>
+        <v>-54.61</v>
       </c>
       <c r="L28" t="n">
-        <v>127.58</v>
+        <v>552.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:02:52</t>
+          <t>05:58:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.18</v>
+        <v>3.66</v>
       </c>
       <c r="F29" t="n">
-        <v>12.44</v>
+        <v>13.33</v>
       </c>
       <c r="G29" t="n">
-        <v>222.3</v>
+        <v>241.1</v>
       </c>
       <c r="H29" t="n">
-        <v>51.3</v>
+        <v>44</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>15.72</v>
+        <v>130.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-104.71</v>
+        <v>-70</v>
       </c>
       <c r="L29" t="n">
-        <v>105.88</v>
+        <v>147.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:03:21</t>
+          <t>06:00:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.65</v>
+        <v>3.93</v>
       </c>
       <c r="F30" t="n">
-        <v>13.26</v>
+        <v>12.89</v>
       </c>
       <c r="G30" t="n">
-        <v>247.9</v>
+        <v>236.1</v>
       </c>
       <c r="H30" t="n">
-        <v>54.6</v>
+        <v>50.6</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.61</v>
+        <v>-196.05</v>
       </c>
       <c r="K30" t="n">
-        <v>11.91</v>
+        <v>59.77</v>
       </c>
       <c r="L30" t="n">
-        <v>34.72</v>
+        <v>204.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:05:09</t>
+          <t>06:01:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="F31" t="n">
-        <v>13.1</v>
+        <v>12.56</v>
       </c>
       <c r="G31" t="n">
-        <v>219</v>
+        <v>240.3</v>
       </c>
       <c r="H31" t="n">
-        <v>54.3</v>
+        <v>50.8</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-121.44</v>
+        <v>41.71</v>
       </c>
       <c r="K31" t="n">
-        <v>2.63</v>
+        <v>297.92</v>
       </c>
       <c r="L31" t="n">
-        <v>121.46</v>
+        <v>300.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:08:58</t>
+          <t>06:07:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.37</v>
+        <v>4.03</v>
       </c>
       <c r="F32" t="n">
-        <v>13.3</v>
+        <v>12.83</v>
       </c>
       <c r="G32" t="n">
-        <v>241.1</v>
+        <v>219.2</v>
       </c>
       <c r="H32" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-90.65000000000001</v>
+        <v>21.06</v>
       </c>
       <c r="K32" t="n">
-        <v>-28.67</v>
+        <v>-32.39</v>
       </c>
       <c r="L32" t="n">
-        <v>95.08</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:10:58</t>
+          <t>06:09:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="F33" t="n">
-        <v>12.55</v>
+        <v>13.47</v>
       </c>
       <c r="G33" t="n">
-        <v>245.5</v>
+        <v>250</v>
       </c>
       <c r="H33" t="n">
-        <v>46</v>
+        <v>55.6</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-31.95</v>
+        <v>-90.16</v>
       </c>
       <c r="K33" t="n">
-        <v>-43.99</v>
+        <v>-97.38</v>
       </c>
       <c r="L33" t="n">
-        <v>54.37</v>
+        <v>132.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:11:53</t>
+          <t>06:10:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="F34" t="n">
-        <v>12.83</v>
+        <v>12.41</v>
       </c>
       <c r="G34" t="n">
-        <v>231.5</v>
+        <v>245</v>
       </c>
       <c r="H34" t="n">
-        <v>53</v>
+        <v>49.5</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.99</v>
+        <v>180.29</v>
       </c>
       <c r="K34" t="n">
-        <v>-166.68</v>
+        <v>36.29</v>
       </c>
       <c r="L34" t="n">
-        <v>173.73</v>
+        <v>183.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:16:05</t>
+          <t>06:14:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="F35" t="n">
-        <v>13.1</v>
+        <v>13.27</v>
       </c>
       <c r="G35" t="n">
-        <v>228.5</v>
+        <v>239.8</v>
       </c>
       <c r="H35" t="n">
-        <v>49.4</v>
+        <v>52.4</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-75.31</v>
+        <v>-163.88</v>
       </c>
       <c r="K35" t="n">
-        <v>306.83</v>
+        <v>-35.95</v>
       </c>
       <c r="L35" t="n">
-        <v>315.94</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:18:00</t>
+          <t>06:16:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="F36" t="n">
-        <v>12.72</v>
+        <v>13.28</v>
       </c>
       <c r="G36" t="n">
-        <v>243.3</v>
+        <v>236</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-30.4</v>
+        <v>155.22</v>
       </c>
       <c r="K36" t="n">
-        <v>155.82</v>
+        <v>255.65</v>
       </c>
       <c r="L36" t="n">
-        <v>158.76</v>
+        <v>299.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:20:25</t>
+          <t>06:18:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.03</v>
+        <v>3.56</v>
       </c>
       <c r="F37" t="n">
-        <v>12.22</v>
+        <v>12.43</v>
       </c>
       <c r="G37" t="n">
-        <v>240.7</v>
+        <v>238.7</v>
       </c>
       <c r="H37" t="n">
-        <v>54.4</v>
+        <v>53.2</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-56.68</v>
+        <v>-102.18</v>
       </c>
       <c r="K37" t="n">
-        <v>95.02</v>
+        <v>-3.84</v>
       </c>
       <c r="L37" t="n">
-        <v>110.64</v>
+        <v>102.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:26:06</t>
+          <t>06:23:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="F38" t="n">
-        <v>12.68</v>
+        <v>12.72</v>
       </c>
       <c r="G38" t="n">
-        <v>241.2</v>
+        <v>232.1</v>
       </c>
       <c r="H38" t="n">
-        <v>49.8</v>
+        <v>59.3</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>324.41</v>
+        <v>395.78</v>
       </c>
       <c r="K38" t="n">
-        <v>-442.69</v>
+        <v>-12.63</v>
       </c>
       <c r="L38" t="n">
-        <v>548.83</v>
+        <v>395.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:27:44</t>
+          <t>06:24:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.49</v>
+        <v>3.67</v>
       </c>
       <c r="F39" t="n">
-        <v>12.53</v>
+        <v>12.96</v>
       </c>
       <c r="G39" t="n">
-        <v>233.8</v>
+        <v>247.5</v>
       </c>
       <c r="H39" t="n">
-        <v>57.4</v>
+        <v>48.7</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-24.89</v>
+        <v>-217.52</v>
       </c>
       <c r="K39" t="n">
-        <v>-111.45</v>
+        <v>-212.33</v>
       </c>
       <c r="L39" t="n">
-        <v>114.2</v>
+        <v>303.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:29:40</t>
+          <t>06:26:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="F40" t="n">
-        <v>12.39</v>
+        <v>12.97</v>
       </c>
       <c r="G40" t="n">
-        <v>238.9</v>
+        <v>231.8</v>
       </c>
       <c r="H40" t="n">
-        <v>52.1</v>
+        <v>53.6</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-40.05</v>
+        <v>-230.29</v>
       </c>
       <c r="K40" t="n">
-        <v>336.26</v>
+        <v>21.55</v>
       </c>
       <c r="L40" t="n">
-        <v>338.64</v>
+        <v>231.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:35:38</t>
+          <t>06:30:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="F41" t="n">
-        <v>12.64</v>
+        <v>12.88</v>
       </c>
       <c r="G41" t="n">
-        <v>233.7</v>
+        <v>256.3</v>
       </c>
       <c r="H41" t="n">
-        <v>51</v>
+        <v>57.1</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>92.77</v>
+        <v>-126.45</v>
       </c>
       <c r="K41" t="n">
-        <v>-82.86</v>
+        <v>-156.45</v>
       </c>
       <c r="L41" t="n">
-        <v>124.38</v>
+        <v>201.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:37:38</t>
+          <t>06:32:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="F42" t="n">
-        <v>12.32</v>
+        <v>12.86</v>
       </c>
       <c r="G42" t="n">
-        <v>240.8</v>
+        <v>231.3</v>
       </c>
       <c r="H42" t="n">
-        <v>58.2</v>
+        <v>54.7</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-464.08</v>
+        <v>-174.9</v>
       </c>
       <c r="K42" t="n">
-        <v>8.98</v>
+        <v>543.54</v>
       </c>
       <c r="L42" t="n">
-        <v>464.16</v>
+        <v>570.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:38:42</t>
+          <t>06:34:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.36</v>
+        <v>3.34</v>
       </c>
       <c r="F43" t="n">
-        <v>11.67</v>
+        <v>12.43</v>
       </c>
       <c r="G43" t="n">
-        <v>230.5</v>
+        <v>238.5</v>
       </c>
       <c r="H43" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-474.72</v>
+        <v>-26.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-331.86</v>
+        <v>-165.83</v>
       </c>
       <c r="L43" t="n">
-        <v>579.21</v>
+        <v>167.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:49:57</t>
+          <t>06:45:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="F44" t="n">
-        <v>12.67</v>
+        <v>12.19</v>
       </c>
       <c r="G44" t="n">
-        <v>243.1</v>
+        <v>227.8</v>
       </c>
       <c r="H44" t="n">
-        <v>50.9</v>
+        <v>46.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-141.02</v>
+        <v>54.44</v>
       </c>
       <c r="K44" t="n">
-        <v>61.22</v>
+        <v>81.48</v>
       </c>
       <c r="L44" t="n">
-        <v>153.73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:52:08</t>
+          <t>06:47:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="F45" t="n">
-        <v>12.89</v>
+        <v>12.69</v>
       </c>
       <c r="G45" t="n">
-        <v>231.5</v>
+        <v>251.1</v>
       </c>
       <c r="H45" t="n">
-        <v>55.5</v>
+        <v>53.2</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-25.1</v>
+        <v>91.92</v>
       </c>
       <c r="K45" t="n">
-        <v>23.93</v>
+        <v>-127.83</v>
       </c>
       <c r="L45" t="n">
-        <v>34.68</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:54:20</t>
+          <t>06:49:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="F46" t="n">
-        <v>13.38</v>
+        <v>12.56</v>
       </c>
       <c r="G46" t="n">
-        <v>229.7</v>
+        <v>235.8</v>
       </c>
       <c r="H46" t="n">
-        <v>52.2</v>
+        <v>51.1</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-71.62</v>
+        <v>66.06</v>
       </c>
       <c r="K46" t="n">
-        <v>99.26000000000001</v>
+        <v>-122.06</v>
       </c>
       <c r="L46" t="n">
-        <v>122.4</v>
+        <v>138.79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:58:51</t>
+          <t>06:54:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.16</v>
+        <v>4.65</v>
       </c>
       <c r="F47" t="n">
-        <v>12.6</v>
+        <v>12.85</v>
       </c>
       <c r="G47" t="n">
-        <v>238.2</v>
+        <v>246</v>
       </c>
       <c r="H47" t="n">
-        <v>45.3</v>
+        <v>54.2</v>
       </c>
       <c r="I47" t="n">
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.43</v>
+        <v>372.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-149.09</v>
+        <v>105.03</v>
       </c>
       <c r="L47" t="n">
-        <v>149.16</v>
+        <v>386.97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:00:05</t>
+          <t>06:55:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="F48" t="n">
-        <v>12.47</v>
+        <v>12.72</v>
       </c>
       <c r="G48" t="n">
-        <v>247.4</v>
+        <v>228.5</v>
       </c>
       <c r="H48" t="n">
-        <v>54</v>
+        <v>51.6</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-26.19</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>210.84</v>
+        <v>67.38</v>
       </c>
       <c r="L48" t="n">
-        <v>212.46</v>
+        <v>100.13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:01:01</t>
+          <t>06:58:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="F49" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="G49" t="n">
-        <v>235.8</v>
+        <v>232.8</v>
       </c>
       <c r="H49" t="n">
-        <v>51.5</v>
+        <v>48</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-42.74</v>
+        <v>14.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-213.46</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>217.69</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:05:56</t>
+          <t>07:02:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="F50" t="n">
         <v>12.77</v>
       </c>
       <c r="G50" t="n">
-        <v>238.1</v>
+        <v>226.9</v>
       </c>
       <c r="H50" t="n">
-        <v>60.6</v>
+        <v>52</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>70.18000000000001</v>
+        <v>-357.5</v>
       </c>
       <c r="K50" t="n">
-        <v>2.41</v>
+        <v>355.27</v>
       </c>
       <c r="L50" t="n">
-        <v>70.22</v>
+        <v>504.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:06:26</t>
+          <t>07:03:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.28</v>
+        <v>3.68</v>
       </c>
       <c r="F51" t="n">
-        <v>12.75</v>
+        <v>12.82</v>
       </c>
       <c r="G51" t="n">
-        <v>235.7</v>
+        <v>235.8</v>
       </c>
       <c r="H51" t="n">
-        <v>45.6</v>
+        <v>54.9</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-95.84</v>
+        <v>27.34</v>
       </c>
       <c r="K51" t="n">
-        <v>143.52</v>
+        <v>612.97</v>
       </c>
       <c r="L51" t="n">
-        <v>172.57</v>
+        <v>613.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:08:52</t>
+          <t>07:05:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.06</v>
+        <v>5.51</v>
       </c>
       <c r="F52" t="n">
-        <v>12.36</v>
+        <v>12.92</v>
       </c>
       <c r="G52" t="n">
-        <v>234.8</v>
+        <v>240</v>
       </c>
       <c r="H52" t="n">
-        <v>47.6</v>
+        <v>50.3</v>
       </c>
       <c r="I52" t="n">
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>311.74</v>
+        <v>-430.46</v>
       </c>
       <c r="K52" t="n">
-        <v>241.99</v>
+        <v>360.33</v>
       </c>
       <c r="L52" t="n">
-        <v>394.64</v>
+        <v>561.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:14:47</t>
+          <t>07:11:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="F53" t="n">
-        <v>12.54</v>
+        <v>12.42</v>
       </c>
       <c r="G53" t="n">
-        <v>237.5</v>
+        <v>245.4</v>
       </c>
       <c r="H53" t="n">
-        <v>51.1</v>
+        <v>55.7</v>
       </c>
       <c r="I53" t="n">
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-80.95999999999999</v>
+        <v>-58.79</v>
       </c>
       <c r="K53" t="n">
-        <v>22.86</v>
+        <v>144.48</v>
       </c>
       <c r="L53" t="n">
-        <v>84.13</v>
+        <v>155.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:15:41</t>
+          <t>07:13:37</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.94</v>
+        <v>3.59</v>
       </c>
       <c r="F54" t="n">
-        <v>12.41</v>
+        <v>12.39</v>
       </c>
       <c r="G54" t="n">
-        <v>240.9</v>
+        <v>232.5</v>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-420.77</v>
+        <v>-98.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-544.51</v>
+        <v>180.1</v>
       </c>
       <c r="L54" t="n">
-        <v>688.14</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:17:56</t>
+          <t>07:14:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.18</v>
+        <v>4.42</v>
       </c>
       <c r="F55" t="n">
-        <v>12.78</v>
+        <v>12.16</v>
       </c>
       <c r="G55" t="n">
-        <v>224.3</v>
+        <v>225.6</v>
       </c>
       <c r="H55" t="n">
-        <v>49.7</v>
+        <v>42.9</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-699.62</v>
+        <v>-154.95</v>
       </c>
       <c r="K55" t="n">
-        <v>439.64</v>
+        <v>-229.84</v>
       </c>
       <c r="L55" t="n">
-        <v>826.29</v>
+        <v>277.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:22:49</t>
+          <t>07:19:29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="F56" t="n">
-        <v>12.89</v>
+        <v>13.1</v>
       </c>
       <c r="G56" t="n">
-        <v>234.2</v>
+        <v>238.7</v>
       </c>
       <c r="H56" t="n">
-        <v>51.1</v>
+        <v>55.3</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-508.11</v>
+        <v>143.34</v>
       </c>
       <c r="K56" t="n">
-        <v>93.13</v>
+        <v>-220.56</v>
       </c>
       <c r="L56" t="n">
-        <v>516.58</v>
+        <v>263.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:23:39</t>
+          <t>07:21:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="F57" t="n">
-        <v>12.85</v>
+        <v>12.71</v>
       </c>
       <c r="G57" t="n">
-        <v>234.7</v>
+        <v>229.9</v>
       </c>
       <c r="H57" t="n">
-        <v>51.1</v>
+        <v>53.6</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>76.37</v>
+        <v>-106.99</v>
       </c>
       <c r="K57" t="n">
-        <v>-200.32</v>
+        <v>137.99</v>
       </c>
       <c r="L57" t="n">
-        <v>214.38</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:25:05</t>
+          <t>07:22:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.95</v>
+        <v>4.44</v>
       </c>
       <c r="F58" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="G58" t="n">
-        <v>254.9</v>
+        <v>232.8</v>
       </c>
       <c r="H58" t="n">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-229.31</v>
+        <v>-848.22</v>
       </c>
       <c r="K58" t="n">
-        <v>42.76</v>
+        <v>-427.46</v>
       </c>
       <c r="L58" t="n">
-        <v>233.26</v>
+        <v>949.84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:33:17</t>
+          <t>07:33:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.31</v>
+        <v>4.01</v>
       </c>
       <c r="F59" t="n">
-        <v>12.65</v>
+        <v>12.07</v>
       </c>
       <c r="G59" t="n">
-        <v>242.6</v>
+        <v>234.4</v>
       </c>
       <c r="H59" t="n">
-        <v>55.3</v>
+        <v>55</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>8.970000000000001</v>
+        <v>-6.91</v>
       </c>
       <c r="K59" t="n">
-        <v>221.05</v>
+        <v>-56.2</v>
       </c>
       <c r="L59" t="n">
-        <v>221.23</v>
+        <v>56.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:34:06</t>
+          <t>07:34:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="F60" t="n">
-        <v>12.44</v>
+        <v>13.04</v>
       </c>
       <c r="G60" t="n">
-        <v>241.2</v>
+        <v>239.3</v>
       </c>
       <c r="H60" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-119.12</v>
+        <v>-158.49</v>
       </c>
       <c r="K60" t="n">
-        <v>-8.949999999999999</v>
+        <v>-43.8</v>
       </c>
       <c r="L60" t="n">
-        <v>119.46</v>
+        <v>164.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:36:01</t>
+          <t>07:36:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.91</v>
+        <v>4.49</v>
       </c>
       <c r="F61" t="n">
-        <v>13.23</v>
+        <v>13.08</v>
       </c>
       <c r="G61" t="n">
-        <v>234.1</v>
+        <v>251.2</v>
       </c>
       <c r="H61" t="n">
-        <v>47.2</v>
+        <v>50.2</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-247.68</v>
+        <v>10.15</v>
       </c>
       <c r="K61" t="n">
-        <v>91.66</v>
+        <v>224.99</v>
       </c>
       <c r="L61" t="n">
-        <v>264.1</v>
+        <v>225.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:41:18</t>
+          <t>07:42:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.24</v>
+        <v>3.82</v>
       </c>
       <c r="F62" t="n">
-        <v>13.31</v>
+        <v>12.9</v>
       </c>
       <c r="G62" t="n">
-        <v>253.8</v>
+        <v>241.3</v>
       </c>
       <c r="H62" t="n">
-        <v>46.6</v>
+        <v>52.5</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>108.53</v>
+        <v>-110.68</v>
       </c>
       <c r="K62" t="n">
-        <v>-163.36</v>
+        <v>-204.68</v>
       </c>
       <c r="L62" t="n">
-        <v>196.13</v>
+        <v>232.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:42:52</t>
+          <t>07:44:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.14</v>
+        <v>3.83</v>
       </c>
       <c r="F63" t="n">
-        <v>12.6</v>
+        <v>12.47</v>
       </c>
       <c r="G63" t="n">
-        <v>241.6</v>
+        <v>239.2</v>
       </c>
       <c r="H63" t="n">
-        <v>49</v>
+        <v>43.9</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.13</v>
+        <v>6.24</v>
       </c>
       <c r="K63" t="n">
-        <v>-62.15</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>62.19</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:44:37</t>
+          <t>07:45:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.07</v>
+        <v>4.75</v>
       </c>
       <c r="F64" t="n">
-        <v>13.43</v>
+        <v>12.46</v>
       </c>
       <c r="G64" t="n">
-        <v>237.8</v>
+        <v>237.9</v>
       </c>
       <c r="H64" t="n">
-        <v>58.2</v>
+        <v>53.9</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>114.79</v>
+        <v>201.2</v>
       </c>
       <c r="K64" t="n">
-        <v>-114.56</v>
+        <v>139.81</v>
       </c>
       <c r="L64" t="n">
-        <v>162.17</v>
+        <v>245.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:50:28</t>
+          <t>07:50:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.52</v>
+        <v>3.48</v>
       </c>
       <c r="F65" t="n">
-        <v>12.86</v>
+        <v>13.01</v>
       </c>
       <c r="G65" t="n">
-        <v>247.2</v>
+        <v>224.1</v>
       </c>
       <c r="H65" t="n">
-        <v>52.1</v>
+        <v>55.8</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-106.27</v>
+        <v>21.56</v>
       </c>
       <c r="K65" t="n">
-        <v>-259.4</v>
+        <v>-132.13</v>
       </c>
       <c r="L65" t="n">
-        <v>280.32</v>
+        <v>133.88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:51:43</t>
+          <t>07:52:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.47</v>
+        <v>4.57</v>
       </c>
       <c r="F66" t="n">
-        <v>12.44</v>
+        <v>12.04</v>
       </c>
       <c r="G66" t="n">
-        <v>246.6</v>
+        <v>228.3</v>
       </c>
       <c r="H66" t="n">
-        <v>54.8</v>
+        <v>45.8</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>37.93</v>
+        <v>343.47</v>
       </c>
       <c r="K66" t="n">
-        <v>60.36</v>
+        <v>259.2</v>
       </c>
       <c r="L66" t="n">
-        <v>71.29000000000001</v>
+        <v>430.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:53:52</t>
+          <t>07:54:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.39</v>
+        <v>4.04</v>
       </c>
       <c r="F67" t="n">
-        <v>12.11</v>
+        <v>13.25</v>
       </c>
       <c r="G67" t="n">
-        <v>244.7</v>
+        <v>237.6</v>
       </c>
       <c r="H67" t="n">
         <v>47.6</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>132.46</v>
+        <v>-124.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-253.57</v>
+        <v>-498.36</v>
       </c>
       <c r="L67" t="n">
-        <v>286.08</v>
+        <v>513.6900000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:57:48</t>
+          <t>07:59:25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.45</v>
+        <v>3.64</v>
       </c>
       <c r="F68" t="n">
-        <v>13.35</v>
+        <v>12.53</v>
       </c>
       <c r="G68" t="n">
-        <v>232.6</v>
+        <v>235.2</v>
       </c>
       <c r="H68" t="n">
-        <v>50.4</v>
+        <v>52.5</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>352.63</v>
+        <v>-333.96</v>
       </c>
       <c r="K68" t="n">
-        <v>727.24</v>
+        <v>507.08</v>
       </c>
       <c r="L68" t="n">
-        <v>808.22</v>
+        <v>607.1799999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:59:19</t>
+          <t>08:01:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.85</v>
+        <v>4.82</v>
       </c>
       <c r="F69" t="n">
-        <v>13.06</v>
+        <v>12.95</v>
       </c>
       <c r="G69" t="n">
-        <v>236</v>
+        <v>236.8</v>
       </c>
       <c r="H69" t="n">
-        <v>55.8</v>
+        <v>52.3</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>141.86</v>
+        <v>-458.59</v>
       </c>
       <c r="K69" t="n">
-        <v>-35.72</v>
+        <v>411.24</v>
       </c>
       <c r="L69" t="n">
-        <v>146.29</v>
+        <v>615.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:00:19</t>
+          <t>08:03:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="F70" t="n">
-        <v>12.86</v>
+        <v>11.76</v>
       </c>
       <c r="G70" t="n">
-        <v>239.8</v>
+        <v>245.4</v>
       </c>
       <c r="H70" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>754.33</v>
+        <v>-282.53</v>
       </c>
       <c r="K70" t="n">
-        <v>-518.05</v>
+        <v>3.6</v>
       </c>
       <c r="L70" t="n">
-        <v>915.09</v>
+        <v>282.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:04:46</t>
+          <t>08:08:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.15</v>
+        <v>4.64</v>
       </c>
       <c r="F71" t="n">
-        <v>11.89</v>
+        <v>12.28</v>
       </c>
       <c r="G71" t="n">
-        <v>241</v>
+        <v>234.5</v>
       </c>
       <c r="H71" t="n">
-        <v>58.3</v>
+        <v>50.1</v>
       </c>
       <c r="I71" t="n">
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-558.09</v>
+        <v>-16.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-424.22</v>
+        <v>197.11</v>
       </c>
       <c r="L71" t="n">
-        <v>701.02</v>
+        <v>197.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:06:44</t>
+          <t>08:09:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.14</v>
+        <v>3.81</v>
       </c>
       <c r="F72" t="n">
-        <v>12.54</v>
+        <v>12.61</v>
       </c>
       <c r="G72" t="n">
-        <v>232.2</v>
+        <v>236</v>
       </c>
       <c r="H72" t="n">
-        <v>58</v>
+        <v>51.1</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-184.4</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>193.16</v>
+        <v>-390.14</v>
       </c>
       <c r="L72" t="n">
-        <v>267.05</v>
+        <v>395.52</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:08:52</t>
+          <t>08:10:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.79</v>
+        <v>4.09</v>
       </c>
       <c r="F73" t="n">
-        <v>12.91</v>
+        <v>11.74</v>
       </c>
       <c r="G73" t="n">
-        <v>235.6</v>
+        <v>227.5</v>
       </c>
       <c r="H73" t="n">
-        <v>49.4</v>
+        <v>56.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.640000000000001</v>
+        <v>-531.9400000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-333.22</v>
+        <v>-1288.57</v>
       </c>
       <c r="L73" t="n">
-        <v>333.33</v>
+        <v>1394.05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:16:23</t>
+          <t>08:22:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>4.89</v>
       </c>
       <c r="F74" t="n">
-        <v>11.93</v>
+        <v>12.87</v>
       </c>
       <c r="G74" t="n">
-        <v>239.4</v>
+        <v>235.7</v>
       </c>
       <c r="H74" t="n">
-        <v>51.9</v>
+        <v>54.3</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>5.47</v>
+        <v>140.47</v>
       </c>
       <c r="K74" t="n">
-        <v>11.69</v>
+        <v>30.21</v>
       </c>
       <c r="L74" t="n">
-        <v>12.91</v>
+        <v>143.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:18:03</t>
+          <t>08:24:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="F75" t="n">
-        <v>12.33</v>
+        <v>12.83</v>
       </c>
       <c r="G75" t="n">
-        <v>233.4</v>
+        <v>229.8</v>
       </c>
       <c r="H75" t="n">
-        <v>53</v>
+        <v>52.3</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-118.61</v>
+        <v>-37.55</v>
       </c>
       <c r="K75" t="n">
-        <v>-49.15</v>
+        <v>-16.07</v>
       </c>
       <c r="L75" t="n">
-        <v>128.4</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:19:31</t>
+          <t>08:25:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.3</v>
+        <v>3.76</v>
       </c>
       <c r="F76" t="n">
-        <v>13.16</v>
+        <v>12.43</v>
       </c>
       <c r="G76" t="n">
-        <v>252.7</v>
+        <v>236</v>
       </c>
       <c r="H76" t="n">
-        <v>42.6</v>
+        <v>46.7</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.85</v>
+        <v>175.09</v>
       </c>
       <c r="K76" t="n">
-        <v>-176.34</v>
+        <v>-133</v>
       </c>
       <c r="L76" t="n">
-        <v>176.37</v>
+        <v>219.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:25:30</t>
+          <t>08:31:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="F77" t="n">
-        <v>12.93</v>
+        <v>12.61</v>
       </c>
       <c r="G77" t="n">
-        <v>238.4</v>
+        <v>238.8</v>
       </c>
       <c r="H77" t="n">
-        <v>51.7</v>
+        <v>50.1</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>94.64</v>
+        <v>-179.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-122.39</v>
+        <v>47.96</v>
       </c>
       <c r="L77" t="n">
-        <v>154.71</v>
+        <v>185.48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:26:59</t>
+          <t>08:33:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
       <c r="F78" t="n">
-        <v>12.96</v>
+        <v>11.86</v>
       </c>
       <c r="G78" t="n">
-        <v>226.9</v>
+        <v>248.9</v>
       </c>
       <c r="H78" t="n">
-        <v>58</v>
+        <v>50.4</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-39.61</v>
+        <v>108.55</v>
       </c>
       <c r="K78" t="n">
-        <v>398.41</v>
+        <v>-159.37</v>
       </c>
       <c r="L78" t="n">
-        <v>400.37</v>
+        <v>192.83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:28:42</t>
+          <t>08:35:11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.41</v>
+        <v>3.83</v>
       </c>
       <c r="F79" t="n">
-        <v>12.58</v>
+        <v>12.74</v>
       </c>
       <c r="G79" t="n">
-        <v>244.7</v>
+        <v>245.2</v>
       </c>
       <c r="H79" t="n">
-        <v>50.7</v>
+        <v>54.1</v>
       </c>
       <c r="I79" t="n">
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>154.6</v>
+        <v>-224.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-265.37</v>
+        <v>8.82</v>
       </c>
       <c r="L79" t="n">
-        <v>307.12</v>
+        <v>224.77</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:34:20</t>
+          <t>08:40:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.25</v>
+        <v>4.78</v>
       </c>
       <c r="F80" t="n">
-        <v>12.45</v>
+        <v>13.07</v>
       </c>
       <c r="G80" t="n">
-        <v>231.3</v>
+        <v>233.3</v>
       </c>
       <c r="H80" t="n">
-        <v>46.2</v>
+        <v>57.3</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-87.73999999999999</v>
+        <v>123.37</v>
       </c>
       <c r="K80" t="n">
-        <v>357.3</v>
+        <v>305.6</v>
       </c>
       <c r="L80" t="n">
-        <v>367.91</v>
+        <v>329.56</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:35:02</t>
+          <t>08:43:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="F81" t="n">
-        <v>13.18</v>
+        <v>12.64</v>
       </c>
       <c r="G81" t="n">
-        <v>211.8</v>
+        <v>237.1</v>
       </c>
       <c r="H81" t="n">
-        <v>51.8</v>
+        <v>53.6</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>137.29</v>
+        <v>29.56</v>
       </c>
       <c r="K81" t="n">
-        <v>162.8</v>
+        <v>-134.68</v>
       </c>
       <c r="L81" t="n">
-        <v>212.96</v>
+        <v>137.88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:37:24</t>
+          <t>08:44:37</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.96</v>
+        <v>4.26</v>
       </c>
       <c r="F82" t="n">
-        <v>12.93</v>
+        <v>12.78</v>
       </c>
       <c r="G82" t="n">
-        <v>240.5</v>
+        <v>241.9</v>
       </c>
       <c r="H82" t="n">
-        <v>52.1</v>
+        <v>38.1</v>
       </c>
       <c r="I82" t="n">
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>168.97</v>
+        <v>-89.81999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>234.54</v>
+        <v>-0.15</v>
       </c>
       <c r="L82" t="n">
-        <v>289.07</v>
+        <v>89.81999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:42:40</t>
+          <t>08:48:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="F83" t="n">
-        <v>13.31</v>
+        <v>12.41</v>
       </c>
       <c r="G83" t="n">
-        <v>233.3</v>
+        <v>252.8</v>
       </c>
       <c r="H83" t="n">
-        <v>55.7</v>
+        <v>52.7</v>
       </c>
       <c r="I83" t="n">
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>325.46</v>
+        <v>518.47</v>
       </c>
       <c r="K83" t="n">
-        <v>452.28</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>557.21</v>
+        <v>522.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:44:39</t>
+          <t>08:50:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.43</v>
+        <v>4.63</v>
       </c>
       <c r="F84" t="n">
-        <v>12.95</v>
+        <v>12.91</v>
       </c>
       <c r="G84" t="n">
-        <v>240.9</v>
+        <v>245.9</v>
       </c>
       <c r="H84" t="n">
-        <v>47.8</v>
+        <v>50.7</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>579.77</v>
+        <v>6.52</v>
       </c>
       <c r="K84" t="n">
-        <v>-148.12</v>
+        <v>-397.92</v>
       </c>
       <c r="L84" t="n">
-        <v>598.4</v>
+        <v>397.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:46:43</t>
+          <t>08:52:23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.57</v>
+        <v>4.78</v>
       </c>
       <c r="F85" t="n">
-        <v>12.6</v>
+        <v>12.83</v>
       </c>
       <c r="G85" t="n">
-        <v>240.2</v>
+        <v>234.3</v>
       </c>
       <c r="H85" t="n">
-        <v>52.1</v>
+        <v>53</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-134.09</v>
+        <v>689.36</v>
       </c>
       <c r="K85" t="n">
-        <v>764.75</v>
+        <v>341.64</v>
       </c>
       <c r="L85" t="n">
-        <v>776.42</v>
+        <v>769.38</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:50:57</t>
+          <t>08:58:18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="F86" t="n">
-        <v>12.74</v>
+        <v>11.81</v>
       </c>
       <c r="G86" t="n">
-        <v>230.7</v>
+        <v>229.1</v>
       </c>
       <c r="H86" t="n">
-        <v>58.8</v>
+        <v>49.6</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-260.45</v>
+        <v>-192.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-213.55</v>
+        <v>194.97</v>
       </c>
       <c r="L86" t="n">
-        <v>336.8</v>
+        <v>273.69</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:52:39</t>
+          <t>09:00:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.14</v>
+        <v>4.29</v>
       </c>
       <c r="F87" t="n">
-        <v>13.23</v>
+        <v>12.54</v>
       </c>
       <c r="G87" t="n">
-        <v>247.7</v>
+        <v>245</v>
       </c>
       <c r="H87" t="n">
-        <v>53</v>
+        <v>45.8</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-113.37</v>
+        <v>319.46</v>
       </c>
       <c r="K87" t="n">
-        <v>135.86</v>
+        <v>361.38</v>
       </c>
       <c r="L87" t="n">
-        <v>176.95</v>
+        <v>482.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:54:26</t>
+          <t>09:02:45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="F88" t="n">
-        <v>12.49</v>
+        <v>12.32</v>
       </c>
       <c r="G88" t="n">
-        <v>231.4</v>
+        <v>226</v>
       </c>
       <c r="H88" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-531.8</v>
+        <v>-817.8</v>
       </c>
       <c r="K88" t="n">
-        <v>-425.64</v>
+        <v>-231.14</v>
       </c>
       <c r="L88" t="n">
-        <v>681.16</v>
+        <v>849.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-50.95</v>
+        <v>-44.81</v>
       </c>
       <c r="K14" t="n">
-        <v>191.24</v>
+        <v>168.21</v>
       </c>
       <c r="L14" t="n">
-        <v>197.91</v>
+        <v>174.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-105.7</v>
+        <v>-133.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-87.56</v>
+        <v>-110.36</v>
       </c>
       <c r="L15" t="n">
-        <v>137.26</v>
+        <v>172.99</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-183.91</v>
+        <v>-152.79</v>
       </c>
       <c r="K16" t="n">
-        <v>-278.57</v>
+        <v>-231.43</v>
       </c>
       <c r="L16" t="n">
-        <v>333.8</v>
+        <v>277.32</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>60.18</v>
+        <v>124.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.59</v>
+        <v>-17.73</v>
       </c>
       <c r="L17" t="n">
-        <v>60.79</v>
+        <v>125.56</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>94.37</v>
+        <v>138.07</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.19</v>
+        <v>-17.84</v>
       </c>
       <c r="L18" t="n">
-        <v>95.15000000000001</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-67.09</v>
+        <v>-86.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>17.21</v>
+        <v>22.14</v>
       </c>
       <c r="L19" t="n">
-        <v>69.26000000000001</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>215.14</v>
+        <v>239.5</v>
       </c>
       <c r="K20" t="n">
-        <v>-121.21</v>
+        <v>-134.94</v>
       </c>
       <c r="L20" t="n">
-        <v>246.93</v>
+        <v>274.9</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-45.84</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>121.47</v>
+        <v>191.37</v>
       </c>
       <c r="L21" t="n">
-        <v>129.83</v>
+        <v>204.54</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>15.31</v>
+        <v>28.48</v>
       </c>
       <c r="K22" t="n">
-        <v>-123.94</v>
+        <v>-230.46</v>
       </c>
       <c r="L22" t="n">
-        <v>124.88</v>
+        <v>232.21</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>135.15</v>
+        <v>253.18</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.38</v>
+        <v>-2.59</v>
       </c>
       <c r="L23" t="n">
-        <v>135.16</v>
+        <v>253.19</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>12.88</v>
+        <v>13.26</v>
       </c>
       <c r="K24" t="n">
-        <v>-872.83</v>
+        <v>-898.9</v>
       </c>
       <c r="L24" t="n">
-        <v>872.9299999999999</v>
+        <v>899</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-117.17</v>
+        <v>-138.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-603.35</v>
+        <v>-713.3</v>
       </c>
       <c r="L25" t="n">
-        <v>614.62</v>
+        <v>726.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>462.15</v>
+        <v>672.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-31.73</v>
+        <v>-46.16</v>
       </c>
       <c r="L26" t="n">
-        <v>463.24</v>
+        <v>673.8200000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>358.6</v>
+        <v>493.41</v>
       </c>
       <c r="K27" t="n">
-        <v>302.41</v>
+        <v>416.1</v>
       </c>
       <c r="L27" t="n">
-        <v>469.09</v>
+        <v>645.4400000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-550.22</v>
+        <v>-799.0599999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-54.61</v>
+        <v>-79.31</v>
       </c>
       <c r="L28" t="n">
-        <v>552.92</v>
+        <v>802.99</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>130.14</v>
+        <v>155.68</v>
       </c>
       <c r="K29" t="n">
-        <v>-70</v>
+        <v>-83.73999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>147.77</v>
+        <v>176.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-196.05</v>
+        <v>-207.5</v>
       </c>
       <c r="K30" t="n">
-        <v>59.77</v>
+        <v>63.26</v>
       </c>
       <c r="L30" t="n">
-        <v>204.95</v>
+        <v>216.93</v>
       </c>
     </row>
     <row r="31">
@@ -1357,10 +1357,10 @@
         <v>41.71</v>
       </c>
       <c r="K31" t="n">
-        <v>297.92</v>
+        <v>297.91</v>
       </c>
       <c r="L31" t="n">
-        <v>300.83</v>
+        <v>300.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>21.06</v>
+        <v>63.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.39</v>
+        <v>-98.3</v>
       </c>
       <c r="L32" t="n">
-        <v>38.64</v>
+        <v>117.26</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-90.16</v>
+        <v>-96.26000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-97.38</v>
+        <v>-103.97</v>
       </c>
       <c r="L33" t="n">
-        <v>132.71</v>
+        <v>141.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>180.29</v>
+        <v>195.11</v>
       </c>
       <c r="K34" t="n">
-        <v>36.29</v>
+        <v>39.27</v>
       </c>
       <c r="L34" t="n">
-        <v>183.91</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-163.88</v>
+        <v>-264.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-35.95</v>
+        <v>-57.98</v>
       </c>
       <c r="L35" t="n">
-        <v>167.78</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>155.22</v>
+        <v>183.74</v>
       </c>
       <c r="K36" t="n">
-        <v>255.65</v>
+        <v>302.62</v>
       </c>
       <c r="L36" t="n">
-        <v>299.08</v>
+        <v>354.03</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-102.18</v>
+        <v>-160.94</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.84</v>
+        <v>-6.04</v>
       </c>
       <c r="L37" t="n">
-        <v>102.26</v>
+        <v>161.05</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>395.78</v>
+        <v>513.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.63</v>
+        <v>-16.38</v>
       </c>
       <c r="L38" t="n">
-        <v>395.98</v>
+        <v>513.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-217.52</v>
+        <v>-280.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-212.33</v>
+        <v>-273.53</v>
       </c>
       <c r="L39" t="n">
-        <v>303.97</v>
+        <v>391.6</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-230.29</v>
+        <v>-349.49</v>
       </c>
       <c r="K40" t="n">
-        <v>21.55</v>
+        <v>32.71</v>
       </c>
       <c r="L40" t="n">
-        <v>231.3</v>
+        <v>351.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-126.45</v>
+        <v>-222.08</v>
       </c>
       <c r="K41" t="n">
-        <v>-156.45</v>
+        <v>-274.77</v>
       </c>
       <c r="L41" t="n">
-        <v>201.16</v>
+        <v>353.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-174.9</v>
+        <v>-205.5</v>
       </c>
       <c r="K42" t="n">
-        <v>543.54</v>
+        <v>638.64</v>
       </c>
       <c r="L42" t="n">
-        <v>570.99</v>
+        <v>670.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.74</v>
+        <v>-47.53</v>
       </c>
       <c r="K43" t="n">
-        <v>-165.83</v>
+        <v>-294.7</v>
       </c>
       <c r="L43" t="n">
-        <v>167.97</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>54.44</v>
+        <v>74.81</v>
       </c>
       <c r="K44" t="n">
-        <v>81.48</v>
+        <v>111.97</v>
       </c>
       <c r="L44" t="n">
-        <v>98</v>
+        <v>134.66</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>91.92</v>
+        <v>105.57</v>
       </c>
       <c r="K45" t="n">
-        <v>-127.83</v>
+        <v>-146.8</v>
       </c>
       <c r="L45" t="n">
-        <v>157.45</v>
+        <v>180.82</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>66.06</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-122.06</v>
+        <v>-142.76</v>
       </c>
       <c r="L46" t="n">
-        <v>138.79</v>
+        <v>162.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>372.45</v>
+        <v>381.23</v>
       </c>
       <c r="K47" t="n">
-        <v>105.03</v>
+        <v>107.51</v>
       </c>
       <c r="L47" t="n">
-        <v>386.97</v>
+        <v>396.1</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-74.06999999999999</v>
+        <v>-118.26</v>
       </c>
       <c r="K48" t="n">
-        <v>67.38</v>
+        <v>107.58</v>
       </c>
       <c r="L48" t="n">
-        <v>100.13</v>
+        <v>159.87</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>14.42</v>
+        <v>19.48</v>
       </c>
       <c r="K49" t="n">
-        <v>95.18000000000001</v>
+        <v>128.61</v>
       </c>
       <c r="L49" t="n">
-        <v>96.26000000000001</v>
+        <v>130.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-357.5</v>
+        <v>-327.08</v>
       </c>
       <c r="K50" t="n">
-        <v>355.27</v>
+        <v>325.05</v>
       </c>
       <c r="L50" t="n">
-        <v>504.01</v>
+        <v>461.13</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>27.34</v>
+        <v>28.11</v>
       </c>
       <c r="K51" t="n">
-        <v>612.97</v>
+        <v>630.35</v>
       </c>
       <c r="L51" t="n">
-        <v>613.58</v>
+        <v>630.98</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-430.46</v>
+        <v>-543.5700000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>360.33</v>
+        <v>455.01</v>
       </c>
       <c r="L52" t="n">
-        <v>561.37</v>
+        <v>708.87</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-58.79</v>
+        <v>-137.07</v>
       </c>
       <c r="K53" t="n">
-        <v>144.48</v>
+        <v>336.88</v>
       </c>
       <c r="L53" t="n">
-        <v>155.98</v>
+        <v>363.7</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-98.22</v>
+        <v>-164.03</v>
       </c>
       <c r="K54" t="n">
-        <v>180.1</v>
+        <v>300.76</v>
       </c>
       <c r="L54" t="n">
-        <v>205.15</v>
+        <v>342.58</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-154.95</v>
+        <v>-252.68</v>
       </c>
       <c r="K55" t="n">
-        <v>-229.84</v>
+        <v>-374.81</v>
       </c>
       <c r="L55" t="n">
-        <v>277.19</v>
+        <v>452.03</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>143.34</v>
+        <v>215.02</v>
       </c>
       <c r="K56" t="n">
-        <v>-220.56</v>
+        <v>-330.86</v>
       </c>
       <c r="L56" t="n">
-        <v>263.05</v>
+        <v>394.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-106.99</v>
+        <v>-241.89</v>
       </c>
       <c r="K57" t="n">
-        <v>137.99</v>
+        <v>311.99</v>
       </c>
       <c r="L57" t="n">
-        <v>174.61</v>
+        <v>394.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-848.22</v>
+        <v>-895.5</v>
       </c>
       <c r="K58" t="n">
-        <v>-427.46</v>
+        <v>-451.28</v>
       </c>
       <c r="L58" t="n">
-        <v>949.84</v>
+        <v>1002.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.91</v>
+        <v>-13.74</v>
       </c>
       <c r="K59" t="n">
-        <v>-56.2</v>
+        <v>-111.79</v>
       </c>
       <c r="L59" t="n">
-        <v>56.62</v>
+        <v>112.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-158.49</v>
+        <v>-213.64</v>
       </c>
       <c r="K60" t="n">
-        <v>-43.8</v>
+        <v>-59.04</v>
       </c>
       <c r="L60" t="n">
-        <v>164.44</v>
+        <v>221.65</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>10.15</v>
+        <v>12.1</v>
       </c>
       <c r="K61" t="n">
-        <v>224.99</v>
+        <v>268.17</v>
       </c>
       <c r="L61" t="n">
-        <v>225.22</v>
+        <v>268.44</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-110.68</v>
+        <v>-108.46</v>
       </c>
       <c r="K62" t="n">
-        <v>-204.68</v>
+        <v>-200.57</v>
       </c>
       <c r="L62" t="n">
-        <v>232.69</v>
+        <v>228.01</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>6.24</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-75.34999999999999</v>
+        <v>-120.32</v>
       </c>
       <c r="L63" t="n">
-        <v>75.61</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>201.2</v>
+        <v>246.14</v>
       </c>
       <c r="K64" t="n">
-        <v>139.81</v>
+        <v>171.03</v>
       </c>
       <c r="L64" t="n">
-        <v>245.01</v>
+        <v>299.73</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>21.56</v>
+        <v>34.55</v>
       </c>
       <c r="K65" t="n">
-        <v>-132.13</v>
+        <v>-211.78</v>
       </c>
       <c r="L65" t="n">
-        <v>133.88</v>
+        <v>214.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>343.47</v>
+        <v>416.68</v>
       </c>
       <c r="K66" t="n">
-        <v>259.2</v>
+        <v>314.45</v>
       </c>
       <c r="L66" t="n">
-        <v>430.3</v>
+        <v>522.02</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-124.55</v>
+        <v>-128</v>
       </c>
       <c r="K67" t="n">
-        <v>-498.36</v>
+        <v>-512.14</v>
       </c>
       <c r="L67" t="n">
-        <v>513.6900000000001</v>
+        <v>527.9</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-333.96</v>
+        <v>-336.96</v>
       </c>
       <c r="K68" t="n">
-        <v>507.08</v>
+        <v>511.64</v>
       </c>
       <c r="L68" t="n">
-        <v>607.1799999999999</v>
+        <v>612.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-458.59</v>
+        <v>-569.8200000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>411.24</v>
+        <v>510.99</v>
       </c>
       <c r="L69" t="n">
-        <v>615.97</v>
+        <v>765.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-282.53</v>
+        <v>-368.11</v>
       </c>
       <c r="K70" t="n">
-        <v>3.6</v>
+        <v>4.69</v>
       </c>
       <c r="L70" t="n">
-        <v>282.55</v>
+        <v>368.14</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.59</v>
+        <v>-38.38</v>
       </c>
       <c r="K71" t="n">
-        <v>197.11</v>
+        <v>456.02</v>
       </c>
       <c r="L71" t="n">
-        <v>197.8</v>
+        <v>457.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>65.01000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-390.14</v>
+        <v>-501.21</v>
       </c>
       <c r="L72" t="n">
-        <v>395.52</v>
+        <v>508.13</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-531.9400000000001</v>
+        <v>-605.1799999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-1288.57</v>
+        <v>-1465.98</v>
       </c>
       <c r="L73" t="n">
-        <v>1394.05</v>
+        <v>1585.98</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>140.47</v>
+        <v>197.76</v>
       </c>
       <c r="K74" t="n">
-        <v>30.21</v>
+        <v>42.53</v>
       </c>
       <c r="L74" t="n">
-        <v>143.69</v>
+        <v>202.28</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.55</v>
+        <v>-79.86</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.07</v>
+        <v>-34.17</v>
       </c>
       <c r="L75" t="n">
-        <v>40.85</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>175.09</v>
+        <v>153.93</v>
       </c>
       <c r="K76" t="n">
-        <v>-133</v>
+        <v>-116.92</v>
       </c>
       <c r="L76" t="n">
-        <v>219.88</v>
+        <v>193.3</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-179.17</v>
+        <v>-255.24</v>
       </c>
       <c r="K77" t="n">
-        <v>47.96</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>185.48</v>
+        <v>264.23</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>108.55</v>
+        <v>134.49</v>
       </c>
       <c r="K78" t="n">
-        <v>-159.37</v>
+        <v>-197.45</v>
       </c>
       <c r="L78" t="n">
-        <v>192.83</v>
+        <v>238.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-224.59</v>
+        <v>-253.76</v>
       </c>
       <c r="K79" t="n">
-        <v>8.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>224.77</v>
+        <v>253.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>123.37</v>
+        <v>151.1</v>
       </c>
       <c r="K80" t="n">
-        <v>305.6</v>
+        <v>374.3</v>
       </c>
       <c r="L80" t="n">
-        <v>329.56</v>
+        <v>403.65</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>29.56</v>
+        <v>42.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-134.68</v>
+        <v>-194.52</v>
       </c>
       <c r="L81" t="n">
-        <v>137.88</v>
+        <v>199.15</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-89.81999999999999</v>
+        <v>-192.14</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="L82" t="n">
-        <v>89.81999999999999</v>
+        <v>192.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>518.47</v>
+        <v>698.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-67.90000000000001</v>
+        <v>-91.53</v>
       </c>
       <c r="L83" t="n">
-        <v>522.9</v>
+        <v>704.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>6.52</v>
+        <v>10.04</v>
       </c>
       <c r="K84" t="n">
-        <v>-397.92</v>
+        <v>-612.8099999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>397.97</v>
+        <v>612.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>689.36</v>
+        <v>753.17</v>
       </c>
       <c r="K85" t="n">
-        <v>341.64</v>
+        <v>373.26</v>
       </c>
       <c r="L85" t="n">
-        <v>769.38</v>
+        <v>840.59</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-192.08</v>
+        <v>-378.8</v>
       </c>
       <c r="K86" t="n">
-        <v>194.97</v>
+        <v>384.48</v>
       </c>
       <c r="L86" t="n">
-        <v>273.69</v>
+        <v>539.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>319.46</v>
+        <v>402.6</v>
       </c>
       <c r="K87" t="n">
-        <v>361.38</v>
+        <v>455.43</v>
       </c>
       <c r="L87" t="n">
-        <v>482.33</v>
+        <v>607.87</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-817.8</v>
+        <v>-905.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-231.14</v>
+        <v>-255.86</v>
       </c>
       <c r="L88" t="n">
-        <v>849.83</v>
+        <v>940.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-44.81</v>
+        <v>-34.84</v>
       </c>
       <c r="K14" t="n">
-        <v>168.21</v>
+        <v>130.79</v>
       </c>
       <c r="L14" t="n">
-        <v>174.08</v>
+        <v>135.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-133.21</v>
+        <v>-95.84999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-110.36</v>
+        <v>-79.41</v>
       </c>
       <c r="L15" t="n">
-        <v>172.99</v>
+        <v>124.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-152.79</v>
+        <v>-127.09</v>
       </c>
       <c r="K16" t="n">
-        <v>-231.43</v>
+        <v>-192.5</v>
       </c>
       <c r="L16" t="n">
-        <v>277.32</v>
+        <v>230.67</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>124.3</v>
+        <v>88.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.73</v>
+        <v>-12.58</v>
       </c>
       <c r="L17" t="n">
-        <v>125.56</v>
+        <v>89.09</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>138.07</v>
+        <v>97.75</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.84</v>
+        <v>-12.63</v>
       </c>
       <c r="L18" t="n">
-        <v>139.22</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-86.34999999999999</v>
+        <v>-69.78</v>
       </c>
       <c r="K19" t="n">
-        <v>22.14</v>
+        <v>17.89</v>
       </c>
       <c r="L19" t="n">
-        <v>89.15000000000001</v>
+        <v>72.04000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>239.5</v>
+        <v>167.54</v>
       </c>
       <c r="K20" t="n">
-        <v>-134.94</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>274.9</v>
+        <v>192.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-72.20999999999999</v>
+        <v>-48.29</v>
       </c>
       <c r="K21" t="n">
-        <v>191.37</v>
+        <v>127.96</v>
       </c>
       <c r="L21" t="n">
-        <v>204.54</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>28.48</v>
+        <v>17.06</v>
       </c>
       <c r="K22" t="n">
-        <v>-230.46</v>
+        <v>-138.08</v>
       </c>
       <c r="L22" t="n">
-        <v>232.21</v>
+        <v>139.13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>253.18</v>
+        <v>143.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.59</v>
+        <v>-1.47</v>
       </c>
       <c r="L23" t="n">
-        <v>253.19</v>
+        <v>143.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>13.26</v>
+        <v>7.16</v>
       </c>
       <c r="K24" t="n">
-        <v>-898.9</v>
+        <v>-485.51</v>
       </c>
       <c r="L24" t="n">
-        <v>899</v>
+        <v>485.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-138.52</v>
+        <v>-71.70999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-713.3</v>
+        <v>-369.25</v>
       </c>
       <c r="L25" t="n">
-        <v>726.62</v>
+        <v>376.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>672.24</v>
+        <v>327.97</v>
       </c>
       <c r="K26" t="n">
-        <v>-46.16</v>
+        <v>-22.52</v>
       </c>
       <c r="L26" t="n">
-        <v>673.8200000000001</v>
+        <v>328.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>493.41</v>
+        <v>249.89</v>
       </c>
       <c r="K27" t="n">
-        <v>416.1</v>
+        <v>210.74</v>
       </c>
       <c r="L27" t="n">
-        <v>645.4400000000001</v>
+        <v>326.89</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-799.0599999999999</v>
+        <v>-383.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-79.31</v>
+        <v>-38.02</v>
       </c>
       <c r="L28" t="n">
-        <v>802.99</v>
+        <v>384.94</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>155.68</v>
+        <v>110</v>
       </c>
       <c r="K29" t="n">
-        <v>-83.73999999999999</v>
+        <v>-59.17</v>
       </c>
       <c r="L29" t="n">
-        <v>176.77</v>
+        <v>124.9</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-207.5</v>
+        <v>-153.65</v>
       </c>
       <c r="K30" t="n">
-        <v>63.26</v>
+        <v>46.84</v>
       </c>
       <c r="L30" t="n">
-        <v>216.93</v>
+        <v>160.64</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>41.71</v>
+        <v>29.11</v>
       </c>
       <c r="K31" t="n">
-        <v>297.91</v>
+        <v>207.91</v>
       </c>
       <c r="L31" t="n">
-        <v>300.81</v>
+        <v>209.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>63.93</v>
+        <v>43.43</v>
       </c>
       <c r="K32" t="n">
-        <v>-98.3</v>
+        <v>-66.78</v>
       </c>
       <c r="L32" t="n">
-        <v>117.26</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-96.26000000000001</v>
+        <v>-78.56</v>
       </c>
       <c r="K33" t="n">
-        <v>-103.97</v>
+        <v>-84.86</v>
       </c>
       <c r="L33" t="n">
-        <v>141.69</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>195.11</v>
+        <v>138.56</v>
       </c>
       <c r="K34" t="n">
-        <v>39.27</v>
+        <v>27.89</v>
       </c>
       <c r="L34" t="n">
-        <v>199.02</v>
+        <v>141.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-264.32</v>
+        <v>-160.9</v>
       </c>
       <c r="K35" t="n">
-        <v>-57.98</v>
+        <v>-35.29</v>
       </c>
       <c r="L35" t="n">
-        <v>270.6</v>
+        <v>164.72</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>183.74</v>
+        <v>111.67</v>
       </c>
       <c r="K36" t="n">
-        <v>302.62</v>
+        <v>183.92</v>
       </c>
       <c r="L36" t="n">
-        <v>354.03</v>
+        <v>215.17</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-160.94</v>
+        <v>-117.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.04</v>
+        <v>-4.41</v>
       </c>
       <c r="L37" t="n">
-        <v>161.05</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>513.16</v>
+        <v>280.39</v>
       </c>
       <c r="K38" t="n">
-        <v>-16.38</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>513.42</v>
+        <v>280.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-280.23</v>
+        <v>-165.78</v>
       </c>
       <c r="K39" t="n">
-        <v>-273.53</v>
+        <v>-161.82</v>
       </c>
       <c r="L39" t="n">
-        <v>391.6</v>
+        <v>231.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-349.49</v>
+        <v>-198.6</v>
       </c>
       <c r="K40" t="n">
-        <v>32.71</v>
+        <v>18.59</v>
       </c>
       <c r="L40" t="n">
-        <v>351.02</v>
+        <v>199.47</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-222.08</v>
+        <v>-122.32</v>
       </c>
       <c r="K41" t="n">
-        <v>-274.77</v>
+        <v>-151.34</v>
       </c>
       <c r="L41" t="n">
-        <v>353.29</v>
+        <v>194.59</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-205.5</v>
+        <v>-118.89</v>
       </c>
       <c r="K42" t="n">
-        <v>638.64</v>
+        <v>369.48</v>
       </c>
       <c r="L42" t="n">
-        <v>670.89</v>
+        <v>388.14</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-47.53</v>
+        <v>-28.37</v>
       </c>
       <c r="K43" t="n">
-        <v>-294.7</v>
+        <v>-175.88</v>
       </c>
       <c r="L43" t="n">
-        <v>298.5</v>
+        <v>178.16</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>74.81</v>
+        <v>53.43</v>
       </c>
       <c r="K44" t="n">
-        <v>111.97</v>
+        <v>79.98</v>
       </c>
       <c r="L44" t="n">
-        <v>134.66</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>105.57</v>
+        <v>78.37</v>
       </c>
       <c r="K45" t="n">
-        <v>-146.8</v>
+        <v>-108.99</v>
       </c>
       <c r="L45" t="n">
-        <v>180.82</v>
+        <v>134.24</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>77.26000000000001</v>
+        <v>59.27</v>
       </c>
       <c r="K46" t="n">
-        <v>-142.76</v>
+        <v>-109.52</v>
       </c>
       <c r="L46" t="n">
-        <v>162.32</v>
+        <v>124.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>381.23</v>
+        <v>271.33</v>
       </c>
       <c r="K47" t="n">
-        <v>107.51</v>
+        <v>76.52</v>
       </c>
       <c r="L47" t="n">
-        <v>396.1</v>
+        <v>281.92</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-118.26</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>107.58</v>
+        <v>77.41</v>
       </c>
       <c r="L48" t="n">
-        <v>159.87</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>19.48</v>
+        <v>15.49</v>
       </c>
       <c r="K49" t="n">
-        <v>128.61</v>
+        <v>102.3</v>
       </c>
       <c r="L49" t="n">
-        <v>130.08</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-327.08</v>
+        <v>-228.23</v>
       </c>
       <c r="K50" t="n">
-        <v>325.05</v>
+        <v>226.81</v>
       </c>
       <c r="L50" t="n">
-        <v>461.13</v>
+        <v>321.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>28.11</v>
+        <v>16.47</v>
       </c>
       <c r="K51" t="n">
-        <v>630.35</v>
+        <v>369.4</v>
       </c>
       <c r="L51" t="n">
-        <v>630.98</v>
+        <v>369.77</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-543.5700000000001</v>
+        <v>-299.72</v>
       </c>
       <c r="K52" t="n">
-        <v>455.01</v>
+        <v>250.89</v>
       </c>
       <c r="L52" t="n">
-        <v>708.87</v>
+        <v>390.87</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-137.07</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>336.88</v>
+        <v>169.56</v>
       </c>
       <c r="L53" t="n">
-        <v>363.7</v>
+        <v>183.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-164.03</v>
+        <v>-88</v>
       </c>
       <c r="K54" t="n">
-        <v>300.76</v>
+        <v>161.36</v>
       </c>
       <c r="L54" t="n">
-        <v>342.58</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-252.68</v>
+        <v>-134.94</v>
       </c>
       <c r="K55" t="n">
-        <v>-374.81</v>
+        <v>-200.17</v>
       </c>
       <c r="L55" t="n">
-        <v>452.03</v>
+        <v>241.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>215.02</v>
+        <v>126.38</v>
       </c>
       <c r="K56" t="n">
-        <v>-330.86</v>
+        <v>-194.46</v>
       </c>
       <c r="L56" t="n">
-        <v>394.59</v>
+        <v>231.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-241.89</v>
+        <v>-121.62</v>
       </c>
       <c r="K57" t="n">
-        <v>311.99</v>
+        <v>156.86</v>
       </c>
       <c r="L57" t="n">
-        <v>394.78</v>
+        <v>198.48</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-895.5</v>
+        <v>-514.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-451.28</v>
+        <v>-259.05</v>
       </c>
       <c r="L58" t="n">
-        <v>1002.78</v>
+        <v>575.62</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.74</v>
+        <v>-10.14</v>
       </c>
       <c r="K59" t="n">
-        <v>-111.79</v>
+        <v>-82.45</v>
       </c>
       <c r="L59" t="n">
-        <v>112.63</v>
+        <v>83.06999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-213.64</v>
+        <v>-144.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-59.04</v>
+        <v>-40.04</v>
       </c>
       <c r="L60" t="n">
-        <v>221.65</v>
+        <v>150.31</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>12.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>268.17</v>
+        <v>182.15</v>
       </c>
       <c r="L61" t="n">
-        <v>268.44</v>
+        <v>182.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-108.46</v>
+        <v>-85.75</v>
       </c>
       <c r="K62" t="n">
-        <v>-200.57</v>
+        <v>-158.59</v>
       </c>
       <c r="L62" t="n">
-        <v>228.01</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>9.960000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-120.32</v>
+        <v>-95.08</v>
       </c>
       <c r="L63" t="n">
-        <v>120.73</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>246.14</v>
+        <v>169.33</v>
       </c>
       <c r="K64" t="n">
-        <v>171.03</v>
+        <v>117.67</v>
       </c>
       <c r="L64" t="n">
-        <v>299.73</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>34.55</v>
+        <v>21.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-211.78</v>
+        <v>-133.36</v>
       </c>
       <c r="L65" t="n">
-        <v>214.58</v>
+        <v>135.12</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>416.68</v>
+        <v>242.94</v>
       </c>
       <c r="K66" t="n">
-        <v>314.45</v>
+        <v>183.34</v>
       </c>
       <c r="L66" t="n">
-        <v>522.02</v>
+        <v>304.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-128</v>
+        <v>-81.26000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-512.14</v>
+        <v>-325.11</v>
       </c>
       <c r="L67" t="n">
-        <v>527.9</v>
+        <v>335.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-336.96</v>
+        <v>-207.53</v>
       </c>
       <c r="K68" t="n">
-        <v>511.64</v>
+        <v>315.11</v>
       </c>
       <c r="L68" t="n">
-        <v>612.63</v>
+        <v>377.32</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-569.8200000000001</v>
+        <v>-312.42</v>
       </c>
       <c r="K69" t="n">
-        <v>510.99</v>
+        <v>280.16</v>
       </c>
       <c r="L69" t="n">
-        <v>765.38</v>
+        <v>419.64</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-368.11</v>
+        <v>-232.51</v>
       </c>
       <c r="K70" t="n">
-        <v>4.69</v>
+        <v>2.96</v>
       </c>
       <c r="L70" t="n">
-        <v>368.14</v>
+        <v>232.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-38.38</v>
+        <v>-19.31</v>
       </c>
       <c r="K71" t="n">
-        <v>456.02</v>
+        <v>229.51</v>
       </c>
       <c r="L71" t="n">
-        <v>457.64</v>
+        <v>230.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>83.52</v>
+        <v>48.93</v>
       </c>
       <c r="K72" t="n">
-        <v>-501.21</v>
+        <v>-293.62</v>
       </c>
       <c r="L72" t="n">
-        <v>508.13</v>
+        <v>297.67</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-605.1799999999999</v>
+        <v>-284</v>
       </c>
       <c r="K73" t="n">
-        <v>-1465.98</v>
+        <v>-687.95</v>
       </c>
       <c r="L73" t="n">
-        <v>1585.98</v>
+        <v>744.26</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>197.76</v>
+        <v>140.85</v>
       </c>
       <c r="K74" t="n">
-        <v>42.53</v>
+        <v>30.29</v>
       </c>
       <c r="L74" t="n">
-        <v>202.28</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-79.86</v>
+        <v>-67.95</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.17</v>
+        <v>-29.07</v>
       </c>
       <c r="L75" t="n">
-        <v>86.86</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>153.93</v>
+        <v>133.69</v>
       </c>
       <c r="K76" t="n">
-        <v>-116.92</v>
+        <v>-101.55</v>
       </c>
       <c r="L76" t="n">
-        <v>193.3</v>
+        <v>167.89</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-255.24</v>
+        <v>-169.31</v>
       </c>
       <c r="K77" t="n">
-        <v>68.31999999999999</v>
+        <v>45.32</v>
       </c>
       <c r="L77" t="n">
-        <v>264.23</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>134.49</v>
+        <v>95.89</v>
       </c>
       <c r="K78" t="n">
-        <v>-197.45</v>
+        <v>-140.77</v>
       </c>
       <c r="L78" t="n">
-        <v>238.91</v>
+        <v>170.32</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-253.76</v>
+        <v>-174.22</v>
       </c>
       <c r="K79" t="n">
-        <v>9.960000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="L79" t="n">
-        <v>253.95</v>
+        <v>174.35</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>151.1</v>
+        <v>96.88</v>
       </c>
       <c r="K80" t="n">
-        <v>374.3</v>
+        <v>239.99</v>
       </c>
       <c r="L80" t="n">
-        <v>403.65</v>
+        <v>258.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>42.69</v>
+        <v>30.61</v>
       </c>
       <c r="K81" t="n">
-        <v>-194.52</v>
+        <v>-139.48</v>
       </c>
       <c r="L81" t="n">
-        <v>199.15</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-192.14</v>
+        <v>-125.4</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.33</v>
+        <v>-0.21</v>
       </c>
       <c r="L82" t="n">
-        <v>192.14</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>698.86</v>
+        <v>352.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-91.53</v>
+        <v>-46.12</v>
       </c>
       <c r="L83" t="n">
-        <v>704.83</v>
+        <v>355.14</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>10.04</v>
+        <v>5.02</v>
       </c>
       <c r="K84" t="n">
-        <v>-612.8099999999999</v>
+        <v>-306.45</v>
       </c>
       <c r="L84" t="n">
-        <v>612.89</v>
+        <v>306.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>753.17</v>
+        <v>445.57</v>
       </c>
       <c r="K85" t="n">
-        <v>373.26</v>
+        <v>220.82</v>
       </c>
       <c r="L85" t="n">
-        <v>840.59</v>
+        <v>497.29</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-378.8</v>
+        <v>-181.43</v>
       </c>
       <c r="K86" t="n">
-        <v>384.48</v>
+        <v>184.15</v>
       </c>
       <c r="L86" t="n">
-        <v>539.73</v>
+        <v>258.51</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>402.6</v>
+        <v>232.13</v>
       </c>
       <c r="K87" t="n">
-        <v>455.43</v>
+        <v>262.59</v>
       </c>
       <c r="L87" t="n">
-        <v>607.87</v>
+        <v>350.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-905.26</v>
+        <v>-421.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-255.86</v>
+        <v>-119.14</v>
       </c>
       <c r="L88" t="n">
-        <v>940.73</v>
+        <v>438.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-34.84</v>
+        <v>-35.07</v>
       </c>
       <c r="K14" t="n">
-        <v>130.79</v>
+        <v>131.65</v>
       </c>
       <c r="L14" t="n">
-        <v>135.35</v>
+        <v>136.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-95.84999999999999</v>
+        <v>-96.33</v>
       </c>
       <c r="K15" t="n">
-        <v>-79.41</v>
+        <v>-79.81</v>
       </c>
       <c r="L15" t="n">
-        <v>124.47</v>
+        <v>125.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-127.09</v>
+        <v>-126.77</v>
       </c>
       <c r="K16" t="n">
-        <v>-192.5</v>
+        <v>-192.01</v>
       </c>
       <c r="L16" t="n">
-        <v>230.67</v>
+        <v>230.08</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>88.2</v>
+        <v>90.8</v>
       </c>
       <c r="K17" t="n">
-        <v>-12.58</v>
+        <v>-12.95</v>
       </c>
       <c r="L17" t="n">
-        <v>89.09</v>
+        <v>91.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>97.75</v>
+        <v>101.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.63</v>
+        <v>-13.17</v>
       </c>
       <c r="L18" t="n">
-        <v>98.56</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-69.78</v>
+        <v>-71.33</v>
       </c>
       <c r="K19" t="n">
-        <v>17.89</v>
+        <v>18.29</v>
       </c>
       <c r="L19" t="n">
-        <v>72.04000000000001</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>167.54</v>
+        <v>176.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-94.40000000000001</v>
+        <v>-99.17</v>
       </c>
       <c r="L20" t="n">
-        <v>192.31</v>
+        <v>202.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-48.29</v>
+        <v>-51.07</v>
       </c>
       <c r="K21" t="n">
-        <v>127.96</v>
+        <v>135.35</v>
       </c>
       <c r="L21" t="n">
-        <v>136.77</v>
+        <v>144.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>17.06</v>
+        <v>18.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-138.08</v>
+        <v>-148.84</v>
       </c>
       <c r="L22" t="n">
-        <v>139.13</v>
+        <v>149.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>143.38</v>
+        <v>156.56</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.47</v>
+        <v>-1.6</v>
       </c>
       <c r="L23" t="n">
-        <v>143.39</v>
+        <v>156.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>7.16</v>
+        <v>7.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-485.51</v>
+        <v>-534.21</v>
       </c>
       <c r="L24" t="n">
-        <v>485.56</v>
+        <v>534.26</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-71.70999999999999</v>
+        <v>-78.63</v>
       </c>
       <c r="K25" t="n">
-        <v>-369.25</v>
+        <v>-404.91</v>
       </c>
       <c r="L25" t="n">
-        <v>376.15</v>
+        <v>412.47</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>327.97</v>
+        <v>369.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-22.52</v>
+        <v>-25.34</v>
       </c>
       <c r="L26" t="n">
-        <v>328.74</v>
+        <v>369.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>249.89</v>
+        <v>277.73</v>
       </c>
       <c r="K27" t="n">
-        <v>210.74</v>
+        <v>234.21</v>
       </c>
       <c r="L27" t="n">
-        <v>326.89</v>
+        <v>363.3</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-383.05</v>
+        <v>-430.92</v>
       </c>
       <c r="K28" t="n">
-        <v>-38.02</v>
+        <v>-42.77</v>
       </c>
       <c r="L28" t="n">
-        <v>384.94</v>
+        <v>433.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>110</v>
+        <v>110.19</v>
       </c>
       <c r="K29" t="n">
-        <v>-59.17</v>
+        <v>-59.28</v>
       </c>
       <c r="L29" t="n">
-        <v>124.9</v>
+        <v>125.13</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-153.65</v>
+        <v>-154.81</v>
       </c>
       <c r="K30" t="n">
-        <v>46.84</v>
+        <v>47.19</v>
       </c>
       <c r="L30" t="n">
-        <v>160.64</v>
+        <v>161.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>29.11</v>
+        <v>29.58</v>
       </c>
       <c r="K31" t="n">
-        <v>207.91</v>
+        <v>211.28</v>
       </c>
       <c r="L31" t="n">
-        <v>209.93</v>
+        <v>213.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>43.43</v>
+        <v>45.13</v>
       </c>
       <c r="K32" t="n">
-        <v>-66.78</v>
+        <v>-69.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>79.66</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.56</v>
+        <v>-80.64</v>
       </c>
       <c r="K33" t="n">
-        <v>-84.86</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>115.64</v>
+        <v>118.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>138.56</v>
+        <v>143.91</v>
       </c>
       <c r="K34" t="n">
-        <v>27.89</v>
+        <v>28.97</v>
       </c>
       <c r="L34" t="n">
-        <v>141.34</v>
+        <v>146.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-160.9</v>
+        <v>-172.04</v>
       </c>
       <c r="K35" t="n">
-        <v>-35.29</v>
+        <v>-37.73</v>
       </c>
       <c r="L35" t="n">
-        <v>164.72</v>
+        <v>176.13</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>111.67</v>
+        <v>119.52</v>
       </c>
       <c r="K36" t="n">
-        <v>183.92</v>
+        <v>196.85</v>
       </c>
       <c r="L36" t="n">
-        <v>215.17</v>
+        <v>230.3</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-117.31</v>
+        <v>-122.99</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.41</v>
+        <v>-4.62</v>
       </c>
       <c r="L37" t="n">
-        <v>117.39</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>280.39</v>
+        <v>310.31</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.91</v>
       </c>
       <c r="L38" t="n">
-        <v>280.54</v>
+        <v>310.47</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-165.78</v>
+        <v>-178.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-161.82</v>
+        <v>-174.43</v>
       </c>
       <c r="L39" t="n">
-        <v>231.66</v>
+        <v>249.72</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-198.6</v>
+        <v>-216.8</v>
       </c>
       <c r="K40" t="n">
-        <v>18.59</v>
+        <v>20.29</v>
       </c>
       <c r="L40" t="n">
-        <v>199.47</v>
+        <v>217.75</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-122.32</v>
+        <v>-134.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-151.34</v>
+        <v>-166.78</v>
       </c>
       <c r="L41" t="n">
-        <v>194.59</v>
+        <v>214.44</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-118.89</v>
+        <v>-131.31</v>
       </c>
       <c r="K42" t="n">
-        <v>369.48</v>
+        <v>408.07</v>
       </c>
       <c r="L42" t="n">
-        <v>388.14</v>
+        <v>428.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-28.37</v>
+        <v>-30.61</v>
       </c>
       <c r="K43" t="n">
-        <v>-175.88</v>
+        <v>-189.8</v>
       </c>
       <c r="L43" t="n">
-        <v>178.16</v>
+        <v>192.25</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>53.43</v>
+        <v>53.48</v>
       </c>
       <c r="K44" t="n">
-        <v>79.98</v>
+        <v>80.05</v>
       </c>
       <c r="L44" t="n">
-        <v>96.19</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>78.37</v>
+        <v>79.17</v>
       </c>
       <c r="K45" t="n">
-        <v>-108.99</v>
+        <v>-110.09</v>
       </c>
       <c r="L45" t="n">
-        <v>134.24</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>59.27</v>
+        <v>59.43</v>
       </c>
       <c r="K46" t="n">
-        <v>-109.52</v>
+        <v>-109.81</v>
       </c>
       <c r="L46" t="n">
-        <v>124.53</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>271.33</v>
+        <v>277.96</v>
       </c>
       <c r="K47" t="n">
-        <v>76.52</v>
+        <v>78.39</v>
       </c>
       <c r="L47" t="n">
-        <v>281.92</v>
+        <v>288.81</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-85.09999999999999</v>
+        <v>-87.11</v>
       </c>
       <c r="K48" t="n">
-        <v>77.41</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>115.04</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>15.49</v>
+        <v>15.68</v>
       </c>
       <c r="K49" t="n">
-        <v>102.3</v>
+        <v>103.5</v>
       </c>
       <c r="L49" t="n">
-        <v>103.46</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-228.23</v>
+        <v>-240.21</v>
       </c>
       <c r="K50" t="n">
-        <v>226.81</v>
+        <v>238.71</v>
       </c>
       <c r="L50" t="n">
-        <v>321.77</v>
+        <v>338.65</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>16.47</v>
+        <v>17.84</v>
       </c>
       <c r="K51" t="n">
-        <v>369.4</v>
+        <v>400.07</v>
       </c>
       <c r="L51" t="n">
-        <v>369.77</v>
+        <v>400.47</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-299.72</v>
+        <v>-322.55</v>
       </c>
       <c r="K52" t="n">
-        <v>250.89</v>
+        <v>270</v>
       </c>
       <c r="L52" t="n">
-        <v>390.87</v>
+        <v>420.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-68.98999999999999</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>169.56</v>
+        <v>189.15</v>
       </c>
       <c r="L53" t="n">
-        <v>183.05</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-88</v>
+        <v>-96.43000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>161.36</v>
+        <v>176.82</v>
       </c>
       <c r="L54" t="n">
-        <v>183.8</v>
+        <v>201.4</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-134.94</v>
+        <v>-146.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-200.17</v>
+        <v>-217.42</v>
       </c>
       <c r="L55" t="n">
-        <v>241.41</v>
+        <v>262.21</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>126.38</v>
+        <v>138.54</v>
       </c>
       <c r="K56" t="n">
-        <v>-194.46</v>
+        <v>-213.18</v>
       </c>
       <c r="L56" t="n">
-        <v>231.92</v>
+        <v>254.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-121.62</v>
+        <v>-136.21</v>
       </c>
       <c r="K57" t="n">
-        <v>156.86</v>
+        <v>175.68</v>
       </c>
       <c r="L57" t="n">
-        <v>198.48</v>
+        <v>222.3</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-514.04</v>
+        <v>-565.98</v>
       </c>
       <c r="K58" t="n">
-        <v>-259.05</v>
+        <v>-285.22</v>
       </c>
       <c r="L58" t="n">
-        <v>575.62</v>
+        <v>633.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.14</v>
+        <v>-10.29</v>
       </c>
       <c r="K59" t="n">
-        <v>-82.45</v>
+        <v>-83.70999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>83.06999999999999</v>
+        <v>84.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-144.88</v>
+        <v>-149.15</v>
       </c>
       <c r="K60" t="n">
-        <v>-40.04</v>
+        <v>-41.22</v>
       </c>
       <c r="L60" t="n">
-        <v>150.31</v>
+        <v>154.74</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>8.220000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="K61" t="n">
-        <v>182.15</v>
+        <v>186.91</v>
       </c>
       <c r="L61" t="n">
-        <v>182.33</v>
+        <v>187.1</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-85.75</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-158.59</v>
+        <v>-161.33</v>
       </c>
       <c r="L62" t="n">
-        <v>180.29</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>7.87</v>
+        <v>7.91</v>
       </c>
       <c r="K63" t="n">
-        <v>-95.08</v>
+        <v>-95.56999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>95.41</v>
+        <v>95.89</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>169.33</v>
+        <v>174.16</v>
       </c>
       <c r="K64" t="n">
-        <v>117.67</v>
+        <v>121.02</v>
       </c>
       <c r="L64" t="n">
-        <v>206.2</v>
+        <v>212.08</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>21.76</v>
+        <v>23.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-133.36</v>
+        <v>-143.27</v>
       </c>
       <c r="L65" t="n">
-        <v>135.12</v>
+        <v>145.16</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>242.94</v>
+        <v>258.62</v>
       </c>
       <c r="K66" t="n">
-        <v>183.34</v>
+        <v>195.17</v>
       </c>
       <c r="L66" t="n">
-        <v>304.36</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-81.26000000000001</v>
+        <v>-85.88</v>
       </c>
       <c r="K67" t="n">
-        <v>-325.11</v>
+        <v>-343.62</v>
       </c>
       <c r="L67" t="n">
-        <v>335.11</v>
+        <v>354.19</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-207.53</v>
+        <v>-223.66</v>
       </c>
       <c r="K68" t="n">
-        <v>315.11</v>
+        <v>339.6</v>
       </c>
       <c r="L68" t="n">
-        <v>377.32</v>
+        <v>406.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-312.42</v>
+        <v>-342.63</v>
       </c>
       <c r="K69" t="n">
-        <v>280.16</v>
+        <v>307.25</v>
       </c>
       <c r="L69" t="n">
-        <v>419.64</v>
+        <v>460.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-232.51</v>
+        <v>-249.26</v>
       </c>
       <c r="K70" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="L70" t="n">
-        <v>232.53</v>
+        <v>249.28</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.31</v>
+        <v>-21.69</v>
       </c>
       <c r="K71" t="n">
-        <v>229.51</v>
+        <v>257.71</v>
       </c>
       <c r="L71" t="n">
-        <v>230.33</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>48.93</v>
+        <v>53.42</v>
       </c>
       <c r="K72" t="n">
-        <v>-293.62</v>
+        <v>-320.56</v>
       </c>
       <c r="L72" t="n">
-        <v>297.67</v>
+        <v>324.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-284</v>
+        <v>-323.45</v>
       </c>
       <c r="K73" t="n">
-        <v>-687.95</v>
+        <v>-783.53</v>
       </c>
       <c r="L73" t="n">
-        <v>744.26</v>
+        <v>847.67</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>140.85</v>
+        <v>144.79</v>
       </c>
       <c r="K74" t="n">
-        <v>30.29</v>
+        <v>31.14</v>
       </c>
       <c r="L74" t="n">
-        <v>144.07</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.95</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-29.07</v>
+        <v>-28.89</v>
       </c>
       <c r="L75" t="n">
-        <v>73.91</v>
+        <v>73.43000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>133.69</v>
+        <v>130.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-101.55</v>
+        <v>-99.31999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>167.89</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-169.31</v>
+        <v>-174.32</v>
       </c>
       <c r="K77" t="n">
-        <v>45.32</v>
+        <v>46.66</v>
       </c>
       <c r="L77" t="n">
-        <v>175.28</v>
+        <v>180.46</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>95.89</v>
+        <v>97.84</v>
       </c>
       <c r="K78" t="n">
-        <v>-140.77</v>
+        <v>-143.65</v>
       </c>
       <c r="L78" t="n">
-        <v>170.32</v>
+        <v>173.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-174.22</v>
+        <v>-181.2</v>
       </c>
       <c r="K79" t="n">
-        <v>6.84</v>
+        <v>7.11</v>
       </c>
       <c r="L79" t="n">
-        <v>174.35</v>
+        <v>181.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>96.88</v>
+        <v>103.26</v>
       </c>
       <c r="K80" t="n">
-        <v>239.99</v>
+        <v>255.78</v>
       </c>
       <c r="L80" t="n">
-        <v>258.81</v>
+        <v>275.83</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>30.61</v>
+        <v>32.11</v>
       </c>
       <c r="K81" t="n">
-        <v>-139.48</v>
+        <v>-146.32</v>
       </c>
       <c r="L81" t="n">
-        <v>142.8</v>
+        <v>149.81</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.4</v>
+        <v>-130.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="L82" t="n">
-        <v>125.4</v>
+        <v>130.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>352.13</v>
+        <v>391.12</v>
       </c>
       <c r="K83" t="n">
-        <v>-46.12</v>
+        <v>-51.22</v>
       </c>
       <c r="L83" t="n">
-        <v>355.14</v>
+        <v>394.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>5.02</v>
+        <v>5.57</v>
       </c>
       <c r="K84" t="n">
-        <v>-306.45</v>
+        <v>-340.08</v>
       </c>
       <c r="L84" t="n">
-        <v>306.49</v>
+        <v>340.13</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>445.57</v>
+        <v>484.23</v>
       </c>
       <c r="K85" t="n">
-        <v>220.82</v>
+        <v>239.98</v>
       </c>
       <c r="L85" t="n">
-        <v>497.29</v>
+        <v>540.4299999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-181.43</v>
+        <v>-204.82</v>
       </c>
       <c r="K86" t="n">
-        <v>184.15</v>
+        <v>207.89</v>
       </c>
       <c r="L86" t="n">
-        <v>258.51</v>
+        <v>291.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>232.13</v>
+        <v>253.68</v>
       </c>
       <c r="K87" t="n">
-        <v>262.59</v>
+        <v>286.97</v>
       </c>
       <c r="L87" t="n">
-        <v>350.49</v>
+        <v>383.02</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-421.52</v>
+        <v>-481.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-119.14</v>
+        <v>-136.04</v>
       </c>
       <c r="L88" t="n">
-        <v>438.03</v>
+        <v>500.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-35.07</v>
+        <v>-20.22</v>
       </c>
       <c r="K14" t="n">
-        <v>131.65</v>
+        <v>75.91</v>
       </c>
       <c r="L14" t="n">
-        <v>136.25</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-96.33</v>
+        <v>-45.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-79.81</v>
+        <v>-37.36</v>
       </c>
       <c r="L15" t="n">
-        <v>125.09</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-126.77</v>
+        <v>-60.4</v>
       </c>
       <c r="K16" t="n">
-        <v>-192.01</v>
+        <v>-91.48</v>
       </c>
       <c r="L16" t="n">
-        <v>230.08</v>
+        <v>109.62</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>90.8</v>
+        <v>43.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-12.95</v>
+        <v>-6.22</v>
       </c>
       <c r="L17" t="n">
-        <v>91.72</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>101.91</v>
+        <v>53.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.17</v>
+        <v>-6.92</v>
       </c>
       <c r="L18" t="n">
-        <v>102.76</v>
+        <v>53.98</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-71.33</v>
+        <v>-43.94</v>
       </c>
       <c r="K19" t="n">
-        <v>18.29</v>
+        <v>11.27</v>
       </c>
       <c r="L19" t="n">
-        <v>73.64</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>176.01</v>
+        <v>89.03</v>
       </c>
       <c r="K20" t="n">
-        <v>-99.17</v>
+        <v>-50.16</v>
       </c>
       <c r="L20" t="n">
-        <v>202.03</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-51.07</v>
+        <v>-25.64</v>
       </c>
       <c r="K21" t="n">
-        <v>135.35</v>
+        <v>67.94</v>
       </c>
       <c r="L21" t="n">
-        <v>144.66</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>18.39</v>
+        <v>9.15</v>
       </c>
       <c r="K22" t="n">
-        <v>-148.84</v>
+        <v>-74.02</v>
       </c>
       <c r="L22" t="n">
-        <v>149.98</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>156.56</v>
+        <v>90.95</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6</v>
+        <v>-0.93</v>
       </c>
       <c r="L23" t="n">
-        <v>156.57</v>
+        <v>90.95</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>7.88</v>
+        <v>4.34</v>
       </c>
       <c r="K24" t="n">
-        <v>-534.21</v>
+        <v>-293.96</v>
       </c>
       <c r="L24" t="n">
-        <v>534.26</v>
+        <v>293.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-78.63</v>
+        <v>-41.21</v>
       </c>
       <c r="K25" t="n">
-        <v>-404.91</v>
+        <v>-212.19</v>
       </c>
       <c r="L25" t="n">
-        <v>412.47</v>
+        <v>216.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>369.08</v>
+        <v>202.72</v>
       </c>
       <c r="K26" t="n">
-        <v>-25.34</v>
+        <v>-13.92</v>
       </c>
       <c r="L26" t="n">
-        <v>369.95</v>
+        <v>203.19</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>277.73</v>
+        <v>153.71</v>
       </c>
       <c r="K27" t="n">
-        <v>234.21</v>
+        <v>129.63</v>
       </c>
       <c r="L27" t="n">
-        <v>363.3</v>
+        <v>201.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-430.92</v>
+        <v>-230.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-42.77</v>
+        <v>-22.92</v>
       </c>
       <c r="L28" t="n">
-        <v>433.04</v>
+        <v>232.03</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>110.19</v>
+        <v>54.09</v>
       </c>
       <c r="K29" t="n">
-        <v>-59.28</v>
+        <v>-29.1</v>
       </c>
       <c r="L29" t="n">
-        <v>125.13</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-154.81</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>47.19</v>
+        <v>21.81</v>
       </c>
       <c r="L30" t="n">
-        <v>161.84</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>29.58</v>
+        <v>13.82</v>
       </c>
       <c r="K31" t="n">
-        <v>211.28</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>213.34</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>45.13</v>
+        <v>6.04</v>
       </c>
       <c r="K32" t="n">
-        <v>-69.40000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>82.78</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-80.64</v>
+        <v>-42.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-87.09999999999999</v>
+        <v>-45.96</v>
       </c>
       <c r="L33" t="n">
-        <v>118.69</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>143.91</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>28.97</v>
+        <v>15.36</v>
       </c>
       <c r="L34" t="n">
-        <v>146.8</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-172.04</v>
+        <v>-83.87</v>
       </c>
       <c r="K35" t="n">
-        <v>-37.73</v>
+        <v>-18.4</v>
       </c>
       <c r="L35" t="n">
-        <v>176.13</v>
+        <v>85.86</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>119.52</v>
+        <v>60.46</v>
       </c>
       <c r="K36" t="n">
-        <v>196.85</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>230.3</v>
+        <v>116.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-122.99</v>
+        <v>-62.17</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.62</v>
+        <v>-2.33</v>
       </c>
       <c r="L37" t="n">
-        <v>123.08</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>310.31</v>
+        <v>157.5</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.91</v>
+        <v>-5.03</v>
       </c>
       <c r="L38" t="n">
-        <v>310.47</v>
+        <v>157.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-178.7</v>
+        <v>-94.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-174.43</v>
+        <v>-91.98</v>
       </c>
       <c r="L39" t="n">
-        <v>249.72</v>
+        <v>131.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-216.8</v>
+        <v>-112.46</v>
       </c>
       <c r="K40" t="n">
-        <v>20.29</v>
+        <v>10.52</v>
       </c>
       <c r="L40" t="n">
-        <v>217.75</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.79</v>
+        <v>-76.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-166.78</v>
+        <v>-94.06999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>214.44</v>
+        <v>120.95</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-131.31</v>
+        <v>-70.94</v>
       </c>
       <c r="K42" t="n">
-        <v>408.07</v>
+        <v>220.46</v>
       </c>
       <c r="L42" t="n">
-        <v>428.67</v>
+        <v>231.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-30.61</v>
+        <v>-17.27</v>
       </c>
       <c r="K43" t="n">
-        <v>-189.8</v>
+        <v>-107.05</v>
       </c>
       <c r="L43" t="n">
-        <v>192.25</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>53.48</v>
+        <v>27.37</v>
       </c>
       <c r="K44" t="n">
-        <v>80.05</v>
+        <v>40.96</v>
       </c>
       <c r="L44" t="n">
-        <v>96.27</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>79.17</v>
+        <v>36.98</v>
       </c>
       <c r="K45" t="n">
-        <v>-110.09</v>
+        <v>-51.42</v>
       </c>
       <c r="L45" t="n">
-        <v>135.6</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>59.43</v>
+        <v>27.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-109.81</v>
+        <v>-51.07</v>
       </c>
       <c r="L46" t="n">
-        <v>124.86</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>277.96</v>
+        <v>116.77</v>
       </c>
       <c r="K47" t="n">
-        <v>78.39</v>
+        <v>32.93</v>
       </c>
       <c r="L47" t="n">
-        <v>288.81</v>
+        <v>121.33</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-87.11</v>
+        <v>-39.12</v>
       </c>
       <c r="K48" t="n">
-        <v>79.23999999999999</v>
+        <v>35.59</v>
       </c>
       <c r="L48" t="n">
-        <v>117.76</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>15.68</v>
+        <v>7.66</v>
       </c>
       <c r="K49" t="n">
-        <v>103.5</v>
+        <v>50.57</v>
       </c>
       <c r="L49" t="n">
-        <v>104.68</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-240.21</v>
+        <v>-121.14</v>
       </c>
       <c r="K50" t="n">
-        <v>238.71</v>
+        <v>120.38</v>
       </c>
       <c r="L50" t="n">
-        <v>338.65</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>17.84</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>400.07</v>
+        <v>200.83</v>
       </c>
       <c r="L51" t="n">
-        <v>400.47</v>
+        <v>201.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-322.55</v>
+        <v>-154.26</v>
       </c>
       <c r="K52" t="n">
-        <v>270</v>
+        <v>129.13</v>
       </c>
       <c r="L52" t="n">
-        <v>420.64</v>
+        <v>201.17</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-76.95999999999999</v>
+        <v>-35.72</v>
       </c>
       <c r="K53" t="n">
-        <v>189.15</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>204.2</v>
+        <v>94.78</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-96.43000000000001</v>
+        <v>-51.71</v>
       </c>
       <c r="K54" t="n">
-        <v>176.82</v>
+        <v>94.81</v>
       </c>
       <c r="L54" t="n">
-        <v>201.4</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-146.57</v>
+        <v>-67.23</v>
       </c>
       <c r="K55" t="n">
-        <v>-217.42</v>
+        <v>-99.72</v>
       </c>
       <c r="L55" t="n">
-        <v>262.21</v>
+        <v>120.27</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>138.54</v>
+        <v>76.52</v>
       </c>
       <c r="K56" t="n">
-        <v>-213.18</v>
+        <v>-117.74</v>
       </c>
       <c r="L56" t="n">
-        <v>254.24</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-136.21</v>
+        <v>-74.63</v>
       </c>
       <c r="K57" t="n">
-        <v>175.68</v>
+        <v>96.25</v>
       </c>
       <c r="L57" t="n">
-        <v>222.3</v>
+        <v>121.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-565.98</v>
+        <v>-302.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-285.22</v>
+        <v>-152.38</v>
       </c>
       <c r="L58" t="n">
-        <v>633.78</v>
+        <v>338.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.29</v>
+        <v>-4.68</v>
       </c>
       <c r="K59" t="n">
-        <v>-83.70999999999999</v>
+        <v>-38.04</v>
       </c>
       <c r="L59" t="n">
-        <v>84.34</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-149.15</v>
+        <v>-61.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-41.22</v>
+        <v>-16.98</v>
       </c>
       <c r="L60" t="n">
-        <v>154.74</v>
+        <v>63.74</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>8.44</v>
+        <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>186.91</v>
+        <v>77.53</v>
       </c>
       <c r="L61" t="n">
-        <v>187.1</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-87.23999999999999</v>
+        <v>-41.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-161.33</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>183.4</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>7.91</v>
+        <v>3.78</v>
       </c>
       <c r="K63" t="n">
-        <v>-95.56999999999999</v>
+        <v>-45.74</v>
       </c>
       <c r="L63" t="n">
-        <v>95.89</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>174.16</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>121.02</v>
+        <v>50.16</v>
       </c>
       <c r="L64" t="n">
-        <v>212.08</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>23.37</v>
+        <v>11.87</v>
       </c>
       <c r="K65" t="n">
-        <v>-143.27</v>
+        <v>-72.78</v>
       </c>
       <c r="L65" t="n">
-        <v>145.16</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>258.62</v>
+        <v>124.33</v>
       </c>
       <c r="K66" t="n">
-        <v>195.17</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>324</v>
+        <v>155.76</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.88</v>
+        <v>-42.29</v>
       </c>
       <c r="K67" t="n">
-        <v>-343.62</v>
+        <v>-169.21</v>
       </c>
       <c r="L67" t="n">
-        <v>354.19</v>
+        <v>174.42</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-223.66</v>
+        <v>-118.67</v>
       </c>
       <c r="K68" t="n">
-        <v>339.6</v>
+        <v>180.19</v>
       </c>
       <c r="L68" t="n">
-        <v>406.63</v>
+        <v>215.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-342.63</v>
+        <v>-149.73</v>
       </c>
       <c r="K69" t="n">
-        <v>307.25</v>
+        <v>134.27</v>
       </c>
       <c r="L69" t="n">
-        <v>460.22</v>
+        <v>201.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-249.26</v>
+        <v>-123.63</v>
       </c>
       <c r="K70" t="n">
-        <v>3.17</v>
+        <v>1.57</v>
       </c>
       <c r="L70" t="n">
-        <v>249.28</v>
+        <v>123.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.69</v>
+        <v>-11.49</v>
       </c>
       <c r="K71" t="n">
-        <v>257.71</v>
+        <v>136.59</v>
       </c>
       <c r="L71" t="n">
-        <v>258.62</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>53.42</v>
+        <v>29.37</v>
       </c>
       <c r="K72" t="n">
-        <v>-320.56</v>
+        <v>-176.24</v>
       </c>
       <c r="L72" t="n">
-        <v>324.98</v>
+        <v>178.68</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-323.45</v>
+        <v>-175.46</v>
       </c>
       <c r="K73" t="n">
-        <v>-783.53</v>
+        <v>-425.03</v>
       </c>
       <c r="L73" t="n">
-        <v>847.67</v>
+        <v>459.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>144.79</v>
+        <v>57.7</v>
       </c>
       <c r="K74" t="n">
-        <v>31.14</v>
+        <v>12.41</v>
       </c>
       <c r="L74" t="n">
-        <v>148.1</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.51000000000001</v>
+        <v>-19.78</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.89</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>73.43000000000001</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>130.75</v>
+        <v>62.72</v>
       </c>
       <c r="K76" t="n">
-        <v>-99.31999999999999</v>
+        <v>-47.64</v>
       </c>
       <c r="L76" t="n">
-        <v>164.2</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-174.32</v>
+        <v>-72.75</v>
       </c>
       <c r="K77" t="n">
-        <v>46.66</v>
+        <v>19.47</v>
       </c>
       <c r="L77" t="n">
-        <v>180.46</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>97.84</v>
+        <v>42.48</v>
       </c>
       <c r="K78" t="n">
-        <v>-143.65</v>
+        <v>-62.36</v>
       </c>
       <c r="L78" t="n">
-        <v>173.8</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-181.2</v>
+        <v>-86.72</v>
       </c>
       <c r="K79" t="n">
-        <v>7.11</v>
+        <v>3.4</v>
       </c>
       <c r="L79" t="n">
-        <v>181.34</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>103.26</v>
+        <v>49.29</v>
       </c>
       <c r="K80" t="n">
-        <v>255.78</v>
+        <v>122.09</v>
       </c>
       <c r="L80" t="n">
-        <v>275.83</v>
+        <v>131.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>32.11</v>
+        <v>15.92</v>
       </c>
       <c r="K81" t="n">
-        <v>-146.32</v>
+        <v>-72.53</v>
       </c>
       <c r="L81" t="n">
-        <v>149.81</v>
+        <v>74.26000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-130.12</v>
+        <v>-63.41</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="L82" t="n">
-        <v>130.12</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>391.12</v>
+        <v>182.46</v>
       </c>
       <c r="K83" t="n">
-        <v>-51.22</v>
+        <v>-23.9</v>
       </c>
       <c r="L83" t="n">
-        <v>394.46</v>
+        <v>184.02</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>5.57</v>
+        <v>2.47</v>
       </c>
       <c r="K84" t="n">
-        <v>-340.08</v>
+        <v>-150.74</v>
       </c>
       <c r="L84" t="n">
-        <v>340.13</v>
+        <v>150.76</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>484.23</v>
+        <v>211.06</v>
       </c>
       <c r="K85" t="n">
-        <v>239.98</v>
+        <v>104.6</v>
       </c>
       <c r="L85" t="n">
-        <v>540.4299999999999</v>
+        <v>235.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-204.82</v>
+        <v>-109.61</v>
       </c>
       <c r="K86" t="n">
-        <v>207.89</v>
+        <v>111.25</v>
       </c>
       <c r="L86" t="n">
-        <v>291.84</v>
+        <v>156.18</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>253.68</v>
+        <v>136.39</v>
       </c>
       <c r="K87" t="n">
-        <v>286.97</v>
+        <v>154.29</v>
       </c>
       <c r="L87" t="n">
-        <v>383.02</v>
+        <v>205.93</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-481.33</v>
+        <v>-258.24</v>
       </c>
       <c r="K88" t="n">
-        <v>-136.04</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>500.18</v>
+        <v>268.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-20.22</v>
+        <v>-19.69</v>
       </c>
       <c r="K14" t="n">
-        <v>75.91</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>78.56</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.09</v>
+        <v>-45.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-37.36</v>
+        <v>-37.46</v>
       </c>
       <c r="L15" t="n">
-        <v>58.56</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.4</v>
+        <v>-56.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-91.48</v>
+        <v>-85.37</v>
       </c>
       <c r="L16" t="n">
-        <v>109.62</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>43.61</v>
+        <v>43.59</v>
       </c>
       <c r="K17" t="n">
         <v>-6.22</v>
       </c>
       <c r="L17" t="n">
-        <v>44.06</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>53.54</v>
+        <v>56.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.92</v>
+        <v>-7.27</v>
       </c>
       <c r="L18" t="n">
-        <v>53.98</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.94</v>
+        <v>-46.67</v>
       </c>
       <c r="K19" t="n">
-        <v>11.27</v>
+        <v>11.97</v>
       </c>
       <c r="L19" t="n">
-        <v>45.36</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>89.03</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.16</v>
+        <v>-50.11</v>
       </c>
       <c r="L20" t="n">
-        <v>102.19</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.64</v>
+        <v>-27.08</v>
       </c>
       <c r="K21" t="n">
-        <v>67.94</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>72.62</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>9.15</v>
+        <v>9.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-74.02</v>
+        <v>-78.94</v>
       </c>
       <c r="L22" t="n">
-        <v>74.58</v>
+        <v>79.54000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>90.95</v>
+        <v>97.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.93</v>
+        <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>90.95</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>4.34</v>
+        <v>4.09</v>
       </c>
       <c r="K24" t="n">
-        <v>-293.96</v>
+        <v>-277.3</v>
       </c>
       <c r="L24" t="n">
-        <v>293.99</v>
+        <v>277.33</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-41.21</v>
+        <v>-39.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-212.19</v>
+        <v>-205.95</v>
       </c>
       <c r="L25" t="n">
-        <v>216.16</v>
+        <v>209.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>202.72</v>
+        <v>211.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-13.92</v>
+        <v>-14.52</v>
       </c>
       <c r="L26" t="n">
-        <v>203.19</v>
+        <v>211.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>153.71</v>
+        <v>158.33</v>
       </c>
       <c r="K27" t="n">
-        <v>129.63</v>
+        <v>133.52</v>
       </c>
       <c r="L27" t="n">
-        <v>201.08</v>
+        <v>207.12</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-230.9</v>
+        <v>-246.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-22.92</v>
+        <v>-24.46</v>
       </c>
       <c r="L28" t="n">
-        <v>232.03</v>
+        <v>247.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>54.09</v>
+        <v>53.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.1</v>
+        <v>-28.99</v>
       </c>
       <c r="L29" t="n">
-        <v>61.42</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-71.54000000000001</v>
+        <v>-68.95999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>21.81</v>
+        <v>21.02</v>
       </c>
       <c r="L30" t="n">
-        <v>74.79000000000001</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>13.82</v>
+        <v>13.01</v>
       </c>
       <c r="K31" t="n">
-        <v>98.68000000000001</v>
+        <v>92.95</v>
       </c>
       <c r="L31" t="n">
-        <v>99.65000000000001</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>6.04</v>
+        <v>5.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="L32" t="n">
-        <v>11.09</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.55</v>
+        <v>-42.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-45.96</v>
+        <v>-46.41</v>
       </c>
       <c r="L33" t="n">
-        <v>62.64</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>76.29000000000001</v>
+        <v>75.66</v>
       </c>
       <c r="K34" t="n">
-        <v>15.36</v>
+        <v>15.23</v>
       </c>
       <c r="L34" t="n">
-        <v>77.81999999999999</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-83.87</v>
+        <v>-86.88</v>
       </c>
       <c r="K35" t="n">
-        <v>-18.4</v>
+        <v>-19.06</v>
       </c>
       <c r="L35" t="n">
-        <v>85.86</v>
+        <v>88.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>60.46</v>
+        <v>59.68</v>
       </c>
       <c r="K36" t="n">
-        <v>99.56999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="L36" t="n">
-        <v>116.49</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-62.17</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.33</v>
+        <v>-2.49</v>
       </c>
       <c r="L37" t="n">
-        <v>62.22</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>157.5</v>
+        <v>157.28</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.03</v>
+        <v>-5.02</v>
       </c>
       <c r="L38" t="n">
-        <v>157.58</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-94.23</v>
+        <v>-95.26000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-91.98</v>
+        <v>-92.98999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>131.68</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.46</v>
+        <v>-116.78</v>
       </c>
       <c r="K40" t="n">
-        <v>10.52</v>
+        <v>10.93</v>
       </c>
       <c r="L40" t="n">
-        <v>112.96</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-76.03</v>
+        <v>-81.31999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-94.06999999999999</v>
+        <v>-100.61</v>
       </c>
       <c r="L41" t="n">
-        <v>120.95</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-70.94</v>
+        <v>-73.23</v>
       </c>
       <c r="K42" t="n">
-        <v>220.46</v>
+        <v>227.58</v>
       </c>
       <c r="L42" t="n">
-        <v>231.59</v>
+        <v>239.07</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-17.27</v>
+        <v>-18.66</v>
       </c>
       <c r="K43" t="n">
-        <v>-107.05</v>
+        <v>-115.69</v>
       </c>
       <c r="L43" t="n">
-        <v>108.44</v>
+        <v>117.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>27.37</v>
+        <v>28.28</v>
       </c>
       <c r="K44" t="n">
-        <v>40.96</v>
+        <v>42.33</v>
       </c>
       <c r="L44" t="n">
-        <v>49.26</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>36.98</v>
+        <v>36.44</v>
       </c>
       <c r="K45" t="n">
-        <v>-51.42</v>
+        <v>-50.67</v>
       </c>
       <c r="L45" t="n">
-        <v>63.34</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>27.64</v>
+        <v>27.45</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.07</v>
+        <v>-50.73</v>
       </c>
       <c r="L46" t="n">
-        <v>58.07</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>116.77</v>
+        <v>107.62</v>
       </c>
       <c r="K47" t="n">
-        <v>32.93</v>
+        <v>30.35</v>
       </c>
       <c r="L47" t="n">
-        <v>121.33</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-39.12</v>
+        <v>-40.29</v>
       </c>
       <c r="K48" t="n">
-        <v>35.59</v>
+        <v>36.65</v>
       </c>
       <c r="L48" t="n">
-        <v>52.88</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>7.66</v>
+        <v>7.92</v>
       </c>
       <c r="K49" t="n">
-        <v>50.57</v>
+        <v>52.28</v>
       </c>
       <c r="L49" t="n">
-        <v>51.15</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-121.14</v>
+        <v>-114.61</v>
       </c>
       <c r="K50" t="n">
-        <v>120.38</v>
+        <v>113.89</v>
       </c>
       <c r="L50" t="n">
-        <v>170.78</v>
+        <v>161.57</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>8.960000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="K51" t="n">
-        <v>200.83</v>
+        <v>189.17</v>
       </c>
       <c r="L51" t="n">
-        <v>201.03</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-154.26</v>
+        <v>-145.78</v>
       </c>
       <c r="K52" t="n">
-        <v>129.13</v>
+        <v>122.03</v>
       </c>
       <c r="L52" t="n">
-        <v>201.17</v>
+        <v>190.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-35.72</v>
+        <v>-39.12</v>
       </c>
       <c r="K53" t="n">
-        <v>87.79000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>94.78</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.71</v>
+        <v>-54.26</v>
       </c>
       <c r="K54" t="n">
-        <v>94.81</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>107.99</v>
+        <v>113.33</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-67.23</v>
+        <v>-70.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-99.72</v>
+        <v>-103.99</v>
       </c>
       <c r="L55" t="n">
-        <v>120.27</v>
+        <v>125.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>76.52</v>
+        <v>81.86</v>
       </c>
       <c r="K56" t="n">
-        <v>-117.74</v>
+        <v>-125.96</v>
       </c>
       <c r="L56" t="n">
-        <v>140.42</v>
+        <v>150.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-74.63</v>
+        <v>-84.05</v>
       </c>
       <c r="K57" t="n">
-        <v>96.25</v>
+        <v>108.41</v>
       </c>
       <c r="L57" t="n">
-        <v>121.79</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-302.38</v>
+        <v>-310.21</v>
       </c>
       <c r="K58" t="n">
-        <v>-152.38</v>
+        <v>-156.33</v>
       </c>
       <c r="L58" t="n">
-        <v>338.61</v>
+        <v>347.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.68</v>
+        <v>-5.01</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.04</v>
+        <v>-40.77</v>
       </c>
       <c r="L59" t="n">
-        <v>38.32</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.44</v>
+        <v>-60.26</v>
       </c>
       <c r="K60" t="n">
-        <v>-16.98</v>
+        <v>-16.65</v>
       </c>
       <c r="L60" t="n">
-        <v>63.74</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K61" t="n">
-        <v>77.53</v>
+        <v>74.17</v>
       </c>
       <c r="L61" t="n">
-        <v>77.61</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.83</v>
+        <v>-40.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-77.34999999999999</v>
+        <v>-74.59</v>
       </c>
       <c r="L62" t="n">
-        <v>87.93000000000001</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>-45.74</v>
+        <v>-48.31</v>
       </c>
       <c r="L63" t="n">
-        <v>45.89</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>72.18000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="K64" t="n">
-        <v>50.16</v>
+        <v>47.96</v>
       </c>
       <c r="L64" t="n">
-        <v>87.90000000000001</v>
+        <v>84.05</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>11.87</v>
+        <v>12.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-72.78</v>
+        <v>-76.84</v>
       </c>
       <c r="L65" t="n">
-        <v>73.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>124.33</v>
+        <v>120.18</v>
       </c>
       <c r="K66" t="n">
-        <v>93.81999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L66" t="n">
-        <v>155.76</v>
+        <v>150.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-42.29</v>
+        <v>-40.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-169.21</v>
+        <v>-160.81</v>
       </c>
       <c r="L67" t="n">
-        <v>174.42</v>
+        <v>165.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-118.67</v>
+        <v>-114.06</v>
       </c>
       <c r="K68" t="n">
-        <v>180.19</v>
+        <v>173.19</v>
       </c>
       <c r="L68" t="n">
-        <v>215.75</v>
+        <v>207.37</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-149.73</v>
+        <v>-155.08</v>
       </c>
       <c r="K69" t="n">
-        <v>134.27</v>
+        <v>139.07</v>
       </c>
       <c r="L69" t="n">
-        <v>201.12</v>
+        <v>208.3</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-123.63</v>
+        <v>-126.64</v>
       </c>
       <c r="K70" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="L70" t="n">
-        <v>123.64</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.49</v>
+        <v>-13.89</v>
       </c>
       <c r="K71" t="n">
-        <v>136.59</v>
+        <v>165.05</v>
       </c>
       <c r="L71" t="n">
-        <v>137.07</v>
+        <v>165.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>29.37</v>
+        <v>30.64</v>
       </c>
       <c r="K72" t="n">
-        <v>-176.24</v>
+        <v>-183.85</v>
       </c>
       <c r="L72" t="n">
-        <v>178.68</v>
+        <v>186.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-175.46</v>
+        <v>-172.2</v>
       </c>
       <c r="K73" t="n">
-        <v>-425.03</v>
+        <v>-417.14</v>
       </c>
       <c r="L73" t="n">
-        <v>459.83</v>
+        <v>451.28</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>57.7</v>
+        <v>55.2</v>
       </c>
       <c r="K74" t="n">
-        <v>12.41</v>
+        <v>11.87</v>
       </c>
       <c r="L74" t="n">
-        <v>59.01</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.78</v>
+        <v>-18.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>21.51</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>62.72</v>
+        <v>59.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.64</v>
+        <v>-45.53</v>
       </c>
       <c r="L76" t="n">
-        <v>78.76000000000001</v>
+        <v>75.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-72.75</v>
+        <v>-69.38</v>
       </c>
       <c r="K77" t="n">
-        <v>19.47</v>
+        <v>18.57</v>
       </c>
       <c r="L77" t="n">
-        <v>75.31</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>42.48</v>
+        <v>41.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.36</v>
+        <v>-60.76</v>
       </c>
       <c r="L78" t="n">
-        <v>75.45</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-86.72</v>
+        <v>-84.33</v>
       </c>
       <c r="K79" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="L79" t="n">
-        <v>86.78</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>49.29</v>
+        <v>48.25</v>
       </c>
       <c r="K80" t="n">
-        <v>122.09</v>
+        <v>119.51</v>
       </c>
       <c r="L80" t="n">
-        <v>131.66</v>
+        <v>128.88</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>15.92</v>
+        <v>16.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.53</v>
+        <v>-75.75</v>
       </c>
       <c r="L81" t="n">
-        <v>74.26000000000001</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-63.41</v>
+        <v>-68.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="L82" t="n">
-        <v>63.41</v>
+        <v>68.87</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>182.46</v>
+        <v>181.26</v>
       </c>
       <c r="K83" t="n">
-        <v>-23.9</v>
+        <v>-23.74</v>
       </c>
       <c r="L83" t="n">
-        <v>184.02</v>
+        <v>182.81</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-150.74</v>
+        <v>-157.23</v>
       </c>
       <c r="L84" t="n">
-        <v>150.76</v>
+        <v>157.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>211.06</v>
+        <v>213.91</v>
       </c>
       <c r="K85" t="n">
-        <v>104.6</v>
+        <v>106.01</v>
       </c>
       <c r="L85" t="n">
-        <v>235.56</v>
+        <v>238.74</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-109.61</v>
+        <v>-124.28</v>
       </c>
       <c r="K86" t="n">
-        <v>111.25</v>
+        <v>126.14</v>
       </c>
       <c r="L86" t="n">
-        <v>156.18</v>
+        <v>177.08</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>136.39</v>
+        <v>143.77</v>
       </c>
       <c r="K87" t="n">
-        <v>154.29</v>
+        <v>162.63</v>
       </c>
       <c r="L87" t="n">
-        <v>205.93</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-258.24</v>
+        <v>-269.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-72.98999999999999</v>
+        <v>-76.17</v>
       </c>
       <c r="L88" t="n">
-        <v>268.35</v>
+        <v>280.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.69</v>
+        <v>-19.07</v>
       </c>
       <c r="K14" t="n">
-        <v>73.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>76.48</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.21</v>
+        <v>-46.27</v>
       </c>
       <c r="K15" t="n">
-        <v>-37.46</v>
+        <v>-38.33</v>
       </c>
       <c r="L15" t="n">
-        <v>58.71</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-56.36</v>
+        <v>-52.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-85.37</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>102.3</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>43.59</v>
+        <v>47.89</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.22</v>
+        <v>-6.83</v>
       </c>
       <c r="L17" t="n">
-        <v>44.03</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>56.3</v>
+        <v>59.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.27</v>
+        <v>-7.71</v>
       </c>
       <c r="L18" t="n">
-        <v>56.76</v>
+        <v>60.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.67</v>
+        <v>-49.79</v>
       </c>
       <c r="K19" t="n">
-        <v>11.97</v>
+        <v>12.77</v>
       </c>
       <c r="L19" t="n">
-        <v>48.18</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>88.93000000000001</v>
+        <v>89.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.11</v>
+        <v>-50.23</v>
       </c>
       <c r="L20" t="n">
-        <v>102.08</v>
+        <v>102.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-27.08</v>
+        <v>-28.86</v>
       </c>
       <c r="K21" t="n">
-        <v>71.76000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="L21" t="n">
-        <v>76.7</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>9.75</v>
+        <v>10.52</v>
       </c>
       <c r="K22" t="n">
-        <v>-78.94</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>79.54000000000001</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>97.98</v>
+        <v>106.03</v>
       </c>
       <c r="K23" t="n">
-        <v>-1</v>
+        <v>-1.09</v>
       </c>
       <c r="L23" t="n">
-        <v>97.98999999999999</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-277.3</v>
+        <v>-257.72</v>
       </c>
       <c r="L24" t="n">
-        <v>277.33</v>
+        <v>257.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-39.99</v>
+        <v>-38.45</v>
       </c>
       <c r="K25" t="n">
-        <v>-205.95</v>
+        <v>-198.02</v>
       </c>
       <c r="L25" t="n">
-        <v>209.8</v>
+        <v>201.72</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>211.44</v>
+        <v>214.63</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.52</v>
+        <v>-14.74</v>
       </c>
       <c r="L26" t="n">
-        <v>211.94</v>
+        <v>215.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>158.33</v>
+        <v>159.72</v>
       </c>
       <c r="K27" t="n">
-        <v>133.52</v>
+        <v>134.69</v>
       </c>
       <c r="L27" t="n">
-        <v>207.12</v>
+        <v>208.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-246.44</v>
+        <v>-249.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-24.46</v>
+        <v>-24.77</v>
       </c>
       <c r="L28" t="n">
-        <v>247.65</v>
+        <v>250.82</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>53.89</v>
+        <v>54.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-28.99</v>
+        <v>-29.27</v>
       </c>
       <c r="L29" t="n">
-        <v>61.19</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-68.95999999999999</v>
+        <v>-67.62</v>
       </c>
       <c r="K30" t="n">
-        <v>21.02</v>
+        <v>20.61</v>
       </c>
       <c r="L30" t="n">
-        <v>72.09</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>13.01</v>
+        <v>12.38</v>
       </c>
       <c r="K31" t="n">
-        <v>92.95</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>93.86</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.91</v>
+        <v>-9.5</v>
       </c>
       <c r="L32" t="n">
-        <v>10.63</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.97</v>
+        <v>-43.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.41</v>
+        <v>-47.08</v>
       </c>
       <c r="L33" t="n">
-        <v>63.24</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>75.66</v>
+        <v>75.16</v>
       </c>
       <c r="K34" t="n">
-        <v>15.23</v>
+        <v>15.13</v>
       </c>
       <c r="L34" t="n">
-        <v>77.18000000000001</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-86.88</v>
+        <v>-91.26000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-19.06</v>
+        <v>-20.02</v>
       </c>
       <c r="L35" t="n">
-        <v>88.94</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>59.68</v>
+        <v>59.03</v>
       </c>
       <c r="K36" t="n">
-        <v>98.3</v>
+        <v>97.22</v>
       </c>
       <c r="L36" t="n">
-        <v>115</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-66.31999999999999</v>
+        <v>-71.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.49</v>
+        <v>-2.68</v>
       </c>
       <c r="L37" t="n">
-        <v>66.37</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>157.28</v>
+        <v>156.24</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.02</v>
+        <v>-4.99</v>
       </c>
       <c r="L38" t="n">
-        <v>157.36</v>
+        <v>156.32</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-95.26000000000001</v>
+        <v>-96.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-92.98999999999999</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>133.12</v>
+        <v>134.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-116.78</v>
+        <v>-121.25</v>
       </c>
       <c r="K40" t="n">
-        <v>10.93</v>
+        <v>11.35</v>
       </c>
       <c r="L40" t="n">
-        <v>117.29</v>
+        <v>121.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-81.31999999999999</v>
+        <v>-86.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-100.61</v>
+        <v>-107.58</v>
       </c>
       <c r="L41" t="n">
-        <v>129.37</v>
+        <v>138.32</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-73.23</v>
+        <v>-72.2</v>
       </c>
       <c r="K42" t="n">
-        <v>227.58</v>
+        <v>224.39</v>
       </c>
       <c r="L42" t="n">
-        <v>239.07</v>
+        <v>235.72</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-18.66</v>
+        <v>-20.15</v>
       </c>
       <c r="K43" t="n">
-        <v>-115.69</v>
+        <v>-124.97</v>
       </c>
       <c r="L43" t="n">
-        <v>117.18</v>
+        <v>126.58</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>28.28</v>
+        <v>29.56</v>
       </c>
       <c r="K44" t="n">
-        <v>42.33</v>
+        <v>44.24</v>
       </c>
       <c r="L44" t="n">
-        <v>50.91</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>36.44</v>
+        <v>36.59</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.67</v>
+        <v>-50.88</v>
       </c>
       <c r="L45" t="n">
-        <v>62.41</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>27.45</v>
+        <v>27.84</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.73</v>
+        <v>-51.43</v>
       </c>
       <c r="L46" t="n">
-        <v>57.68</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>107.62</v>
+        <v>102.21</v>
       </c>
       <c r="K47" t="n">
-        <v>30.35</v>
+        <v>28.82</v>
       </c>
       <c r="L47" t="n">
-        <v>111.82</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-40.29</v>
+        <v>-42.8</v>
       </c>
       <c r="K48" t="n">
-        <v>36.65</v>
+        <v>38.93</v>
       </c>
       <c r="L48" t="n">
-        <v>54.46</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>7.92</v>
+        <v>8.34</v>
       </c>
       <c r="K49" t="n">
-        <v>52.28</v>
+        <v>55.04</v>
       </c>
       <c r="L49" t="n">
-        <v>52.88</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-114.61</v>
+        <v>-107.68</v>
       </c>
       <c r="K50" t="n">
-        <v>113.89</v>
+        <v>107.01</v>
       </c>
       <c r="L50" t="n">
-        <v>161.57</v>
+        <v>151.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>8.44</v>
+        <v>7.89</v>
       </c>
       <c r="K51" t="n">
-        <v>189.17</v>
+        <v>176.93</v>
       </c>
       <c r="L51" t="n">
-        <v>189.36</v>
+        <v>177.1</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-145.78</v>
+        <v>-140.31</v>
       </c>
       <c r="K52" t="n">
-        <v>122.03</v>
+        <v>117.45</v>
       </c>
       <c r="L52" t="n">
-        <v>190.11</v>
+        <v>182.98</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-39.12</v>
+        <v>-42.7</v>
       </c>
       <c r="K53" t="n">
-        <v>96.15000000000001</v>
+        <v>104.95</v>
       </c>
       <c r="L53" t="n">
-        <v>103.81</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-54.26</v>
+        <v>-57.04</v>
       </c>
       <c r="K54" t="n">
-        <v>99.48999999999999</v>
+        <v>104.58</v>
       </c>
       <c r="L54" t="n">
-        <v>113.33</v>
+        <v>119.13</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-70.11</v>
+        <v>-72.77</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.99</v>
+        <v>-107.94</v>
       </c>
       <c r="L55" t="n">
-        <v>125.41</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>81.86</v>
+        <v>85.88</v>
       </c>
       <c r="K56" t="n">
-        <v>-125.96</v>
+        <v>-132.14</v>
       </c>
       <c r="L56" t="n">
-        <v>150.23</v>
+        <v>157.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-84.05</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>108.41</v>
+        <v>118.89</v>
       </c>
       <c r="L57" t="n">
-        <v>137.18</v>
+        <v>150.43</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-310.21</v>
+        <v>-295.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.33</v>
+        <v>-148.99</v>
       </c>
       <c r="L58" t="n">
-        <v>347.37</v>
+        <v>331.06</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.01</v>
+        <v>-5.51</v>
       </c>
       <c r="K59" t="n">
-        <v>-40.77</v>
+        <v>-44.82</v>
       </c>
       <c r="L59" t="n">
-        <v>41.08</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.26</v>
+        <v>-61.37</v>
       </c>
       <c r="K60" t="n">
-        <v>-16.65</v>
+        <v>-16.96</v>
       </c>
       <c r="L60" t="n">
-        <v>62.52</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="K61" t="n">
-        <v>74.17</v>
+        <v>73.37</v>
       </c>
       <c r="L61" t="n">
-        <v>74.25</v>
+        <v>73.45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-40.33</v>
+        <v>-39.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-74.59</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>84.79000000000001</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.31</v>
+        <v>-52.11</v>
       </c>
       <c r="L63" t="n">
-        <v>48.47</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>69.02</v>
+        <v>68.69</v>
       </c>
       <c r="K64" t="n">
-        <v>47.96</v>
+        <v>47.73</v>
       </c>
       <c r="L64" t="n">
-        <v>84.05</v>
+        <v>83.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>12.54</v>
+        <v>13.33</v>
       </c>
       <c r="K65" t="n">
-        <v>-76.84</v>
+        <v>-81.69</v>
       </c>
       <c r="L65" t="n">
-        <v>77.84999999999999</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>120.18</v>
+        <v>117.23</v>
       </c>
       <c r="K66" t="n">
-        <v>90.7</v>
+        <v>88.47</v>
       </c>
       <c r="L66" t="n">
-        <v>150.57</v>
+        <v>146.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-40.19</v>
+        <v>-38.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-160.81</v>
+        <v>-152.8</v>
       </c>
       <c r="L67" t="n">
-        <v>165.76</v>
+        <v>157.49</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-114.06</v>
+        <v>-108.4</v>
       </c>
       <c r="K68" t="n">
-        <v>173.19</v>
+        <v>164.6</v>
       </c>
       <c r="L68" t="n">
-        <v>207.37</v>
+        <v>197.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-155.08</v>
+        <v>-151.69</v>
       </c>
       <c r="K69" t="n">
-        <v>139.07</v>
+        <v>136.03</v>
       </c>
       <c r="L69" t="n">
-        <v>208.3</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-126.64</v>
+        <v>-129.34</v>
       </c>
       <c r="K70" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="L70" t="n">
-        <v>126.65</v>
+        <v>129.35</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.89</v>
+        <v>-15.35</v>
       </c>
       <c r="K71" t="n">
-        <v>165.05</v>
+        <v>182.37</v>
       </c>
       <c r="L71" t="n">
-        <v>165.64</v>
+        <v>183.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>30.64</v>
+        <v>31.14</v>
       </c>
       <c r="K72" t="n">
-        <v>-183.85</v>
+        <v>-186.85</v>
       </c>
       <c r="L72" t="n">
-        <v>186.39</v>
+        <v>189.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-172.2</v>
+        <v>-160.16</v>
       </c>
       <c r="K73" t="n">
-        <v>-417.14</v>
+        <v>-387.96</v>
       </c>
       <c r="L73" t="n">
-        <v>451.28</v>
+        <v>419.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>55.2</v>
+        <v>56.85</v>
       </c>
       <c r="K74" t="n">
-        <v>11.87</v>
+        <v>12.23</v>
       </c>
       <c r="L74" t="n">
-        <v>56.47</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.79</v>
+        <v>-20.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="L75" t="n">
-        <v>20.43</v>
+        <v>22.21</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>59.94</v>
+        <v>57.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.53</v>
+        <v>-43.93</v>
       </c>
       <c r="L76" t="n">
-        <v>75.27</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-69.38</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>18.57</v>
+        <v>19</v>
       </c>
       <c r="L77" t="n">
-        <v>71.81999999999999</v>
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>41.39</v>
+        <v>41.7</v>
       </c>
       <c r="K78" t="n">
-        <v>-60.76</v>
+        <v>-61.22</v>
       </c>
       <c r="L78" t="n">
-        <v>73.52</v>
+        <v>74.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-84.33</v>
+        <v>-83.28</v>
       </c>
       <c r="K79" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="L79" t="n">
-        <v>84.40000000000001</v>
+        <v>83.34999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>48.25</v>
+        <v>47.92</v>
       </c>
       <c r="K80" t="n">
-        <v>119.51</v>
+        <v>118.7</v>
       </c>
       <c r="L80" t="n">
-        <v>128.88</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>16.63</v>
+        <v>17.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-75.75</v>
+        <v>-79.98999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>77.55</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-68.87</v>
+        <v>-75.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="L82" t="n">
-        <v>68.87</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>181.26</v>
+        <v>178.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-23.74</v>
+        <v>-23.35</v>
       </c>
       <c r="L83" t="n">
-        <v>182.81</v>
+        <v>179.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K84" t="n">
-        <v>-157.23</v>
+        <v>-160.12</v>
       </c>
       <c r="L84" t="n">
-        <v>157.26</v>
+        <v>160.14</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>213.91</v>
+        <v>203.95</v>
       </c>
       <c r="K85" t="n">
-        <v>106.01</v>
+        <v>101.07</v>
       </c>
       <c r="L85" t="n">
-        <v>238.74</v>
+        <v>227.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-124.28</v>
+        <v>-133.61</v>
       </c>
       <c r="K86" t="n">
-        <v>126.14</v>
+        <v>135.61</v>
       </c>
       <c r="L86" t="n">
-        <v>177.08</v>
+        <v>190.38</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>143.77</v>
+        <v>144.5</v>
       </c>
       <c r="K87" t="n">
-        <v>162.63</v>
+        <v>163.46</v>
       </c>
       <c r="L87" t="n">
-        <v>217.07</v>
+        <v>218.17</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-269.5</v>
+        <v>-267.46</v>
       </c>
       <c r="K88" t="n">
-        <v>-76.17</v>
+        <v>-75.59</v>
       </c>
       <c r="L88" t="n">
-        <v>280.06</v>
+        <v>277.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="F14" t="n">
-        <v>12.45</v>
+        <v>11.54</v>
       </c>
       <c r="G14" t="n">
-        <v>254.5</v>
+        <v>246</v>
       </c>
       <c r="H14" t="n">
-        <v>58.6</v>
+        <v>57.5</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.07</v>
+        <v>-58.42</v>
       </c>
       <c r="K14" t="n">
-        <v>71.59999999999999</v>
+        <v>-42.19</v>
       </c>
       <c r="L14" t="n">
-        <v>74.09999999999999</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:15:20</t>
+          <t>05:13:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.87</v>
+        <v>3.31</v>
       </c>
       <c r="F15" t="n">
-        <v>12.42</v>
+        <v>8.75</v>
       </c>
       <c r="G15" t="n">
-        <v>230.4</v>
+        <v>247.8</v>
       </c>
       <c r="H15" t="n">
-        <v>46.3</v>
+        <v>52.1</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.27</v>
+        <v>-55.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-38.33</v>
+        <v>13.34</v>
       </c>
       <c r="L15" t="n">
-        <v>60.09</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:16:03</t>
+          <t>05:14:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.79</v>
+        <v>2.91</v>
       </c>
       <c r="F16" t="n">
-        <v>12.43</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>238.6</v>
       </c>
       <c r="H16" t="n">
-        <v>56.5</v>
+        <v>55.7</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.85</v>
+        <v>-62.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.04000000000001</v>
+        <v>52.54</v>
       </c>
       <c r="L16" t="n">
-        <v>95.92</v>
+        <v>81.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:21:14</t>
+          <t>05:20:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="F17" t="n">
-        <v>13.17</v>
+        <v>11.19</v>
       </c>
       <c r="G17" t="n">
-        <v>227.3</v>
+        <v>240</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>47.89</v>
+        <v>-28.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.83</v>
+        <v>94.63</v>
       </c>
       <c r="L17" t="n">
-        <v>48.38</v>
+        <v>98.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:22:20</t>
+          <t>05:22:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.37</v>
+        <v>3.54</v>
       </c>
       <c r="F18" t="n">
-        <v>12.53</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>233.7</v>
+        <v>230</v>
       </c>
       <c r="H18" t="n">
-        <v>52.6</v>
+        <v>49.5</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>59.67</v>
+        <v>-90.19</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.71</v>
+        <v>22.77</v>
       </c>
       <c r="L18" t="n">
-        <v>60.17</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:24:02</t>
+          <t>05:23:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.57</v>
+        <v>3.44</v>
       </c>
       <c r="F19" t="n">
-        <v>12.87</v>
+        <v>10.58</v>
       </c>
       <c r="G19" t="n">
-        <v>226.6</v>
+        <v>236.2</v>
       </c>
       <c r="H19" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-49.79</v>
+        <v>49.33</v>
       </c>
       <c r="K19" t="n">
-        <v>12.77</v>
+        <v>30.89</v>
       </c>
       <c r="L19" t="n">
-        <v>51.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:28:32</t>
+          <t>05:27:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.55</v>
+        <v>4.04</v>
       </c>
       <c r="F20" t="n">
-        <v>12.84</v>
+        <v>12.58</v>
       </c>
       <c r="G20" t="n">
-        <v>237.8</v>
+        <v>237.7</v>
       </c>
       <c r="H20" t="n">
-        <v>50.7</v>
+        <v>61.4</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>89.16</v>
+        <v>-137.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.23</v>
+        <v>-79.11</v>
       </c>
       <c r="L20" t="n">
-        <v>102.34</v>
+        <v>158.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:29:56</t>
+          <t>05:29:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="F21" t="n">
-        <v>12.19</v>
+        <v>11.89</v>
       </c>
       <c r="G21" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H21" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.86</v>
+        <v>-38.75</v>
       </c>
       <c r="K21" t="n">
-        <v>76.48</v>
+        <v>-3.82</v>
       </c>
       <c r="L21" t="n">
-        <v>81.73999999999999</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:30:49</t>
+          <t>05:31:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="F22" t="n">
-        <v>12.9</v>
+        <v>8.01</v>
       </c>
       <c r="G22" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="H22" t="n">
-        <v>54.8</v>
+        <v>52.9</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>10.52</v>
+        <v>-22.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.09999999999999</v>
+        <v>-90.77</v>
       </c>
       <c r="L22" t="n">
-        <v>85.75</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:35:42</t>
+          <t>05:34:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.22</v>
+        <v>3.81</v>
       </c>
       <c r="F23" t="n">
-        <v>12.69</v>
+        <v>10.78</v>
       </c>
       <c r="G23" t="n">
-        <v>237</v>
+        <v>225.7</v>
       </c>
       <c r="H23" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>106.03</v>
+        <v>-175.42</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.09</v>
+        <v>-19.47</v>
       </c>
       <c r="L23" t="n">
-        <v>106.03</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:37:31</t>
+          <t>05:35:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.47</v>
+        <v>2.33</v>
       </c>
       <c r="F24" t="n">
-        <v>12.72</v>
+        <v>8.4</v>
       </c>
       <c r="G24" t="n">
-        <v>225.7</v>
+        <v>228.7</v>
       </c>
       <c r="H24" t="n">
-        <v>54.2</v>
+        <v>51.2</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>119.13</v>
       </c>
       <c r="K24" t="n">
-        <v>-257.72</v>
+        <v>-84.61</v>
       </c>
       <c r="L24" t="n">
-        <v>257.75</v>
+        <v>146.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:38:47</t>
+          <t>05:38:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="F25" t="n">
-        <v>13.16</v>
+        <v>11.52</v>
       </c>
       <c r="G25" t="n">
-        <v>253.7</v>
+        <v>246.2</v>
       </c>
       <c r="H25" t="n">
-        <v>46.9</v>
+        <v>54.3</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-38.45</v>
+        <v>-159.79</v>
       </c>
       <c r="K25" t="n">
-        <v>-198.02</v>
+        <v>125.77</v>
       </c>
       <c r="L25" t="n">
-        <v>201.72</v>
+        <v>203.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:41:56</t>
+          <t>05:43:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.83</v>
+        <v>3.64</v>
       </c>
       <c r="F26" t="n">
-        <v>12.67</v>
+        <v>9.25</v>
       </c>
       <c r="G26" t="n">
-        <v>246.2</v>
+        <v>236.4</v>
       </c>
       <c r="H26" t="n">
-        <v>54.3</v>
+        <v>52.4</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>214.63</v>
+        <v>-180.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.74</v>
+        <v>159.86</v>
       </c>
       <c r="L26" t="n">
-        <v>215.14</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:44:46</t>
+          <t>05:45:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.68</v>
+        <v>4.36</v>
       </c>
       <c r="F27" t="n">
-        <v>13.24</v>
+        <v>14.6</v>
       </c>
       <c r="G27" t="n">
-        <v>227.4</v>
+        <v>229.5</v>
       </c>
       <c r="H27" t="n">
-        <v>50.8</v>
+        <v>47.4</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>159.72</v>
+        <v>-2.47</v>
       </c>
       <c r="K27" t="n">
-        <v>134.69</v>
+        <v>-216.26</v>
       </c>
       <c r="L27" t="n">
-        <v>208.93</v>
+        <v>216.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:46:42</t>
+          <t>05:47:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.37</v>
+        <v>3.24</v>
       </c>
       <c r="F28" t="n">
-        <v>12.82</v>
+        <v>9.68</v>
       </c>
       <c r="G28" t="n">
-        <v>234.7</v>
+        <v>238.4</v>
       </c>
       <c r="H28" t="n">
-        <v>47.4</v>
+        <v>55</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-249.6</v>
+        <v>7.03</v>
       </c>
       <c r="K28" t="n">
-        <v>-24.77</v>
+        <v>215.57</v>
       </c>
       <c r="L28" t="n">
-        <v>250.82</v>
+        <v>215.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:58:00</t>
+          <t>05:59:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="F29" t="n">
-        <v>13.33</v>
+        <v>10.4</v>
       </c>
       <c r="G29" t="n">
-        <v>241.1</v>
+        <v>236</v>
       </c>
       <c r="H29" t="n">
-        <v>44</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>54.41</v>
+        <v>30.68</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.27</v>
+        <v>-59.71</v>
       </c>
       <c r="L29" t="n">
-        <v>61.78</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:00:44</t>
+          <t>06:00:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.93</v>
+        <v>3.11</v>
       </c>
       <c r="F30" t="n">
-        <v>12.89</v>
+        <v>10.37</v>
       </c>
       <c r="G30" t="n">
-        <v>236.1</v>
+        <v>245.5</v>
       </c>
       <c r="H30" t="n">
-        <v>50.6</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-67.62</v>
+        <v>32.3</v>
       </c>
       <c r="K30" t="n">
-        <v>20.61</v>
+        <v>-48.33</v>
       </c>
       <c r="L30" t="n">
-        <v>70.69</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:01:50</t>
+          <t>06:01:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="F31" t="n">
-        <v>12.56</v>
+        <v>13.52</v>
       </c>
       <c r="G31" t="n">
-        <v>240.3</v>
+        <v>243.9</v>
       </c>
       <c r="H31" t="n">
-        <v>50.8</v>
+        <v>60.7</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>12.38</v>
+        <v>34.48</v>
       </c>
       <c r="K31" t="n">
-        <v>88.45999999999999</v>
+        <v>-111.59</v>
       </c>
       <c r="L31" t="n">
-        <v>89.33</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:07:44</t>
+          <t>06:04:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.03</v>
+        <v>3.85</v>
       </c>
       <c r="F32" t="n">
-        <v>12.83</v>
+        <v>12.01</v>
       </c>
       <c r="G32" t="n">
-        <v>219.2</v>
+        <v>230.5</v>
       </c>
       <c r="H32" t="n">
-        <v>54.7</v>
+        <v>51.4</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>6.18</v>
+        <v>-67.73999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.5</v>
+        <v>70.02</v>
       </c>
       <c r="L32" t="n">
-        <v>11.33</v>
+        <v>97.43000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:09:20</t>
+          <t>06:06:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.35</v>
+        <v>4.34</v>
       </c>
       <c r="F33" t="n">
-        <v>13.47</v>
+        <v>11.74</v>
       </c>
       <c r="G33" t="n">
-        <v>250</v>
+        <v>229.9</v>
       </c>
       <c r="H33" t="n">
-        <v>55.6</v>
+        <v>48.6</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-43.59</v>
+        <v>-52.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.08</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>64.16</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:10:46</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="F34" t="n">
-        <v>12.41</v>
+        <v>13.24</v>
       </c>
       <c r="G34" t="n">
-        <v>245</v>
+        <v>247.8</v>
       </c>
       <c r="H34" t="n">
-        <v>49.5</v>
+        <v>52.7</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>75.16</v>
+        <v>-74.69</v>
       </c>
       <c r="K34" t="n">
-        <v>15.13</v>
+        <v>18.38</v>
       </c>
       <c r="L34" t="n">
-        <v>76.67</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:14:36</t>
+          <t>06:13:31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.25</v>
+        <v>3.84</v>
       </c>
       <c r="F35" t="n">
-        <v>13.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>239.8</v>
+        <v>233.9</v>
       </c>
       <c r="H35" t="n">
-        <v>52.4</v>
+        <v>51.3</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-91.26000000000001</v>
+        <v>-87.64</v>
       </c>
       <c r="K35" t="n">
-        <v>-20.02</v>
+        <v>-50.52</v>
       </c>
       <c r="L35" t="n">
-        <v>93.43000000000001</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:16:45</t>
+          <t>06:15:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="F36" t="n">
-        <v>13.28</v>
+        <v>14.6</v>
       </c>
       <c r="G36" t="n">
-        <v>236</v>
+        <v>233.9</v>
       </c>
       <c r="H36" t="n">
-        <v>49.7</v>
+        <v>56.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>59.03</v>
+        <v>94.52</v>
       </c>
       <c r="K36" t="n">
-        <v>97.22</v>
+        <v>66.56</v>
       </c>
       <c r="L36" t="n">
-        <v>113.74</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:18:06</t>
+          <t>06:16:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="F37" t="n">
-        <v>12.43</v>
+        <v>13.05</v>
       </c>
       <c r="G37" t="n">
-        <v>238.7</v>
+        <v>238.2</v>
       </c>
       <c r="H37" t="n">
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-71.3</v>
+        <v>51.72</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.68</v>
+        <v>142.02</v>
       </c>
       <c r="L37" t="n">
-        <v>71.34999999999999</v>
+        <v>151.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:23:16</t>
+          <t>06:19:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="F38" t="n">
-        <v>12.72</v>
+        <v>7.96</v>
       </c>
       <c r="G38" t="n">
-        <v>232.1</v>
+        <v>238.4</v>
       </c>
       <c r="H38" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>156.24</v>
+        <v>123.71</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.99</v>
+        <v>-37.83</v>
       </c>
       <c r="L38" t="n">
-        <v>156.32</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:24:07</t>
+          <t>06:21:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="F39" t="n">
-        <v>12.96</v>
+        <v>14.17</v>
       </c>
       <c r="G39" t="n">
-        <v>247.5</v>
+        <v>232.6</v>
       </c>
       <c r="H39" t="n">
-        <v>48.7</v>
+        <v>54.7</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-96.12</v>
+        <v>-91.63</v>
       </c>
       <c r="K39" t="n">
-        <v>-93.81999999999999</v>
+        <v>118.94</v>
       </c>
       <c r="L39" t="n">
-        <v>134.31</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:23:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.75</v>
+        <v>3.99</v>
       </c>
       <c r="F40" t="n">
-        <v>12.97</v>
+        <v>13.71</v>
       </c>
       <c r="G40" t="n">
-        <v>231.8</v>
+        <v>232.7</v>
       </c>
       <c r="H40" t="n">
-        <v>53.6</v>
+        <v>47.7</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-121.25</v>
+        <v>-166.92</v>
       </c>
       <c r="K40" t="n">
-        <v>11.35</v>
+        <v>-135.12</v>
       </c>
       <c r="L40" t="n">
-        <v>121.78</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:30:24</t>
+          <t>06:27:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.34</v>
+        <v>4.43</v>
       </c>
       <c r="F41" t="n">
-        <v>12.88</v>
+        <v>14.6</v>
       </c>
       <c r="G41" t="n">
-        <v>256.3</v>
+        <v>236.8</v>
       </c>
       <c r="H41" t="n">
-        <v>57.1</v>
+        <v>54.2</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-86.95</v>
+        <v>119.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-107.58</v>
+        <v>253.72</v>
       </c>
       <c r="L41" t="n">
-        <v>138.32</v>
+        <v>280.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:32:33</t>
+          <t>06:29:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="F42" t="n">
-        <v>12.86</v>
+        <v>13.66</v>
       </c>
       <c r="G42" t="n">
-        <v>231.3</v>
+        <v>235.4</v>
       </c>
       <c r="H42" t="n">
-        <v>54.7</v>
+        <v>48.5</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-72.2</v>
+        <v>-221.01</v>
       </c>
       <c r="K42" t="n">
-        <v>224.39</v>
+        <v>280.68</v>
       </c>
       <c r="L42" t="n">
-        <v>235.72</v>
+        <v>357.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:34:36</t>
+          <t>06:31:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.34</v>
+        <v>4.04</v>
       </c>
       <c r="F43" t="n">
-        <v>12.43</v>
+        <v>12.77</v>
       </c>
       <c r="G43" t="n">
-        <v>238.5</v>
+        <v>238.6</v>
       </c>
       <c r="H43" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-20.15</v>
+        <v>-264.44</v>
       </c>
       <c r="K43" t="n">
-        <v>-124.97</v>
+        <v>-89.19</v>
       </c>
       <c r="L43" t="n">
-        <v>126.58</v>
+        <v>279.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:45:38</t>
+          <t>06:42:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="F44" t="n">
-        <v>12.19</v>
+        <v>7.99</v>
       </c>
       <c r="G44" t="n">
-        <v>227.8</v>
+        <v>241.2</v>
       </c>
       <c r="H44" t="n">
-        <v>46.3</v>
+        <v>58.3</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>29.56</v>
+        <v>-2.96</v>
       </c>
       <c r="K44" t="n">
-        <v>44.24</v>
+        <v>54.93</v>
       </c>
       <c r="L44" t="n">
-        <v>53.2</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:47:10</t>
+          <t>06:44:23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.88</v>
+        <v>4.34</v>
       </c>
       <c r="F45" t="n">
-        <v>12.69</v>
+        <v>14.6</v>
       </c>
       <c r="G45" t="n">
-        <v>251.1</v>
+        <v>243.6</v>
       </c>
       <c r="H45" t="n">
-        <v>53.2</v>
+        <v>54</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>36.59</v>
+        <v>-0.37</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.88</v>
+        <v>-95.12</v>
       </c>
       <c r="L45" t="n">
-        <v>62.67</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:49:40</t>
+          <t>06:45:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="F46" t="n">
-        <v>12.56</v>
+        <v>11.41</v>
       </c>
       <c r="G46" t="n">
-        <v>235.8</v>
+        <v>242.1</v>
       </c>
       <c r="H46" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>27.84</v>
+        <v>91.75</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.43</v>
+        <v>27.5</v>
       </c>
       <c r="L46" t="n">
-        <v>58.48</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:54:12</t>
+          <t>06:49:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.65</v>
+        <v>3.55</v>
       </c>
       <c r="F47" t="n">
-        <v>12.85</v>
+        <v>13.15</v>
       </c>
       <c r="G47" t="n">
-        <v>246</v>
+        <v>255.9</v>
       </c>
       <c r="H47" t="n">
-        <v>54.2</v>
+        <v>47.6</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>102.21</v>
+        <v>-90.61</v>
       </c>
       <c r="K47" t="n">
-        <v>28.82</v>
+        <v>12.74</v>
       </c>
       <c r="L47" t="n">
-        <v>106.19</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:55:46</t>
+          <t>06:51:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="F48" t="n">
-        <v>12.72</v>
+        <v>8.09</v>
       </c>
       <c r="G48" t="n">
-        <v>228.5</v>
+        <v>238.4</v>
       </c>
       <c r="H48" t="n">
-        <v>51.6</v>
+        <v>46.8</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.8</v>
+        <v>-49.11</v>
       </c>
       <c r="K48" t="n">
-        <v>38.93</v>
+        <v>38.53</v>
       </c>
       <c r="L48" t="n">
-        <v>57.86</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:58:12</t>
+          <t>06:53:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="F49" t="n">
-        <v>12.2</v>
+        <v>13.31</v>
       </c>
       <c r="G49" t="n">
-        <v>232.8</v>
+        <v>228</v>
       </c>
       <c r="H49" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>8.34</v>
+        <v>7.94</v>
       </c>
       <c r="K49" t="n">
-        <v>55.04</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>55.66</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:02:06</t>
+          <t>06:59:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="F50" t="n">
-        <v>12.77</v>
+        <v>11.63</v>
       </c>
       <c r="G50" t="n">
-        <v>226.9</v>
+        <v>239.4</v>
       </c>
       <c r="H50" t="n">
-        <v>52</v>
+        <v>46.1</v>
       </c>
       <c r="I50" t="n">
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-107.68</v>
+        <v>-138.3</v>
       </c>
       <c r="K50" t="n">
-        <v>107.01</v>
+        <v>125.71</v>
       </c>
       <c r="L50" t="n">
-        <v>151.81</v>
+        <v>186.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:03:39</t>
+          <t>07:00:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="F51" t="n">
-        <v>12.82</v>
+        <v>11.96</v>
       </c>
       <c r="G51" t="n">
-        <v>235.8</v>
+        <v>240.5</v>
       </c>
       <c r="H51" t="n">
-        <v>54.9</v>
+        <v>50.5</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>7.89</v>
+        <v>0.61</v>
       </c>
       <c r="K51" t="n">
-        <v>176.93</v>
+        <v>192.95</v>
       </c>
       <c r="L51" t="n">
-        <v>177.1</v>
+        <v>192.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:05:45</t>
+          <t>07:01:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="F52" t="n">
-        <v>12.92</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>240</v>
+        <v>242.5</v>
       </c>
       <c r="H52" t="n">
-        <v>50.3</v>
+        <v>52.6</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-140.31</v>
+        <v>-158.95</v>
       </c>
       <c r="K52" t="n">
-        <v>117.45</v>
+        <v>110.21</v>
       </c>
       <c r="L52" t="n">
-        <v>182.98</v>
+        <v>193.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:11:42</t>
+          <t>07:06:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="F53" t="n">
-        <v>12.42</v>
+        <v>14.17</v>
       </c>
       <c r="G53" t="n">
-        <v>245.4</v>
+        <v>232.4</v>
       </c>
       <c r="H53" t="n">
-        <v>55.7</v>
+        <v>55.3</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-42.7</v>
+        <v>-126.68</v>
       </c>
       <c r="K53" t="n">
-        <v>104.95</v>
+        <v>60.7</v>
       </c>
       <c r="L53" t="n">
-        <v>113.3</v>
+        <v>140.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:13:37</t>
+          <t>07:07:54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="F54" t="n">
-        <v>12.39</v>
+        <v>10.85</v>
       </c>
       <c r="G54" t="n">
-        <v>232.5</v>
+        <v>231.8</v>
       </c>
       <c r="H54" t="n">
-        <v>50.4</v>
+        <v>48.9</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-57.04</v>
+        <v>-108.69</v>
       </c>
       <c r="K54" t="n">
-        <v>104.58</v>
+        <v>91.7</v>
       </c>
       <c r="L54" t="n">
-        <v>119.13</v>
+        <v>142.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:14:52</t>
+          <t>07:10:06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="F55" t="n">
-        <v>12.16</v>
+        <v>13.27</v>
       </c>
       <c r="G55" t="n">
-        <v>225.6</v>
+        <v>227.3</v>
       </c>
       <c r="H55" t="n">
-        <v>42.9</v>
+        <v>45.4</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-72.77</v>
+        <v>-107.5</v>
       </c>
       <c r="K55" t="n">
-        <v>-107.94</v>
+        <v>-140.91</v>
       </c>
       <c r="L55" t="n">
-        <v>130.18</v>
+        <v>177.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:19:29</t>
+          <t>07:13:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="F56" t="n">
-        <v>13.1</v>
+        <v>13.65</v>
       </c>
       <c r="G56" t="n">
-        <v>238.7</v>
+        <v>245.9</v>
       </c>
       <c r="H56" t="n">
-        <v>55.3</v>
+        <v>52</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>85.88</v>
+        <v>55.35</v>
       </c>
       <c r="K56" t="n">
-        <v>-132.14</v>
+        <v>-213.7</v>
       </c>
       <c r="L56" t="n">
-        <v>157.59</v>
+        <v>220.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:21:38</t>
+          <t>07:16:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="F57" t="n">
-        <v>12.71</v>
+        <v>11.66</v>
       </c>
       <c r="G57" t="n">
-        <v>229.9</v>
+        <v>238.3</v>
       </c>
       <c r="H57" t="n">
-        <v>53.6</v>
+        <v>47.5</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-92.18000000000001</v>
+        <v>-187.36</v>
       </c>
       <c r="K57" t="n">
-        <v>118.89</v>
+        <v>82.56</v>
       </c>
       <c r="L57" t="n">
-        <v>150.43</v>
+        <v>204.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:22:27</t>
+          <t>07:17:28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="F58" t="n">
-        <v>12.6</v>
+        <v>13.23</v>
       </c>
       <c r="G58" t="n">
-        <v>232.8</v>
+        <v>236</v>
       </c>
       <c r="H58" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-295.64</v>
+        <v>-383.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-148.99</v>
+        <v>-195.29</v>
       </c>
       <c r="L58" t="n">
-        <v>331.06</v>
+        <v>430.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:33:35</t>
+          <t>07:29:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>12.07</v>
+        <v>14.02</v>
       </c>
       <c r="G59" t="n">
-        <v>234.4</v>
+        <v>225.3</v>
       </c>
       <c r="H59" t="n">
-        <v>55</v>
+        <v>49.8</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.51</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.82</v>
+        <v>-54.77</v>
       </c>
       <c r="L59" t="n">
-        <v>45.15</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:34:58</t>
+          <t>07:31:28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="F60" t="n">
-        <v>13.04</v>
+        <v>14.6</v>
       </c>
       <c r="G60" t="n">
-        <v>239.3</v>
+        <v>244.8</v>
       </c>
       <c r="H60" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.37</v>
+        <v>-62.8</v>
       </c>
       <c r="K60" t="n">
-        <v>-16.96</v>
+        <v>-17.43</v>
       </c>
       <c r="L60" t="n">
-        <v>63.67</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:36:21</t>
+          <t>07:33:32</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="F61" t="n">
-        <v>13.08</v>
+        <v>14.41</v>
       </c>
       <c r="G61" t="n">
-        <v>251.2</v>
+        <v>245.5</v>
       </c>
       <c r="H61" t="n">
-        <v>50.2</v>
+        <v>58.2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>3.31</v>
+        <v>2.31</v>
       </c>
       <c r="K61" t="n">
-        <v>73.37</v>
+        <v>76.88</v>
       </c>
       <c r="L61" t="n">
-        <v>73.45</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:42:11</t>
+          <t>07:39:03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="F62" t="n">
-        <v>12.9</v>
+        <v>12.84</v>
       </c>
       <c r="G62" t="n">
-        <v>241.3</v>
+        <v>241.9</v>
       </c>
       <c r="H62" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="I62" t="n">
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-39.42</v>
+        <v>-48.35</v>
       </c>
       <c r="K62" t="n">
-        <v>-72.90000000000001</v>
+        <v>-86.05</v>
       </c>
       <c r="L62" t="n">
-        <v>82.88</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:44:23</t>
+          <t>07:40:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="F63" t="n">
-        <v>12.47</v>
+        <v>10.63</v>
       </c>
       <c r="G63" t="n">
-        <v>239.2</v>
+        <v>233.5</v>
       </c>
       <c r="H63" t="n">
-        <v>43.9</v>
+        <v>52.2</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>4.31</v>
+        <v>-0.29</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.11</v>
+        <v>-60.9</v>
       </c>
       <c r="L63" t="n">
-        <v>52.29</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:45:31</t>
+          <t>07:42:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="F64" t="n">
-        <v>12.46</v>
+        <v>14.6</v>
       </c>
       <c r="G64" t="n">
-        <v>237.9</v>
+        <v>233.2</v>
       </c>
       <c r="H64" t="n">
-        <v>53.9</v>
+        <v>51.5</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>68.69</v>
+        <v>69.33</v>
       </c>
       <c r="K64" t="n">
-        <v>47.73</v>
+        <v>47.58</v>
       </c>
       <c r="L64" t="n">
-        <v>83.65000000000001</v>
+        <v>84.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:50:32</t>
+          <t>07:45:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="F65" t="n">
-        <v>13.01</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
-        <v>224.1</v>
+        <v>244.3</v>
       </c>
       <c r="H65" t="n">
-        <v>55.8</v>
+        <v>44.7</v>
       </c>
       <c r="I65" t="n">
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>13.33</v>
+        <v>-7.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-81.69</v>
+        <v>-94.67</v>
       </c>
       <c r="L65" t="n">
-        <v>82.77</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:52:56</t>
+          <t>07:47:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="F66" t="n">
-        <v>12.04</v>
+        <v>12.13</v>
       </c>
       <c r="G66" t="n">
-        <v>228.3</v>
+        <v>224.8</v>
       </c>
       <c r="H66" t="n">
-        <v>45.8</v>
+        <v>46.8</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>117.23</v>
+        <v>121.02</v>
       </c>
       <c r="K66" t="n">
-        <v>88.47</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>146.87</v>
+        <v>149.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:54:37</t>
+          <t>07:48:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="F67" t="n">
-        <v>13.25</v>
+        <v>11.12</v>
       </c>
       <c r="G67" t="n">
-        <v>237.6</v>
+        <v>249.1</v>
       </c>
       <c r="H67" t="n">
-        <v>47.6</v>
+        <v>51.4</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-38.19</v>
+        <v>-49.93</v>
       </c>
       <c r="K67" t="n">
-        <v>-152.8</v>
+        <v>-161.33</v>
       </c>
       <c r="L67" t="n">
-        <v>157.49</v>
+        <v>168.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:59:25</t>
+          <t>07:54:40</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="F68" t="n">
-        <v>12.53</v>
+        <v>12.32</v>
       </c>
       <c r="G68" t="n">
-        <v>235.2</v>
+        <v>234.6</v>
       </c>
       <c r="H68" t="n">
-        <v>52.5</v>
+        <v>50.2</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.4</v>
+        <v>-134.61</v>
       </c>
       <c r="K68" t="n">
-        <v>164.6</v>
+        <v>165.08</v>
       </c>
       <c r="L68" t="n">
-        <v>197.09</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:01:48</t>
+          <t>07:56:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="F69" t="n">
-        <v>12.95</v>
+        <v>12.39</v>
       </c>
       <c r="G69" t="n">
-        <v>236.8</v>
+        <v>243</v>
       </c>
       <c r="H69" t="n">
-        <v>52.3</v>
+        <v>51</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-151.69</v>
+        <v>-169.94</v>
       </c>
       <c r="K69" t="n">
-        <v>136.03</v>
+        <v>122.31</v>
       </c>
       <c r="L69" t="n">
-        <v>203.75</v>
+        <v>209.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:03:10</t>
+          <t>07:57:44</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="F70" t="n">
-        <v>11.76</v>
+        <v>12.51</v>
       </c>
       <c r="G70" t="n">
-        <v>245.4</v>
+        <v>219.1</v>
       </c>
       <c r="H70" t="n">
-        <v>50.6</v>
+        <v>55.3</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-129.34</v>
+        <v>-164.52</v>
       </c>
       <c r="K70" t="n">
-        <v>1.65</v>
+        <v>-35.96</v>
       </c>
       <c r="L70" t="n">
-        <v>129.35</v>
+        <v>168.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:08:17</t>
+          <t>08:02:25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,25 +3019,25 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="F71" t="n">
-        <v>12.28</v>
+        <v>13.4</v>
       </c>
       <c r="G71" t="n">
-        <v>234.5</v>
+        <v>229.6</v>
       </c>
       <c r="H71" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.35</v>
+        <v>-106.81</v>
       </c>
       <c r="K71" t="n">
-        <v>182.37</v>
+        <v>148.6</v>
       </c>
       <c r="L71" t="n">
         <v>183.01</v>
@@ -3046,7 +3046,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:09:22</t>
+          <t>08:04:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="F72" t="n">
-        <v>12.61</v>
+        <v>12.27</v>
       </c>
       <c r="G72" t="n">
-        <v>236</v>
+        <v>236.2</v>
       </c>
       <c r="H72" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>31.14</v>
+        <v>-0.46</v>
       </c>
       <c r="K72" t="n">
-        <v>-186.85</v>
+        <v>-226.61</v>
       </c>
       <c r="L72" t="n">
-        <v>189.43</v>
+        <v>226.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:10:27</t>
+          <t>08:06:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="F73" t="n">
-        <v>11.74</v>
+        <v>13.4</v>
       </c>
       <c r="G73" t="n">
-        <v>227.5</v>
+        <v>218.9</v>
       </c>
       <c r="H73" t="n">
-        <v>56.3</v>
+        <v>46.3</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-160.16</v>
+        <v>-166.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-387.96</v>
+        <v>-393.8</v>
       </c>
       <c r="L73" t="n">
-        <v>419.72</v>
+        <v>427.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:22:20</t>
+          <t>08:19:08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="F74" t="n">
-        <v>12.87</v>
+        <v>14.6</v>
       </c>
       <c r="G74" t="n">
-        <v>235.7</v>
+        <v>241.4</v>
       </c>
       <c r="H74" t="n">
-        <v>54.3</v>
+        <v>50.5</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>56.85</v>
+        <v>65.62</v>
       </c>
       <c r="K74" t="n">
-        <v>12.23</v>
+        <v>13.74</v>
       </c>
       <c r="L74" t="n">
-        <v>58.15</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:24:26</t>
+          <t>08:20:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="F75" t="n">
-        <v>12.83</v>
+        <v>14.6</v>
       </c>
       <c r="G75" t="n">
-        <v>229.8</v>
+        <v>240.7</v>
       </c>
       <c r="H75" t="n">
-        <v>52.3</v>
+        <v>47.5</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.42</v>
+        <v>-32.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.74</v>
+        <v>-13.18</v>
       </c>
       <c r="L75" t="n">
-        <v>22.21</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:25:38</t>
+          <t>08:21:18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="F76" t="n">
-        <v>12.43</v>
+        <v>10.09</v>
       </c>
       <c r="G76" t="n">
-        <v>236</v>
+        <v>232.6</v>
       </c>
       <c r="H76" t="n">
-        <v>46.7</v>
+        <v>50.6</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>57.83</v>
+        <v>68.25</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.93</v>
+        <v>-52.98</v>
       </c>
       <c r="L76" t="n">
-        <v>72.63</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:31:49</t>
+          <t>08:26:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="F77" t="n">
-        <v>12.61</v>
+        <v>14.6</v>
       </c>
       <c r="G77" t="n">
-        <v>238.8</v>
+        <v>236.3</v>
       </c>
       <c r="H77" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.98999999999999</v>
+        <v>-75.08</v>
       </c>
       <c r="K77" t="n">
-        <v>19</v>
+        <v>15.91</v>
       </c>
       <c r="L77" t="n">
-        <v>73.48999999999999</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:33:29</t>
+          <t>08:27:56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="F78" t="n">
-        <v>11.86</v>
+        <v>14.1</v>
       </c>
       <c r="G78" t="n">
-        <v>248.9</v>
+        <v>221.3</v>
       </c>
       <c r="H78" t="n">
-        <v>50.4</v>
+        <v>57.1</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>41.7</v>
+        <v>44.58</v>
       </c>
       <c r="K78" t="n">
-        <v>-61.22</v>
+        <v>-72.62</v>
       </c>
       <c r="L78" t="n">
-        <v>74.08</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:35:11</t>
+          <t>08:29:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="F79" t="n">
-        <v>12.74</v>
+        <v>11.23</v>
       </c>
       <c r="G79" t="n">
-        <v>245.2</v>
+        <v>238.7</v>
       </c>
       <c r="H79" t="n">
-        <v>54.1</v>
+        <v>55.2</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-83.28</v>
+        <v>-93.68000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>3.27</v>
+        <v>1.68</v>
       </c>
       <c r="L79" t="n">
-        <v>83.34999999999999</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:40:45</t>
+          <t>08:34:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="F80" t="n">
-        <v>13.07</v>
+        <v>14.6</v>
       </c>
       <c r="G80" t="n">
-        <v>233.3</v>
+        <v>245.3</v>
       </c>
       <c r="H80" t="n">
-        <v>57.3</v>
+        <v>49.2</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>47.92</v>
+        <v>36.74</v>
       </c>
       <c r="K80" t="n">
-        <v>118.7</v>
+        <v>132.72</v>
       </c>
       <c r="L80" t="n">
-        <v>128.01</v>
+        <v>137.71</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:43:30</t>
+          <t>08:36:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="F81" t="n">
-        <v>12.64</v>
+        <v>14.6</v>
       </c>
       <c r="G81" t="n">
-        <v>237.1</v>
+        <v>236.7</v>
       </c>
       <c r="H81" t="n">
-        <v>53.6</v>
+        <v>51.2</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>17.56</v>
+        <v>1.34</v>
       </c>
       <c r="K81" t="n">
-        <v>-79.98999999999999</v>
+        <v>-102.75</v>
       </c>
       <c r="L81" t="n">
-        <v>81.89</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:44:37</t>
+          <t>08:37:23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="F82" t="n">
-        <v>12.78</v>
+        <v>7.7</v>
       </c>
       <c r="G82" t="n">
-        <v>241.9</v>
+        <v>239.5</v>
       </c>
       <c r="H82" t="n">
-        <v>38.1</v>
+        <v>53.6</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-75.83</v>
+        <v>-83.51000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.13</v>
+        <v>-17.08</v>
       </c>
       <c r="L82" t="n">
-        <v>75.83</v>
+        <v>85.23999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:48:52</t>
+          <t>08:41:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="F83" t="n">
-        <v>12.41</v>
+        <v>14.6</v>
       </c>
       <c r="G83" t="n">
-        <v>252.8</v>
+        <v>232.2</v>
       </c>
       <c r="H83" t="n">
-        <v>52.7</v>
+        <v>59</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>178.3</v>
+        <v>170.99</v>
       </c>
       <c r="K83" t="n">
-        <v>-23.35</v>
+        <v>-49.64</v>
       </c>
       <c r="L83" t="n">
-        <v>179.82</v>
+        <v>178.05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:50:09</t>
+          <t>08:44:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="F84" t="n">
-        <v>12.91</v>
+        <v>14.6</v>
       </c>
       <c r="G84" t="n">
-        <v>245.9</v>
+        <v>242.1</v>
       </c>
       <c r="H84" t="n">
-        <v>50.7</v>
+        <v>55.5</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>2.62</v>
+        <v>-25.56</v>
       </c>
       <c r="K84" t="n">
-        <v>-160.12</v>
+        <v>-167.89</v>
       </c>
       <c r="L84" t="n">
-        <v>160.14</v>
+        <v>169.83</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:52:23</t>
+          <t>08:46:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="F85" t="n">
-        <v>12.83</v>
+        <v>14.6</v>
       </c>
       <c r="G85" t="n">
-        <v>234.3</v>
+        <v>240.6</v>
       </c>
       <c r="H85" t="n">
-        <v>53</v>
+        <v>49.8</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>203.95</v>
+        <v>231.39</v>
       </c>
       <c r="K85" t="n">
-        <v>101.07</v>
+        <v>115.64</v>
       </c>
       <c r="L85" t="n">
-        <v>227.62</v>
+        <v>258.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:58:18</t>
+          <t>08:50:57</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="F86" t="n">
-        <v>11.81</v>
+        <v>13.8</v>
       </c>
       <c r="G86" t="n">
-        <v>229.1</v>
+        <v>220.3</v>
       </c>
       <c r="H86" t="n">
-        <v>49.6</v>
+        <v>47.2</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-133.61</v>
+        <v>-181.31</v>
       </c>
       <c r="K86" t="n">
-        <v>135.61</v>
+        <v>83.19</v>
       </c>
       <c r="L86" t="n">
-        <v>190.38</v>
+        <v>199.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:00:21</t>
+          <t>08:52:20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="F87" t="n">
-        <v>12.54</v>
+        <v>14.6</v>
       </c>
       <c r="G87" t="n">
-        <v>245</v>
+        <v>234.7</v>
       </c>
       <c r="H87" t="n">
-        <v>45.8</v>
+        <v>55.1</v>
       </c>
       <c r="I87" t="n">
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>144.5</v>
+        <v>165.26</v>
       </c>
       <c r="K87" t="n">
-        <v>163.46</v>
+        <v>189.53</v>
       </c>
       <c r="L87" t="n">
-        <v>218.17</v>
+        <v>251.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:02:45</t>
+          <t>08:53:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="F88" t="n">
-        <v>12.32</v>
+        <v>14.6</v>
       </c>
       <c r="G88" t="n">
-        <v>226</v>
+        <v>230.4</v>
       </c>
       <c r="H88" t="n">
-        <v>55.2</v>
+        <v>45.6</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-267.46</v>
+        <v>-306.81</v>
       </c>
       <c r="K88" t="n">
-        <v>-75.59</v>
+        <v>-98.47</v>
       </c>
       <c r="L88" t="n">
-        <v>277.94</v>
+        <v>322.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.42</v>
+        <v>-54.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.19</v>
+        <v>-39.48</v>
       </c>
       <c r="L14" t="n">
-        <v>72.06</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.4</v>
+        <v>-51.85</v>
       </c>
       <c r="K15" t="n">
-        <v>13.34</v>
+        <v>12.49</v>
       </c>
       <c r="L15" t="n">
-        <v>56.99</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="16">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-28.61</v>
+        <v>-27.95</v>
       </c>
       <c r="K17" t="n">
-        <v>94.63</v>
+        <v>92.47</v>
       </c>
       <c r="L17" t="n">
-        <v>98.86</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-90.19</v>
+        <v>-90.05</v>
       </c>
       <c r="K18" t="n">
-        <v>22.77</v>
+        <v>22.74</v>
       </c>
       <c r="L18" t="n">
-        <v>93.02</v>
+        <v>92.88</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>49.33</v>
+        <v>45</v>
       </c>
       <c r="K19" t="n">
-        <v>30.89</v>
+        <v>28.18</v>
       </c>
       <c r="L19" t="n">
-        <v>58.2</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-137.78</v>
+        <v>-140.3</v>
       </c>
       <c r="K20" t="n">
-        <v>-79.11</v>
+        <v>-80.55</v>
       </c>
       <c r="L20" t="n">
-        <v>158.88</v>
+        <v>161.78</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-38.75</v>
+        <v>-39.49</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.82</v>
+        <v>-3.89</v>
       </c>
       <c r="L21" t="n">
-        <v>38.94</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.34</v>
+        <v>-20.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-90.77</v>
+        <v>-82.84999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>93.48</v>
+        <v>85.31999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-175.42</v>
+        <v>-178.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-19.47</v>
+        <v>-19.86</v>
       </c>
       <c r="L23" t="n">
-        <v>176.5</v>
+        <v>180.08</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>119.13</v>
+        <v>116.7</v>
       </c>
       <c r="K24" t="n">
-        <v>-84.61</v>
+        <v>-82.88</v>
       </c>
       <c r="L24" t="n">
-        <v>146.12</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-159.79</v>
+        <v>-159.84</v>
       </c>
       <c r="K25" t="n">
-        <v>125.77</v>
+        <v>125.81</v>
       </c>
       <c r="L25" t="n">
-        <v>203.34</v>
+        <v>203.41</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-180.46</v>
+        <v>-165.3</v>
       </c>
       <c r="K26" t="n">
-        <v>159.86</v>
+        <v>146.43</v>
       </c>
       <c r="L26" t="n">
-        <v>241.08</v>
+        <v>220.83</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.47</v>
+        <v>-2.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-216.26</v>
+        <v>-205.27</v>
       </c>
       <c r="L27" t="n">
-        <v>216.27</v>
+        <v>205.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>7.03</v>
+        <v>6.59</v>
       </c>
       <c r="K28" t="n">
-        <v>215.57</v>
+        <v>201.81</v>
       </c>
       <c r="L28" t="n">
-        <v>215.69</v>
+        <v>201.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>30.68</v>
+        <v>29.33</v>
       </c>
       <c r="K29" t="n">
-        <v>-59.71</v>
+        <v>-57.1</v>
       </c>
       <c r="L29" t="n">
-        <v>67.13</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="30">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>34.48</v>
+        <v>35.1</v>
       </c>
       <c r="K31" t="n">
-        <v>-111.59</v>
+        <v>-113.58</v>
       </c>
       <c r="L31" t="n">
-        <v>116.79</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-67.73999999999999</v>
+        <v>-68.87</v>
       </c>
       <c r="K32" t="n">
-        <v>70.02</v>
+        <v>71.19</v>
       </c>
       <c r="L32" t="n">
-        <v>97.43000000000001</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-52.7</v>
+        <v>-53.46</v>
       </c>
       <c r="K33" t="n">
-        <v>70.84999999999999</v>
+        <v>71.87</v>
       </c>
       <c r="L33" t="n">
-        <v>88.3</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-74.69</v>
+        <v>-71.51000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>18.38</v>
+        <v>17.6</v>
       </c>
       <c r="L34" t="n">
-        <v>76.92</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.64</v>
+        <v>-77.81999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-50.52</v>
+        <v>-44.86</v>
       </c>
       <c r="L35" t="n">
-        <v>101.16</v>
+        <v>89.83</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>94.52</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>66.56</v>
+        <v>66.44</v>
       </c>
       <c r="L36" t="n">
-        <v>115.6</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>51.72</v>
+        <v>45.93</v>
       </c>
       <c r="K37" t="n">
-        <v>142.02</v>
+        <v>126.11</v>
       </c>
       <c r="L37" t="n">
-        <v>151.14</v>
+        <v>134.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>123.71</v>
+        <v>123.74</v>
       </c>
       <c r="K38" t="n">
-        <v>-37.83</v>
+        <v>-37.84</v>
       </c>
       <c r="L38" t="n">
-        <v>129.37</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-91.63</v>
+        <v>-83.70999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>118.94</v>
+        <v>108.67</v>
       </c>
       <c r="L39" t="n">
-        <v>150.14</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-166.92</v>
+        <v>-156.4</v>
       </c>
       <c r="K40" t="n">
-        <v>-135.12</v>
+        <v>-126.61</v>
       </c>
       <c r="L40" t="n">
-        <v>214.75</v>
+        <v>201.22</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>119.25</v>
+        <v>107.54</v>
       </c>
       <c r="K41" t="n">
-        <v>253.72</v>
+        <v>228.79</v>
       </c>
       <c r="L41" t="n">
-        <v>280.34</v>
+        <v>252.8</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-221.01</v>
+        <v>-203.14</v>
       </c>
       <c r="K42" t="n">
-        <v>280.68</v>
+        <v>257.98</v>
       </c>
       <c r="L42" t="n">
-        <v>357.25</v>
+        <v>328.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-264.44</v>
+        <v>-260.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-89.19</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>279.07</v>
+        <v>275.04</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.96</v>
+        <v>-2.84</v>
       </c>
       <c r="K44" t="n">
-        <v>54.93</v>
+        <v>52.63</v>
       </c>
       <c r="L44" t="n">
-        <v>55.01</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="K45" t="n">
-        <v>-95.12</v>
+        <v>-90.69</v>
       </c>
       <c r="L45" t="n">
-        <v>95.12</v>
+        <v>90.69</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>91.75</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>27.5</v>
+        <v>27.96</v>
       </c>
       <c r="L46" t="n">
-        <v>95.78</v>
+        <v>97.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-90.61</v>
+        <v>-82.61</v>
       </c>
       <c r="K47" t="n">
-        <v>12.74</v>
+        <v>11.61</v>
       </c>
       <c r="L47" t="n">
-        <v>91.5</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-49.11</v>
+        <v>-44.72</v>
       </c>
       <c r="K48" t="n">
-        <v>38.53</v>
+        <v>35.08</v>
       </c>
       <c r="L48" t="n">
-        <v>62.42</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>7.94</v>
+        <v>7.76</v>
       </c>
       <c r="K49" t="n">
-        <v>75.90000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="L49" t="n">
-        <v>76.31999999999999</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-138.3</v>
+        <v>-132.45</v>
       </c>
       <c r="K50" t="n">
-        <v>125.71</v>
+        <v>120.39</v>
       </c>
       <c r="L50" t="n">
-        <v>186.89</v>
+        <v>178.99</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="K51" t="n">
-        <v>192.95</v>
+        <v>184.77</v>
       </c>
       <c r="L51" t="n">
-        <v>192.95</v>
+        <v>184.77</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-158.95</v>
+        <v>-144.54</v>
       </c>
       <c r="K52" t="n">
-        <v>110.21</v>
+        <v>100.22</v>
       </c>
       <c r="L52" t="n">
-        <v>193.42</v>
+        <v>175.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-126.68</v>
+        <v>-124.25</v>
       </c>
       <c r="K53" t="n">
-        <v>60.7</v>
+        <v>59.53</v>
       </c>
       <c r="L53" t="n">
-        <v>140.47</v>
+        <v>137.77</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-108.69</v>
+        <v>-104.21</v>
       </c>
       <c r="K54" t="n">
-        <v>91.7</v>
+        <v>87.91</v>
       </c>
       <c r="L54" t="n">
-        <v>142.21</v>
+        <v>136.33</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-107.5</v>
+        <v>-107.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-140.91</v>
+        <v>-141.1</v>
       </c>
       <c r="L55" t="n">
-        <v>177.23</v>
+        <v>177.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>55.35</v>
+        <v>54.42</v>
       </c>
       <c r="K56" t="n">
-        <v>-213.7</v>
+        <v>-210.11</v>
       </c>
       <c r="L56" t="n">
-        <v>220.75</v>
+        <v>217.05</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-187.36</v>
+        <v>-191.96</v>
       </c>
       <c r="K57" t="n">
-        <v>82.56</v>
+        <v>84.59</v>
       </c>
       <c r="L57" t="n">
-        <v>204.74</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-383.81</v>
+        <v>-381.42</v>
       </c>
       <c r="K58" t="n">
-        <v>-195.29</v>
+        <v>-194.08</v>
       </c>
       <c r="L58" t="n">
-        <v>430.64</v>
+        <v>427.95</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-54.77</v>
+        <v>-53.46</v>
       </c>
       <c r="L59" t="n">
-        <v>55.45</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-62.8</v>
+        <v>-55.48</v>
       </c>
       <c r="K60" t="n">
-        <v>-17.43</v>
+        <v>-15.4</v>
       </c>
       <c r="L60" t="n">
-        <v>65.17</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="K61" t="n">
-        <v>76.88</v>
+        <v>71.55</v>
       </c>
       <c r="L61" t="n">
-        <v>76.92</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-48.35</v>
+        <v>-46.21</v>
       </c>
       <c r="K62" t="n">
-        <v>-86.05</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>98.7</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.9</v>
+        <v>-55.45</v>
       </c>
       <c r="L63" t="n">
-        <v>60.9</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>69.33</v>
+        <v>61.2</v>
       </c>
       <c r="K64" t="n">
-        <v>47.58</v>
+        <v>42.01</v>
       </c>
       <c r="L64" t="n">
-        <v>84.09</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.54</v>
+        <v>-7.69</v>
       </c>
       <c r="K65" t="n">
-        <v>-94.67</v>
+        <v>-96.48999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>94.97</v>
+        <v>96.79000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>121.02</v>
+        <v>120.77</v>
       </c>
       <c r="K66" t="n">
-        <v>87.54000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="L66" t="n">
-        <v>149.36</v>
+        <v>149.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-49.93</v>
+        <v>-47.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-161.33</v>
+        <v>-154.41</v>
       </c>
       <c r="L67" t="n">
-        <v>168.88</v>
+        <v>161.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-134.61</v>
+        <v>-119.71</v>
       </c>
       <c r="K68" t="n">
-        <v>165.08</v>
+        <v>146.8</v>
       </c>
       <c r="L68" t="n">
-        <v>213.01</v>
+        <v>189.42</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-169.94</v>
+        <v>-156.47</v>
       </c>
       <c r="K69" t="n">
-        <v>122.31</v>
+        <v>112.62</v>
       </c>
       <c r="L69" t="n">
-        <v>209.37</v>
+        <v>192.78</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-164.52</v>
+        <v>-161.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-35.96</v>
+        <v>-35.25</v>
       </c>
       <c r="L70" t="n">
-        <v>168.4</v>
+        <v>165.1</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-106.81</v>
+        <v>-106.31</v>
       </c>
       <c r="K71" t="n">
-        <v>148.6</v>
+        <v>147.9</v>
       </c>
       <c r="L71" t="n">
-        <v>183.01</v>
+        <v>182.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="K72" t="n">
-        <v>-226.61</v>
+        <v>-207.81</v>
       </c>
       <c r="L72" t="n">
-        <v>226.61</v>
+        <v>207.81</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-166.17</v>
+        <v>-156.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-393.8</v>
+        <v>-371</v>
       </c>
       <c r="L73" t="n">
-        <v>427.42</v>
+        <v>402.68</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>65.62</v>
+        <v>65.12</v>
       </c>
       <c r="K74" t="n">
-        <v>13.74</v>
+        <v>13.64</v>
       </c>
       <c r="L74" t="n">
-        <v>67.05</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-32.22</v>
+        <v>-30.74</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.18</v>
+        <v>-12.58</v>
       </c>
       <c r="L75" t="n">
-        <v>34.81</v>
+        <v>33.22</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>68.25</v>
+        <v>68.09</v>
       </c>
       <c r="K76" t="n">
-        <v>-52.98</v>
+        <v>-52.86</v>
       </c>
       <c r="L76" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-75.08</v>
+        <v>-66.23999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>15.91</v>
+        <v>14.03</v>
       </c>
       <c r="L77" t="n">
-        <v>76.75</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>44.58</v>
+        <v>41.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.62</v>
+        <v>-67.62</v>
       </c>
       <c r="L78" t="n">
-        <v>85.20999999999999</v>
+        <v>79.34</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-93.68000000000001</v>
+        <v>-93.41</v>
       </c>
       <c r="K79" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="L79" t="n">
-        <v>93.69</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>36.74</v>
+        <v>34.32</v>
       </c>
       <c r="K80" t="n">
-        <v>132.72</v>
+        <v>123.96</v>
       </c>
       <c r="L80" t="n">
-        <v>137.71</v>
+        <v>128.62</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="K81" t="n">
-        <v>-102.75</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>102.76</v>
+        <v>91.23999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-83.51000000000001</v>
+        <v>-76.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-17.08</v>
+        <v>-15.57</v>
       </c>
       <c r="L82" t="n">
-        <v>85.23999999999999</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>170.99</v>
+        <v>152.17</v>
       </c>
       <c r="K83" t="n">
-        <v>-49.64</v>
+        <v>-44.18</v>
       </c>
       <c r="L83" t="n">
-        <v>178.05</v>
+        <v>158.45</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-25.56</v>
+        <v>-22.9</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.89</v>
+        <v>-150.41</v>
       </c>
       <c r="L84" t="n">
-        <v>169.83</v>
+        <v>152.14</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>231.39</v>
+        <v>237.89</v>
       </c>
       <c r="K85" t="n">
-        <v>115.64</v>
+        <v>118.89</v>
       </c>
       <c r="L85" t="n">
-        <v>258.68</v>
+        <v>265.94</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-181.31</v>
+        <v>-163.43</v>
       </c>
       <c r="K86" t="n">
-        <v>83.19</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>199.48</v>
+        <v>179.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>165.26</v>
+        <v>156.3</v>
       </c>
       <c r="K87" t="n">
-        <v>189.53</v>
+        <v>179.25</v>
       </c>
       <c r="L87" t="n">
-        <v>251.45</v>
+        <v>237.82</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-306.81</v>
+        <v>-310.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-98.47</v>
+        <v>-99.81</v>
       </c>
       <c r="L88" t="n">
-        <v>322.23</v>
+        <v>326.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="F14" t="n">
-        <v>11.54</v>
+        <v>7.75</v>
       </c>
       <c r="G14" t="n">
-        <v>246</v>
+        <v>248.5</v>
       </c>
       <c r="H14" t="n">
-        <v>57.5</v>
+        <v>59.7</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-54.66</v>
+        <v>-4.55</v>
       </c>
       <c r="K14" t="n">
-        <v>-39.48</v>
+        <v>-38.41</v>
       </c>
       <c r="L14" t="n">
-        <v>67.43000000000001</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:13:33</t>
+          <t>05:14:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.31</v>
+        <v>3.39</v>
       </c>
       <c r="F15" t="n">
-        <v>8.75</v>
+        <v>10.29</v>
       </c>
       <c r="G15" t="n">
-        <v>247.8</v>
+        <v>237.8</v>
       </c>
       <c r="H15" t="n">
-        <v>52.1</v>
+        <v>30.8</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-51.85</v>
+        <v>-40.64</v>
       </c>
       <c r="K15" t="n">
-        <v>12.49</v>
+        <v>-12.62</v>
       </c>
       <c r="L15" t="n">
-        <v>53.34</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:14:39</t>
+          <t>05:17:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="F16" t="n">
-        <v>9.890000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>238.6</v>
+        <v>222.4</v>
       </c>
       <c r="H16" t="n">
-        <v>55.7</v>
+        <v>31.8</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-62.91</v>
+        <v>-16.12</v>
       </c>
       <c r="K16" t="n">
-        <v>52.54</v>
+        <v>-39.16</v>
       </c>
       <c r="L16" t="n">
-        <v>81.97</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:20:22</t>
+          <t>05:23:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="F17" t="n">
-        <v>11.19</v>
+        <v>11.27</v>
       </c>
       <c r="G17" t="n">
-        <v>240</v>
+        <v>243.9</v>
       </c>
       <c r="H17" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-27.95</v>
+        <v>-50.96</v>
       </c>
       <c r="K17" t="n">
-        <v>92.47</v>
+        <v>-56.63</v>
       </c>
       <c r="L17" t="n">
-        <v>96.59999999999999</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:22:12</t>
+          <t>05:25:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="F18" t="n">
-        <v>9.970000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="G18" t="n">
-        <v>230</v>
+        <v>232.2</v>
       </c>
       <c r="H18" t="n">
-        <v>49.5</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-90.05</v>
+        <v>-47.85</v>
       </c>
       <c r="K18" t="n">
-        <v>22.74</v>
+        <v>-58.63</v>
       </c>
       <c r="L18" t="n">
-        <v>92.88</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:23:32</t>
+          <t>05:27:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="F19" t="n">
-        <v>10.58</v>
+        <v>10.13</v>
       </c>
       <c r="G19" t="n">
-        <v>236.2</v>
+        <v>233.3</v>
       </c>
       <c r="H19" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>45</v>
+        <v>-24.39</v>
       </c>
       <c r="K19" t="n">
-        <v>28.18</v>
+        <v>90.86</v>
       </c>
       <c r="L19" t="n">
-        <v>53.09</v>
+        <v>94.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:27:41</t>
+          <t>05:32:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.04</v>
+        <v>4.11</v>
       </c>
       <c r="F20" t="n">
-        <v>12.58</v>
+        <v>10.62</v>
       </c>
       <c r="G20" t="n">
-        <v>237.7</v>
+        <v>234</v>
       </c>
       <c r="H20" t="n">
-        <v>61.4</v>
+        <v>62.4</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.3</v>
+        <v>-64.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-80.55</v>
+        <v>105.96</v>
       </c>
       <c r="L20" t="n">
-        <v>161.78</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:29:33</t>
+          <t>05:33:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="F21" t="n">
-        <v>11.89</v>
+        <v>10.62</v>
       </c>
       <c r="G21" t="n">
-        <v>230</v>
+        <v>220.9</v>
       </c>
       <c r="H21" t="n">
-        <v>54.8</v>
+        <v>30.3</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-39.49</v>
+        <v>-50.83</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.89</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>39.68</v>
+        <v>82.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:31:06</t>
+          <t>05:35:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="F22" t="n">
-        <v>8.01</v>
+        <v>11.96</v>
       </c>
       <c r="G22" t="n">
-        <v>242</v>
+        <v>234.8</v>
       </c>
       <c r="H22" t="n">
-        <v>52.9</v>
+        <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-20.39</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-82.84999999999999</v>
+        <v>60.54</v>
       </c>
       <c r="L22" t="n">
-        <v>85.31999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:34:16</t>
+          <t>05:41:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.81</v>
+        <v>3.57</v>
       </c>
       <c r="F23" t="n">
-        <v>10.78</v>
+        <v>11.97</v>
       </c>
       <c r="G23" t="n">
-        <v>225.7</v>
+        <v>249.3</v>
       </c>
       <c r="H23" t="n">
-        <v>54.2</v>
+        <v>20.4</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-178.98</v>
+        <v>88.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-19.86</v>
+        <v>-116.31</v>
       </c>
       <c r="L23" t="n">
-        <v>180.08</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:35:52</t>
+          <t>05:42:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.33</v>
+        <v>3.68</v>
       </c>
       <c r="F24" t="n">
-        <v>8.4</v>
+        <v>14.02</v>
       </c>
       <c r="G24" t="n">
-        <v>228.7</v>
+        <v>242.3</v>
       </c>
       <c r="H24" t="n">
-        <v>51.2</v>
+        <v>45.6</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>116.7</v>
+        <v>93.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.88</v>
+        <v>-192.76</v>
       </c>
       <c r="L24" t="n">
-        <v>143.14</v>
+        <v>214.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:38:13</t>
+          <t>05:44:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="F25" t="n">
-        <v>11.52</v>
+        <v>10.67</v>
       </c>
       <c r="G25" t="n">
-        <v>246.2</v>
+        <v>226.5</v>
       </c>
       <c r="H25" t="n">
-        <v>54.3</v>
+        <v>40</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-159.84</v>
+        <v>27.9</v>
       </c>
       <c r="K25" t="n">
-        <v>125.81</v>
+        <v>-181.87</v>
       </c>
       <c r="L25" t="n">
-        <v>203.41</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:43:19</t>
+          <t>05:48:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.64</v>
+        <v>4.11</v>
       </c>
       <c r="F26" t="n">
-        <v>9.25</v>
+        <v>11.44</v>
       </c>
       <c r="G26" t="n">
-        <v>236.4</v>
+        <v>249.6</v>
       </c>
       <c r="H26" t="n">
-        <v>52.4</v>
+        <v>26</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-165.3</v>
+        <v>179.12</v>
       </c>
       <c r="K26" t="n">
-        <v>146.43</v>
+        <v>-199.18</v>
       </c>
       <c r="L26" t="n">
-        <v>220.83</v>
+        <v>267.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:45:03</t>
+          <t>05:51:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="F27" t="n">
-        <v>14.6</v>
+        <v>10.21</v>
       </c>
       <c r="G27" t="n">
-        <v>229.5</v>
+        <v>245.6</v>
       </c>
       <c r="H27" t="n">
-        <v>47.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.34</v>
+        <v>196.43</v>
       </c>
       <c r="K27" t="n">
-        <v>-205.27</v>
+        <v>165.67</v>
       </c>
       <c r="L27" t="n">
-        <v>205.28</v>
+        <v>256.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:47:47</t>
+          <t>05:52:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.24</v>
+        <v>4.24</v>
       </c>
       <c r="F28" t="n">
-        <v>9.68</v>
+        <v>14.6</v>
       </c>
       <c r="G28" t="n">
-        <v>238.4</v>
+        <v>242.9</v>
       </c>
       <c r="H28" t="n">
-        <v>55</v>
+        <v>90.3</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>6.59</v>
+        <v>-236.82</v>
       </c>
       <c r="K28" t="n">
-        <v>201.81</v>
+        <v>61.73</v>
       </c>
       <c r="L28" t="n">
-        <v>201.92</v>
+        <v>244.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:59:07</t>
+          <t>06:04:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="F29" t="n">
-        <v>10.4</v>
+        <v>7.89</v>
       </c>
       <c r="G29" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H29" t="n">
-        <v>48.6</v>
+        <v>21.9</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>29.33</v>
+        <v>43.01</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.1</v>
+        <v>-42.48</v>
       </c>
       <c r="L29" t="n">
-        <v>64.19</v>
+        <v>60.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:00:23</t>
+          <t>06:05:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.11</v>
+        <v>3.72</v>
       </c>
       <c r="F30" t="n">
-        <v>10.37</v>
+        <v>14.6</v>
       </c>
       <c r="G30" t="n">
-        <v>245.5</v>
+        <v>233.6</v>
       </c>
       <c r="H30" t="n">
-        <v>52</v>
+        <v>13.8</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>32.3</v>
+        <v>-41.29</v>
       </c>
       <c r="K30" t="n">
-        <v>-48.33</v>
+        <v>11.28</v>
       </c>
       <c r="L30" t="n">
-        <v>58.13</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:01:41</t>
+          <t>06:07:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="F31" t="n">
-        <v>13.52</v>
+        <v>13.4</v>
       </c>
       <c r="G31" t="n">
-        <v>243.9</v>
+        <v>228</v>
       </c>
       <c r="H31" t="n">
-        <v>60.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>35.1</v>
+        <v>69.17</v>
       </c>
       <c r="K31" t="n">
-        <v>-113.58</v>
+        <v>0.99</v>
       </c>
       <c r="L31" t="n">
-        <v>118.88</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:04:58</t>
+          <t>06:12:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="F32" t="n">
-        <v>12.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>230.5</v>
+        <v>227.9</v>
       </c>
       <c r="H32" t="n">
-        <v>51.4</v>
+        <v>50.3</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.87</v>
+        <v>-84.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>71.19</v>
+        <v>-63.79</v>
       </c>
       <c r="L32" t="n">
-        <v>99.05</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:06:46</t>
+          <t>06:13:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.34</v>
+        <v>3.28</v>
       </c>
       <c r="F33" t="n">
-        <v>11.74</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>229.9</v>
+        <v>242.3</v>
       </c>
       <c r="H33" t="n">
-        <v>48.6</v>
+        <v>19.5</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-53.46</v>
+        <v>-21.7</v>
       </c>
       <c r="K33" t="n">
-        <v>71.87</v>
+        <v>44.88</v>
       </c>
       <c r="L33" t="n">
-        <v>89.56999999999999</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:14:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="F34" t="n">
-        <v>13.24</v>
+        <v>11.18</v>
       </c>
       <c r="G34" t="n">
-        <v>247.8</v>
+        <v>243.7</v>
       </c>
       <c r="H34" t="n">
-        <v>52.7</v>
+        <v>44.4</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-71.51000000000001</v>
+        <v>50.58</v>
       </c>
       <c r="K34" t="n">
-        <v>17.6</v>
+        <v>21.08</v>
       </c>
       <c r="L34" t="n">
-        <v>73.65000000000001</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:13:31</t>
+          <t>06:19:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.84</v>
+        <v>3.43</v>
       </c>
       <c r="F35" t="n">
-        <v>9.960000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="G35" t="n">
-        <v>233.9</v>
+        <v>231.6</v>
       </c>
       <c r="H35" t="n">
-        <v>51.3</v>
+        <v>6.1</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-77.81999999999999</v>
+        <v>-87.73999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-44.86</v>
+        <v>-37.96</v>
       </c>
       <c r="L35" t="n">
-        <v>89.83</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:15:07</t>
+          <t>06:21:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="F36" t="n">
-        <v>14.6</v>
+        <v>7.12</v>
       </c>
       <c r="G36" t="n">
-        <v>233.9</v>
+        <v>251.9</v>
       </c>
       <c r="H36" t="n">
-        <v>56.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>94.34999999999999</v>
+        <v>-70.19</v>
       </c>
       <c r="K36" t="n">
-        <v>66.44</v>
+        <v>95.91</v>
       </c>
       <c r="L36" t="n">
-        <v>115.4</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:16:21</t>
+          <t>06:21:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="F37" t="n">
-        <v>13.05</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>238.2</v>
+        <v>243.9</v>
       </c>
       <c r="H37" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>45.93</v>
+        <v>29.83</v>
       </c>
       <c r="K37" t="n">
-        <v>126.11</v>
+        <v>-80.33</v>
       </c>
       <c r="L37" t="n">
-        <v>134.22</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:19:55</t>
+          <t>06:25:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="F38" t="n">
-        <v>7.96</v>
+        <v>10.52</v>
       </c>
       <c r="G38" t="n">
-        <v>238.4</v>
+        <v>225.7</v>
       </c>
       <c r="H38" t="n">
-        <v>57.5</v>
+        <v>19.6</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>123.74</v>
+        <v>160.28</v>
       </c>
       <c r="K38" t="n">
-        <v>-37.84</v>
+        <v>-181.82</v>
       </c>
       <c r="L38" t="n">
-        <v>129.4</v>
+        <v>242.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:21:55</t>
+          <t>06:26:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="F39" t="n">
-        <v>14.17</v>
+        <v>8.34</v>
       </c>
       <c r="G39" t="n">
-        <v>232.6</v>
+        <v>250.2</v>
       </c>
       <c r="H39" t="n">
-        <v>54.7</v>
+        <v>37.8</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-83.70999999999999</v>
+        <v>-123.35</v>
       </c>
       <c r="K39" t="n">
-        <v>108.67</v>
+        <v>-10.55</v>
       </c>
       <c r="L39" t="n">
-        <v>137.18</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:23:57</t>
+          <t>06:29:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="F40" t="n">
-        <v>13.71</v>
+        <v>6.58</v>
       </c>
       <c r="G40" t="n">
-        <v>232.7</v>
+        <v>237</v>
       </c>
       <c r="H40" t="n">
-        <v>47.7</v>
+        <v>63.4</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-156.4</v>
+        <v>-59.88</v>
       </c>
       <c r="K40" t="n">
-        <v>-126.61</v>
+        <v>-110.41</v>
       </c>
       <c r="L40" t="n">
-        <v>201.22</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:27:57</t>
+          <t>06:34:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.43</v>
+        <v>4.11</v>
       </c>
       <c r="F41" t="n">
-        <v>14.6</v>
+        <v>11.77</v>
       </c>
       <c r="G41" t="n">
-        <v>236.8</v>
+        <v>249</v>
       </c>
       <c r="H41" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>107.54</v>
+        <v>-212.93</v>
       </c>
       <c r="K41" t="n">
-        <v>228.79</v>
+        <v>110.85</v>
       </c>
       <c r="L41" t="n">
-        <v>252.8</v>
+        <v>240.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:29:29</t>
+          <t>06:36:39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="F42" t="n">
-        <v>13.66</v>
+        <v>10.89</v>
       </c>
       <c r="G42" t="n">
-        <v>235.4</v>
+        <v>236.9</v>
       </c>
       <c r="H42" t="n">
-        <v>48.5</v>
+        <v>57.7</v>
       </c>
       <c r="I42" t="n">
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-203.14</v>
+        <v>-13.47</v>
       </c>
       <c r="K42" t="n">
-        <v>257.98</v>
+        <v>330.74</v>
       </c>
       <c r="L42" t="n">
-        <v>328.36</v>
+        <v>331.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:31:00</t>
+          <t>06:37:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="F43" t="n">
-        <v>12.77</v>
+        <v>10.92</v>
       </c>
       <c r="G43" t="n">
-        <v>238.6</v>
+        <v>253.4</v>
       </c>
       <c r="H43" t="n">
-        <v>49.4</v>
+        <v>34.1</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-260.62</v>
+        <v>-199.13</v>
       </c>
       <c r="K43" t="n">
-        <v>-87.90000000000001</v>
+        <v>339.03</v>
       </c>
       <c r="L43" t="n">
-        <v>275.04</v>
+        <v>393.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:42:27</t>
+          <t>06:48:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="F44" t="n">
-        <v>7.99</v>
+        <v>12.3</v>
       </c>
       <c r="G44" t="n">
-        <v>241.2</v>
+        <v>233.4</v>
       </c>
       <c r="H44" t="n">
-        <v>58.3</v>
+        <v>55.2</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.84</v>
+        <v>-55.92</v>
       </c>
       <c r="K44" t="n">
-        <v>52.63</v>
+        <v>-12.63</v>
       </c>
       <c r="L44" t="n">
-        <v>52.7</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:44:23</t>
+          <t>06:49:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.34</v>
+        <v>3.7</v>
       </c>
       <c r="F45" t="n">
-        <v>14.6</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>243.6</v>
+        <v>252.6</v>
       </c>
       <c r="H45" t="n">
-        <v>54</v>
+        <v>52.8</v>
       </c>
       <c r="I45" t="n">
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.35</v>
+        <v>-50.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-90.69</v>
+        <v>-21.31</v>
       </c>
       <c r="L45" t="n">
-        <v>90.69</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:45:52</t>
+          <t>06:51:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.82</v>
+        <v>4.06</v>
       </c>
       <c r="F46" t="n">
-        <v>11.41</v>
+        <v>14.42</v>
       </c>
       <c r="G46" t="n">
-        <v>242.1</v>
+        <v>232.3</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>30.5</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>93.29000000000001</v>
+        <v>-35.36</v>
       </c>
       <c r="K46" t="n">
-        <v>27.96</v>
+        <v>-41.9</v>
       </c>
       <c r="L46" t="n">
-        <v>97.39</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:49:21</t>
+          <t>06:55:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>13.15</v>
+        <v>13.44</v>
       </c>
       <c r="G47" t="n">
-        <v>255.9</v>
+        <v>234.2</v>
       </c>
       <c r="H47" t="n">
-        <v>47.6</v>
+        <v>59.3</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-82.61</v>
+        <v>-56.71</v>
       </c>
       <c r="K47" t="n">
-        <v>11.61</v>
+        <v>-72.86</v>
       </c>
       <c r="L47" t="n">
-        <v>83.42</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:51:32</t>
+          <t>06:58:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="F48" t="n">
-        <v>8.09</v>
+        <v>12.16</v>
       </c>
       <c r="G48" t="n">
-        <v>238.4</v>
+        <v>237.4</v>
       </c>
       <c r="H48" t="n">
-        <v>46.8</v>
+        <v>60.6</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-44.72</v>
+        <v>-95.78</v>
       </c>
       <c r="K48" t="n">
-        <v>35.08</v>
+        <v>12.36</v>
       </c>
       <c r="L48" t="n">
-        <v>56.84</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:53:25</t>
+          <t>07:00:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="F49" t="n">
-        <v>13.31</v>
+        <v>13.33</v>
       </c>
       <c r="G49" t="n">
-        <v>228</v>
+        <v>229.1</v>
       </c>
       <c r="H49" t="n">
-        <v>49</v>
+        <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>7.76</v>
+        <v>-75.52</v>
       </c>
       <c r="K49" t="n">
-        <v>74.19</v>
+        <v>-70.70999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>74.59</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:59:32</t>
+          <t>07:05:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.59</v>
+        <v>4.11</v>
       </c>
       <c r="F50" t="n">
-        <v>11.63</v>
+        <v>12.76</v>
       </c>
       <c r="G50" t="n">
-        <v>239.4</v>
+        <v>237.4</v>
       </c>
       <c r="H50" t="n">
-        <v>46.1</v>
+        <v>57.5</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-132.45</v>
+        <v>-93.97</v>
       </c>
       <c r="K50" t="n">
-        <v>120.39</v>
+        <v>-94.73</v>
       </c>
       <c r="L50" t="n">
-        <v>178.99</v>
+        <v>133.43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:00:51</t>
+          <t>07:06:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.67</v>
+        <v>4.48</v>
       </c>
       <c r="F51" t="n">
-        <v>11.96</v>
+        <v>14.08</v>
       </c>
       <c r="G51" t="n">
-        <v>240.5</v>
+        <v>235.5</v>
       </c>
       <c r="H51" t="n">
-        <v>50.5</v>
+        <v>47.8</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>0.58</v>
+        <v>-10.55</v>
       </c>
       <c r="K51" t="n">
-        <v>184.77</v>
+        <v>-164.82</v>
       </c>
       <c r="L51" t="n">
-        <v>184.77</v>
+        <v>165.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:01:31</t>
+          <t>07:07:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="F52" t="n">
-        <v>14.6</v>
+        <v>12.33</v>
       </c>
       <c r="G52" t="n">
-        <v>242.5</v>
+        <v>237.5</v>
       </c>
       <c r="H52" t="n">
-        <v>52.6</v>
+        <v>43.4</v>
       </c>
       <c r="I52" t="n">
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-144.54</v>
+        <v>-129.69</v>
       </c>
       <c r="K52" t="n">
-        <v>100.22</v>
+        <v>-129.81</v>
       </c>
       <c r="L52" t="n">
-        <v>175.89</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:06:13</t>
+          <t>07:12:07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="F53" t="n">
-        <v>14.17</v>
+        <v>14.6</v>
       </c>
       <c r="G53" t="n">
-        <v>232.4</v>
+        <v>230.3</v>
       </c>
       <c r="H53" t="n">
-        <v>55.3</v>
+        <v>69</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-124.25</v>
+        <v>-148.92</v>
       </c>
       <c r="K53" t="n">
-        <v>59.53</v>
+        <v>211.78</v>
       </c>
       <c r="L53" t="n">
-        <v>137.77</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:07:54</t>
+          <t>07:13:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.57</v>
+        <v>4.4</v>
       </c>
       <c r="F54" t="n">
-        <v>10.85</v>
+        <v>9.84</v>
       </c>
       <c r="G54" t="n">
-        <v>231.8</v>
+        <v>240</v>
       </c>
       <c r="H54" t="n">
-        <v>48.9</v>
+        <v>24.4</v>
       </c>
       <c r="I54" t="n">
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-104.21</v>
+        <v>3.74</v>
       </c>
       <c r="K54" t="n">
-        <v>87.91</v>
+        <v>-342.26</v>
       </c>
       <c r="L54" t="n">
-        <v>136.33</v>
+        <v>342.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:10:06</t>
+          <t>07:16:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.4</v>
+        <v>3.73</v>
       </c>
       <c r="F55" t="n">
-        <v>13.27</v>
+        <v>10.74</v>
       </c>
       <c r="G55" t="n">
-        <v>227.3</v>
+        <v>231.4</v>
       </c>
       <c r="H55" t="n">
-        <v>45.4</v>
+        <v>27.5</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-107.64</v>
+        <v>-136.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-141.1</v>
+        <v>-122.01</v>
       </c>
       <c r="L55" t="n">
-        <v>177.47</v>
+        <v>182.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:13:41</t>
+          <t>07:21:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="F56" t="n">
-        <v>13.65</v>
+        <v>13.01</v>
       </c>
       <c r="G56" t="n">
-        <v>245.9</v>
+        <v>239</v>
       </c>
       <c r="H56" t="n">
-        <v>52</v>
+        <v>28.8</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>54.42</v>
+        <v>76.81</v>
       </c>
       <c r="K56" t="n">
-        <v>-210.11</v>
+        <v>-276.77</v>
       </c>
       <c r="L56" t="n">
-        <v>217.05</v>
+        <v>287.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:16:05</t>
+          <t>07:22:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.86</v>
+        <v>3.79</v>
       </c>
       <c r="F57" t="n">
-        <v>11.66</v>
+        <v>13.43</v>
       </c>
       <c r="G57" t="n">
-        <v>238.3</v>
+        <v>225.4</v>
       </c>
       <c r="H57" t="n">
-        <v>47.5</v>
+        <v>37.4</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-191.96</v>
+        <v>-162.4</v>
       </c>
       <c r="K57" t="n">
-        <v>84.59</v>
+        <v>-129.39</v>
       </c>
       <c r="L57" t="n">
-        <v>209.77</v>
+        <v>207.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:17:28</t>
+          <t>07:23:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.43</v>
+        <v>4.34</v>
       </c>
       <c r="F58" t="n">
-        <v>13.23</v>
+        <v>10.88</v>
       </c>
       <c r="G58" t="n">
-        <v>236</v>
+        <v>230.8</v>
       </c>
       <c r="H58" t="n">
-        <v>49</v>
+        <v>68.5</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-381.42</v>
+        <v>135.5</v>
       </c>
       <c r="K58" t="n">
-        <v>-194.08</v>
+        <v>158.6</v>
       </c>
       <c r="L58" t="n">
-        <v>427.95</v>
+        <v>208.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:29:59</t>
+          <t>07:32:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="F59" t="n">
-        <v>14.02</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>225.3</v>
+        <v>250.7</v>
       </c>
       <c r="H59" t="n">
-        <v>49.8</v>
+        <v>18</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.42</v>
+        <v>-63.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-53.46</v>
+        <v>24.27</v>
       </c>
       <c r="L59" t="n">
-        <v>54.12</v>
+        <v>67.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:31:28</t>
+          <t>07:33:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.52</v>
+        <v>4.28</v>
       </c>
       <c r="F60" t="n">
-        <v>14.6</v>
+        <v>11.84</v>
       </c>
       <c r="G60" t="n">
-        <v>244.8</v>
+        <v>243.1</v>
       </c>
       <c r="H60" t="n">
-        <v>52.3</v>
+        <v>48.2</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-55.48</v>
+        <v>-54.77</v>
       </c>
       <c r="K60" t="n">
-        <v>-15.4</v>
+        <v>12.81</v>
       </c>
       <c r="L60" t="n">
-        <v>57.58</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:33:32</t>
+          <t>07:36:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="F61" t="n">
-        <v>14.41</v>
+        <v>10.19</v>
       </c>
       <c r="G61" t="n">
-        <v>245.5</v>
+        <v>244.8</v>
       </c>
       <c r="H61" t="n">
-        <v>58.2</v>
+        <v>78.3</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>2.15</v>
+        <v>-2.12</v>
       </c>
       <c r="K61" t="n">
-        <v>71.55</v>
+        <v>74.88</v>
       </c>
       <c r="L61" t="n">
-        <v>71.59</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:39:03</t>
+          <t>07:39:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.81</v>
+        <v>4.25</v>
       </c>
       <c r="F62" t="n">
-        <v>12.84</v>
+        <v>14.24</v>
       </c>
       <c r="G62" t="n">
-        <v>241.9</v>
+        <v>242.7</v>
       </c>
       <c r="H62" t="n">
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-46.21</v>
+        <v>-76.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-82.23999999999999</v>
+        <v>-81.36</v>
       </c>
       <c r="L62" t="n">
-        <v>94.33</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:40:01</t>
+          <t>07:41:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.81</v>
+        <v>4.49</v>
       </c>
       <c r="F63" t="n">
-        <v>10.63</v>
+        <v>14.6</v>
       </c>
       <c r="G63" t="n">
-        <v>233.5</v>
+        <v>249.5</v>
       </c>
       <c r="H63" t="n">
-        <v>52.2</v>
+        <v>66.2</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.26</v>
+        <v>-68.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-55.45</v>
+        <v>-65.47</v>
       </c>
       <c r="L63" t="n">
-        <v>55.45</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:42:08</t>
+          <t>07:43:22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.74</v>
+        <v>4.52</v>
       </c>
       <c r="F64" t="n">
-        <v>14.6</v>
+        <v>10.56</v>
       </c>
       <c r="G64" t="n">
-        <v>233.2</v>
+        <v>244.7</v>
       </c>
       <c r="H64" t="n">
-        <v>51.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>61.2</v>
+        <v>21.6</v>
       </c>
       <c r="K64" t="n">
-        <v>42.01</v>
+        <v>-93.87</v>
       </c>
       <c r="L64" t="n">
-        <v>74.23</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:45:39</t>
+          <t>07:49:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.46</v>
+        <v>4.25</v>
       </c>
       <c r="F65" t="n">
-        <v>9</v>
+        <v>14.6</v>
       </c>
       <c r="G65" t="n">
-        <v>244.3</v>
+        <v>224.5</v>
       </c>
       <c r="H65" t="n">
-        <v>44.7</v>
+        <v>35.9</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.69</v>
+        <v>-140.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-96.48999999999999</v>
+        <v>-63.81</v>
       </c>
       <c r="L65" t="n">
-        <v>96.79000000000001</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:47:41</t>
+          <t>07:51:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.56</v>
+        <v>3.47</v>
       </c>
       <c r="F66" t="n">
-        <v>12.13</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>224.8</v>
+        <v>256.1</v>
       </c>
       <c r="H66" t="n">
-        <v>46.8</v>
+        <v>10.9</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>120.77</v>
+        <v>-75.29000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>87.36</v>
+        <v>33.43</v>
       </c>
       <c r="L66" t="n">
-        <v>149.06</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:48:54</t>
+          <t>07:52:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.02</v>
+        <v>4.45</v>
       </c>
       <c r="F67" t="n">
-        <v>11.12</v>
+        <v>14.6</v>
       </c>
       <c r="G67" t="n">
-        <v>249.1</v>
+        <v>251.5</v>
       </c>
       <c r="H67" t="n">
-        <v>51.4</v>
+        <v>27.4</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-47.78</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-154.41</v>
+        <v>-137.72</v>
       </c>
       <c r="L67" t="n">
-        <v>161.63</v>
+        <v>137.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:54:40</t>
+          <t>07:56:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.62</v>
+        <v>5.07</v>
       </c>
       <c r="F68" t="n">
-        <v>12.32</v>
+        <v>14.6</v>
       </c>
       <c r="G68" t="n">
-        <v>234.6</v>
+        <v>226.6</v>
       </c>
       <c r="H68" t="n">
-        <v>50.2</v>
+        <v>26.3</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-119.71</v>
+        <v>293.08</v>
       </c>
       <c r="K68" t="n">
-        <v>146.8</v>
+        <v>38.63</v>
       </c>
       <c r="L68" t="n">
-        <v>189.42</v>
+        <v>295.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:56:38</t>
+          <t>07:58:12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.8</v>
+        <v>4.39</v>
       </c>
       <c r="F69" t="n">
-        <v>12.39</v>
+        <v>14.6</v>
       </c>
       <c r="G69" t="n">
-        <v>243</v>
+        <v>228.5</v>
       </c>
       <c r="H69" t="n">
-        <v>51</v>
+        <v>55.2</v>
       </c>
       <c r="I69" t="n">
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-156.47</v>
+        <v>-212.66</v>
       </c>
       <c r="K69" t="n">
-        <v>112.62</v>
+        <v>102.68</v>
       </c>
       <c r="L69" t="n">
-        <v>192.78</v>
+        <v>236.16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:57:44</t>
+          <t>07:58:59</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.96</v>
+        <v>4.43</v>
       </c>
       <c r="F70" t="n">
-        <v>12.51</v>
+        <v>14.4</v>
       </c>
       <c r="G70" t="n">
-        <v>219.1</v>
+        <v>243.6</v>
       </c>
       <c r="H70" t="n">
-        <v>55.3</v>
+        <v>58</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-161.3</v>
+        <v>-344.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-35.25</v>
+        <v>44.91</v>
       </c>
       <c r="L70" t="n">
-        <v>165.1</v>
+        <v>347.79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:02:25</t>
+          <t>08:03:42</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="F71" t="n">
-        <v>13.4</v>
+        <v>10.59</v>
       </c>
       <c r="G71" t="n">
-        <v>229.6</v>
+        <v>218.4</v>
       </c>
       <c r="H71" t="n">
-        <v>49.9</v>
+        <v>61.7</v>
       </c>
       <c r="I71" t="n">
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-106.31</v>
+        <v>-218.98</v>
       </c>
       <c r="K71" t="n">
-        <v>147.9</v>
+        <v>-295.57</v>
       </c>
       <c r="L71" t="n">
-        <v>182.14</v>
+        <v>367.85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:04:44</t>
+          <t>08:05:52</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.79</v>
+        <v>3.53</v>
       </c>
       <c r="F72" t="n">
-        <v>12.27</v>
+        <v>14.32</v>
       </c>
       <c r="G72" t="n">
-        <v>236.2</v>
+        <v>234</v>
       </c>
       <c r="H72" t="n">
-        <v>50.6</v>
+        <v>64.2</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.42</v>
+        <v>-145.76</v>
       </c>
       <c r="K72" t="n">
-        <v>-207.81</v>
+        <v>-224.17</v>
       </c>
       <c r="L72" t="n">
-        <v>207.81</v>
+        <v>267.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:06:50</t>
+          <t>08:06:52</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="F73" t="n">
-        <v>13.4</v>
+        <v>14.6</v>
       </c>
       <c r="G73" t="n">
-        <v>218.9</v>
+        <v>242.5</v>
       </c>
       <c r="H73" t="n">
-        <v>46.3</v>
+        <v>13.8</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-156.55</v>
+        <v>-358.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-371</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>402.68</v>
+        <v>370.71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:19:08</t>
+          <t>08:15:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.88</v>
+        <v>4.49</v>
       </c>
       <c r="F74" t="n">
-        <v>14.6</v>
+        <v>13.13</v>
       </c>
       <c r="G74" t="n">
-        <v>241.4</v>
+        <v>240.3</v>
       </c>
       <c r="H74" t="n">
-        <v>50.5</v>
+        <v>54.3</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>65.12</v>
+        <v>41.93</v>
       </c>
       <c r="K74" t="n">
-        <v>13.64</v>
+        <v>79.39</v>
       </c>
       <c r="L74" t="n">
-        <v>66.54000000000001</v>
+        <v>89.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:20:15</t>
+          <t>08:17:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.16</v>
+        <v>4.69</v>
       </c>
       <c r="F75" t="n">
         <v>14.6</v>
       </c>
       <c r="G75" t="n">
-        <v>240.7</v>
+        <v>233.2</v>
       </c>
       <c r="H75" t="n">
-        <v>47.5</v>
+        <v>67.7</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.74</v>
+        <v>-64.98999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-12.58</v>
+        <v>75.97</v>
       </c>
       <c r="L75" t="n">
-        <v>33.22</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:21:18</t>
+          <t>08:18:53</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.74</v>
+        <v>3.97</v>
       </c>
       <c r="F76" t="n">
-        <v>10.09</v>
+        <v>11.11</v>
       </c>
       <c r="G76" t="n">
-        <v>232.6</v>
+        <v>239.5</v>
       </c>
       <c r="H76" t="n">
-        <v>50.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>68.09</v>
+        <v>3.77</v>
       </c>
       <c r="K76" t="n">
-        <v>-52.86</v>
+        <v>64.45</v>
       </c>
       <c r="L76" t="n">
-        <v>86.2</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:26:37</t>
+          <t>08:22:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.89</v>
+        <v>4.16</v>
       </c>
       <c r="F77" t="n">
         <v>14.6</v>
       </c>
       <c r="G77" t="n">
-        <v>236.3</v>
+        <v>249.5</v>
       </c>
       <c r="H77" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.23999999999999</v>
+        <v>-30.51</v>
       </c>
       <c r="K77" t="n">
-        <v>14.03</v>
+        <v>102.24</v>
       </c>
       <c r="L77" t="n">
-        <v>67.70999999999999</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:27:56</t>
+          <t>08:24:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="F78" t="n">
-        <v>14.1</v>
+        <v>12.04</v>
       </c>
       <c r="G78" t="n">
-        <v>221.3</v>
+        <v>239.6</v>
       </c>
       <c r="H78" t="n">
-        <v>57.1</v>
+        <v>49.4</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>41.51</v>
+        <v>-102.26</v>
       </c>
       <c r="K78" t="n">
-        <v>-67.62</v>
+        <v>-82.12</v>
       </c>
       <c r="L78" t="n">
-        <v>79.34</v>
+        <v>131.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:29:30</t>
+          <t>08:26:02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.82</v>
+        <v>4.49</v>
       </c>
       <c r="F79" t="n">
-        <v>11.23</v>
+        <v>14.6</v>
       </c>
       <c r="G79" t="n">
-        <v>238.7</v>
+        <v>233.9</v>
       </c>
       <c r="H79" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-93.41</v>
+        <v>-37.55</v>
       </c>
       <c r="K79" t="n">
-        <v>1.67</v>
+        <v>-100.29</v>
       </c>
       <c r="L79" t="n">
-        <v>93.43000000000001</v>
+        <v>107.09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:34:54</t>
+          <t>08:30:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.76</v>
+        <v>3.77</v>
       </c>
       <c r="F80" t="n">
         <v>14.6</v>
       </c>
       <c r="G80" t="n">
-        <v>245.3</v>
+        <v>239</v>
       </c>
       <c r="H80" t="n">
-        <v>49.2</v>
+        <v>33.9</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>34.32</v>
+        <v>-42.47</v>
       </c>
       <c r="K80" t="n">
-        <v>123.96</v>
+        <v>-97.84</v>
       </c>
       <c r="L80" t="n">
-        <v>128.62</v>
+        <v>106.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:36:00</t>
+          <t>08:31:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.89</v>
+        <v>4.32</v>
       </c>
       <c r="F81" t="n">
-        <v>14.6</v>
+        <v>11.7</v>
       </c>
       <c r="G81" t="n">
-        <v>236.7</v>
+        <v>253.1</v>
       </c>
       <c r="H81" t="n">
-        <v>51.2</v>
+        <v>49.4</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>1.19</v>
+        <v>-70.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-91.23999999999999</v>
+        <v>136.79</v>
       </c>
       <c r="L81" t="n">
-        <v>91.23999999999999</v>
+        <v>153.86</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:37:23</t>
+          <t>08:33:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="F82" t="n">
-        <v>7.7</v>
+        <v>13.38</v>
       </c>
       <c r="G82" t="n">
-        <v>239.5</v>
+        <v>242.5</v>
       </c>
       <c r="H82" t="n">
-        <v>53.6</v>
+        <v>48.7</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-76.12</v>
+        <v>-85.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-15.57</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>77.7</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:41:41</t>
+          <t>08:38:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.3</v>
+        <v>4.01</v>
       </c>
       <c r="F83" t="n">
-        <v>14.6</v>
+        <v>10.28</v>
       </c>
       <c r="G83" t="n">
-        <v>232.2</v>
+        <v>224.9</v>
       </c>
       <c r="H83" t="n">
-        <v>59</v>
+        <v>34.6</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>152.17</v>
+        <v>-45.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-44.18</v>
+        <v>-200.95</v>
       </c>
       <c r="L83" t="n">
-        <v>158.45</v>
+        <v>205.95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:44:06</t>
+          <t>08:40:14</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.62</v>
+        <v>3.53</v>
       </c>
       <c r="F84" t="n">
-        <v>14.6</v>
+        <v>14.33</v>
       </c>
       <c r="G84" t="n">
-        <v>242.1</v>
+        <v>233.3</v>
       </c>
       <c r="H84" t="n">
-        <v>55.5</v>
+        <v>78.8</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-22.9</v>
+        <v>-0.17</v>
       </c>
       <c r="K84" t="n">
-        <v>-150.41</v>
+        <v>150.9</v>
       </c>
       <c r="L84" t="n">
-        <v>152.14</v>
+        <v>150.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:46:20</t>
+          <t>08:41:50</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.76</v>
+        <v>4.38</v>
       </c>
       <c r="F85" t="n">
-        <v>14.6</v>
+        <v>14.02</v>
       </c>
       <c r="G85" t="n">
-        <v>240.6</v>
+        <v>236.6</v>
       </c>
       <c r="H85" t="n">
-        <v>49.8</v>
+        <v>48.1</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>237.89</v>
+        <v>-130.2</v>
       </c>
       <c r="K85" t="n">
-        <v>118.89</v>
+        <v>-123.95</v>
       </c>
       <c r="L85" t="n">
-        <v>265.94</v>
+        <v>179.76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:50:57</t>
+          <t>08:45:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="F86" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G86" t="n">
-        <v>220.3</v>
+        <v>253.1</v>
       </c>
       <c r="H86" t="n">
-        <v>47.2</v>
+        <v>57.7</v>
       </c>
       <c r="I86" t="n">
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-163.43</v>
+        <v>-167.98</v>
       </c>
       <c r="K86" t="n">
-        <v>74.98999999999999</v>
+        <v>284.84</v>
       </c>
       <c r="L86" t="n">
-        <v>179.81</v>
+        <v>330.69</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:52:20</t>
+          <t>08:47:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="F87" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="G87" t="n">
-        <v>234.7</v>
+        <v>245.1</v>
       </c>
       <c r="H87" t="n">
-        <v>55.1</v>
+        <v>47.5</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>156.3</v>
+        <v>-281.2</v>
       </c>
       <c r="K87" t="n">
-        <v>179.25</v>
+        <v>-138.86</v>
       </c>
       <c r="L87" t="n">
-        <v>237.82</v>
+        <v>313.62</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:53:33</t>
+          <t>08:49:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.32</v>
+        <v>5.02</v>
       </c>
       <c r="F88" t="n">
         <v>14.6</v>
       </c>
       <c r="G88" t="n">
-        <v>230.4</v>
+        <v>239.1</v>
       </c>
       <c r="H88" t="n">
-        <v>45.6</v>
+        <v>40.4</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-310.97</v>
+        <v>-368.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-99.81</v>
+        <v>52.59</v>
       </c>
       <c r="L88" t="n">
-        <v>326.6</v>
+        <v>372.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="F14" t="n">
-        <v>7.75</v>
+        <v>11.01</v>
       </c>
       <c r="G14" t="n">
-        <v>248.5</v>
+        <v>242.6</v>
       </c>
       <c r="H14" t="n">
-        <v>59.7</v>
+        <v>58</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.55</v>
+        <v>-0.2</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.41</v>
+        <v>-42.09</v>
       </c>
       <c r="L14" t="n">
-        <v>38.68</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:14:57</t>
+          <t>05:15:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="F15" t="n">
-        <v>10.29</v>
+        <v>10.88</v>
       </c>
       <c r="G15" t="n">
-        <v>237.8</v>
+        <v>233.9</v>
       </c>
       <c r="H15" t="n">
-        <v>30.8</v>
+        <v>61.5</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-40.64</v>
+        <v>-31.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-12.62</v>
+        <v>-17.19</v>
       </c>
       <c r="L15" t="n">
-        <v>42.55</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:17:17</t>
+          <t>05:17:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.19</v>
+        <v>3.65</v>
       </c>
       <c r="F16" t="n">
-        <v>8.800000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="G16" t="n">
-        <v>222.4</v>
+        <v>236.8</v>
       </c>
       <c r="H16" t="n">
-        <v>31.8</v>
+        <v>38.5</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.12</v>
+        <v>-16.55</v>
       </c>
       <c r="K16" t="n">
-        <v>-39.16</v>
+        <v>-51.2</v>
       </c>
       <c r="L16" t="n">
-        <v>42.35</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:23:09</t>
+          <t>05:22:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="F17" t="n">
-        <v>11.27</v>
+        <v>8.27</v>
       </c>
       <c r="G17" t="n">
-        <v>243.9</v>
+        <v>232.2</v>
       </c>
       <c r="H17" t="n">
-        <v>43.6</v>
+        <v>76.5</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-50.96</v>
+        <v>14.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-56.63</v>
+        <v>-64.18000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>76.18000000000001</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:25:11</t>
+          <t>05:24:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="F18" t="n">
-        <v>8.58</v>
+        <v>8.84</v>
       </c>
       <c r="G18" t="n">
-        <v>232.2</v>
+        <v>229.8</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>77.5</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.85</v>
+        <v>-46.18</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.63</v>
+        <v>48.27</v>
       </c>
       <c r="L18" t="n">
-        <v>75.68000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:27:34</t>
+          <t>05:25:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.06</v>
+        <v>4.48</v>
       </c>
       <c r="F19" t="n">
-        <v>10.13</v>
+        <v>12.74</v>
       </c>
       <c r="G19" t="n">
-        <v>233.3</v>
+        <v>235.2</v>
       </c>
       <c r="H19" t="n">
-        <v>58</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-24.39</v>
+        <v>38.41</v>
       </c>
       <c r="K19" t="n">
-        <v>90.86</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>94.08</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:32:20</t>
+          <t>05:31:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.11</v>
+        <v>2.96</v>
       </c>
       <c r="F20" t="n">
-        <v>10.62</v>
+        <v>10.23</v>
       </c>
       <c r="G20" t="n">
-        <v>234</v>
+        <v>228.6</v>
       </c>
       <c r="H20" t="n">
-        <v>62.4</v>
+        <v>36.8</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-64.12</v>
+        <v>-84.31999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>105.96</v>
+        <v>-22.97</v>
       </c>
       <c r="L20" t="n">
-        <v>123.85</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:33:25</t>
+          <t>05:33:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.25</v>
+        <v>3.87</v>
       </c>
       <c r="F21" t="n">
-        <v>10.62</v>
+        <v>10.39</v>
       </c>
       <c r="G21" t="n">
-        <v>220.9</v>
+        <v>235.6</v>
       </c>
       <c r="H21" t="n">
-        <v>30.3</v>
+        <v>56.6</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-50.83</v>
+        <v>10.08</v>
       </c>
       <c r="K21" t="n">
-        <v>65.01000000000001</v>
+        <v>137.65</v>
       </c>
       <c r="L21" t="n">
-        <v>82.52</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:35:26</t>
+          <t>05:34:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="F22" t="n">
-        <v>11.96</v>
+        <v>11.29</v>
       </c>
       <c r="G22" t="n">
-        <v>234.8</v>
+        <v>235.4</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>55.5</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-75.01000000000001</v>
+        <v>48.82</v>
       </c>
       <c r="K22" t="n">
-        <v>60.54</v>
+        <v>118.4</v>
       </c>
       <c r="L22" t="n">
-        <v>96.40000000000001</v>
+        <v>128.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:41:01</t>
+          <t>05:39:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="F23" t="n">
-        <v>11.97</v>
+        <v>11.28</v>
       </c>
       <c r="G23" t="n">
-        <v>249.3</v>
+        <v>240.6</v>
       </c>
       <c r="H23" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>88.38</v>
+        <v>-65.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-116.31</v>
+        <v>195.81</v>
       </c>
       <c r="L23" t="n">
-        <v>146.08</v>
+        <v>206.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:42:04</t>
+          <t>05:41:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.68</v>
+        <v>4.01</v>
       </c>
       <c r="F24" t="n">
-        <v>14.02</v>
+        <v>12.74</v>
       </c>
       <c r="G24" t="n">
-        <v>242.3</v>
+        <v>254.2</v>
       </c>
       <c r="H24" t="n">
-        <v>45.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>93.37</v>
+        <v>220.99</v>
       </c>
       <c r="K24" t="n">
-        <v>-192.76</v>
+        <v>61.95</v>
       </c>
       <c r="L24" t="n">
-        <v>214.19</v>
+        <v>229.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:44:26</t>
+          <t>05:42:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.42</v>
+        <v>4.41</v>
       </c>
       <c r="F25" t="n">
-        <v>10.67</v>
+        <v>12.72</v>
       </c>
       <c r="G25" t="n">
-        <v>226.5</v>
+        <v>233</v>
       </c>
       <c r="H25" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>27.9</v>
+        <v>-231.47</v>
       </c>
       <c r="K25" t="n">
-        <v>-181.87</v>
+        <v>-12.38</v>
       </c>
       <c r="L25" t="n">
-        <v>184</v>
+        <v>231.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:48:57</t>
+          <t>05:47:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.11</v>
+        <v>3.96</v>
       </c>
       <c r="F26" t="n">
-        <v>11.44</v>
+        <v>14.6</v>
       </c>
       <c r="G26" t="n">
-        <v>249.6</v>
+        <v>224.5</v>
       </c>
       <c r="H26" t="n">
-        <v>26</v>
+        <v>41.9</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>179.12</v>
+        <v>-217.02</v>
       </c>
       <c r="K26" t="n">
-        <v>-199.18</v>
+        <v>-121.83</v>
       </c>
       <c r="L26" t="n">
-        <v>267.88</v>
+        <v>248.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:51:03</t>
+          <t>05:49:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="F27" t="n">
-        <v>10.21</v>
+        <v>8.32</v>
       </c>
       <c r="G27" t="n">
-        <v>245.6</v>
+        <v>248.6</v>
       </c>
       <c r="H27" t="n">
-        <v>9.699999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>196.43</v>
+        <v>-60.19</v>
       </c>
       <c r="K27" t="n">
-        <v>165.67</v>
+        <v>-218.77</v>
       </c>
       <c r="L27" t="n">
-        <v>256.96</v>
+        <v>226.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:52:27</t>
+          <t>05:50:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.24</v>
+        <v>3.28</v>
       </c>
       <c r="F28" t="n">
-        <v>14.6</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>242.9</v>
+        <v>237.8</v>
       </c>
       <c r="H28" t="n">
-        <v>90.3</v>
+        <v>73.8</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-236.82</v>
+        <v>-64.63</v>
       </c>
       <c r="K28" t="n">
-        <v>61.73</v>
+        <v>209.58</v>
       </c>
       <c r="L28" t="n">
-        <v>244.74</v>
+        <v>219.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:04:15</t>
+          <t>06:02:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.56</v>
+        <v>3.93</v>
       </c>
       <c r="F29" t="n">
-        <v>7.89</v>
+        <v>14.09</v>
       </c>
       <c r="G29" t="n">
-        <v>237</v>
+        <v>246.8</v>
       </c>
       <c r="H29" t="n">
-        <v>21.9</v>
+        <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>43.01</v>
+        <v>-16.99</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.48</v>
+        <v>57.51</v>
       </c>
       <c r="L29" t="n">
-        <v>60.46</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:05:52</t>
+          <t>06:04:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.72</v>
+        <v>3.33</v>
       </c>
       <c r="F30" t="n">
-        <v>14.6</v>
+        <v>11.61</v>
       </c>
       <c r="G30" t="n">
-        <v>233.6</v>
+        <v>241.2</v>
       </c>
       <c r="H30" t="n">
-        <v>13.8</v>
+        <v>75.7</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.29</v>
+        <v>-27.96</v>
       </c>
       <c r="K30" t="n">
-        <v>11.28</v>
+        <v>-40.52</v>
       </c>
       <c r="L30" t="n">
-        <v>42.8</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:07:33</t>
+          <t>06:06:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="F31" t="n">
-        <v>13.4</v>
+        <v>12.99</v>
       </c>
       <c r="G31" t="n">
-        <v>228</v>
+        <v>236.5</v>
       </c>
       <c r="H31" t="n">
-        <v>82.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>69.17</v>
+        <v>43.34</v>
       </c>
       <c r="K31" t="n">
-        <v>0.99</v>
+        <v>-4.98</v>
       </c>
       <c r="L31" t="n">
-        <v>69.18000000000001</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:12:39</t>
+          <t>06:10:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.33</v>
+        <v>3.93</v>
       </c>
       <c r="F32" t="n">
-        <v>8.800000000000001</v>
+        <v>12.04</v>
       </c>
       <c r="G32" t="n">
-        <v>227.9</v>
+        <v>250.5</v>
       </c>
       <c r="H32" t="n">
-        <v>50.3</v>
+        <v>56.2</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-84.40000000000001</v>
+        <v>34.57</v>
       </c>
       <c r="K32" t="n">
-        <v>-63.79</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>105.8</v>
+        <v>88.43000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:13:50</t>
+          <t>06:13:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.28</v>
+        <v>4.03</v>
       </c>
       <c r="F33" t="n">
-        <v>8.220000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="G33" t="n">
-        <v>242.3</v>
+        <v>249.3</v>
       </c>
       <c r="H33" t="n">
-        <v>19.5</v>
+        <v>37.6</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.7</v>
+        <v>-63.24</v>
       </c>
       <c r="K33" t="n">
-        <v>44.88</v>
+        <v>-47.05</v>
       </c>
       <c r="L33" t="n">
-        <v>49.85</v>
+        <v>78.81999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:14:55</t>
+          <t>06:14:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="F34" t="n">
-        <v>11.18</v>
+        <v>11.36</v>
       </c>
       <c r="G34" t="n">
-        <v>243.7</v>
+        <v>230.7</v>
       </c>
       <c r="H34" t="n">
-        <v>44.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>50.58</v>
+        <v>-60.8</v>
       </c>
       <c r="K34" t="n">
-        <v>21.08</v>
+        <v>51.4</v>
       </c>
       <c r="L34" t="n">
-        <v>54.79</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:19:59</t>
+          <t>06:19:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="F35" t="n">
-        <v>10.24</v>
+        <v>8.94</v>
       </c>
       <c r="G35" t="n">
-        <v>231.6</v>
+        <v>226.9</v>
       </c>
       <c r="H35" t="n">
-        <v>6.1</v>
+        <v>18.8</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.73999999999999</v>
+        <v>48.19</v>
       </c>
       <c r="K35" t="n">
-        <v>-37.96</v>
+        <v>-82.31</v>
       </c>
       <c r="L35" t="n">
-        <v>95.59999999999999</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:21:00</t>
+          <t>06:21:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="F36" t="n">
-        <v>7.12</v>
+        <v>14.6</v>
       </c>
       <c r="G36" t="n">
-        <v>251.9</v>
+        <v>223.8</v>
       </c>
       <c r="H36" t="n">
-        <v>79.59999999999999</v>
+        <v>52.8</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-70.19</v>
+        <v>36.09</v>
       </c>
       <c r="K36" t="n">
-        <v>95.91</v>
+        <v>105.18</v>
       </c>
       <c r="L36" t="n">
-        <v>118.85</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:21:58</t>
+          <t>06:22:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.96</v>
+        <v>3.96</v>
       </c>
       <c r="F37" t="n">
-        <v>8.779999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="G37" t="n">
-        <v>243.9</v>
+        <v>243.7</v>
       </c>
       <c r="H37" t="n">
-        <v>66</v>
+        <v>31.3</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>29.83</v>
+        <v>-101.74</v>
       </c>
       <c r="K37" t="n">
-        <v>-80.33</v>
+        <v>-74.27</v>
       </c>
       <c r="L37" t="n">
-        <v>85.69</v>
+        <v>125.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:25:43</t>
+          <t>06:27:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="F38" t="n">
-        <v>10.52</v>
+        <v>10.09</v>
       </c>
       <c r="G38" t="n">
-        <v>225.7</v>
+        <v>241.5</v>
       </c>
       <c r="H38" t="n">
-        <v>19.6</v>
+        <v>50.7</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>160.28</v>
+        <v>-215.01</v>
       </c>
       <c r="K38" t="n">
-        <v>-181.82</v>
+        <v>118.82</v>
       </c>
       <c r="L38" t="n">
-        <v>242.38</v>
+        <v>245.65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:26:39</t>
+          <t>06:28:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="n">
-        <v>8.34</v>
+        <v>11.18</v>
       </c>
       <c r="G39" t="n">
-        <v>250.2</v>
+        <v>231.1</v>
       </c>
       <c r="H39" t="n">
-        <v>37.8</v>
+        <v>49.9</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-123.35</v>
+        <v>116.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.55</v>
+        <v>-138.62</v>
       </c>
       <c r="L39" t="n">
-        <v>123.8</v>
+        <v>181.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:29:05</t>
+          <t>06:30:03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="F40" t="n">
-        <v>6.58</v>
+        <v>8.91</v>
       </c>
       <c r="G40" t="n">
-        <v>237</v>
+        <v>233.8</v>
       </c>
       <c r="H40" t="n">
-        <v>63.4</v>
+        <v>44.3</v>
       </c>
       <c r="I40" t="n">
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-59.88</v>
+        <v>-133.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-110.41</v>
+        <v>-112.21</v>
       </c>
       <c r="L40" t="n">
-        <v>125.6</v>
+        <v>174.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:34:23</t>
+          <t>06:34:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.11</v>
+        <v>3.59</v>
       </c>
       <c r="F41" t="n">
-        <v>11.77</v>
+        <v>13.17</v>
       </c>
       <c r="G41" t="n">
-        <v>249</v>
+        <v>227.8</v>
       </c>
       <c r="H41" t="n">
-        <v>54.9</v>
+        <v>23.9</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-212.93</v>
+        <v>-144.56</v>
       </c>
       <c r="K41" t="n">
-        <v>110.85</v>
+        <v>61.36</v>
       </c>
       <c r="L41" t="n">
-        <v>240.06</v>
+        <v>157.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:36:39</t>
+          <t>06:36:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="F42" t="n">
-        <v>10.89</v>
+        <v>14.6</v>
       </c>
       <c r="G42" t="n">
-        <v>236.9</v>
+        <v>227.7</v>
       </c>
       <c r="H42" t="n">
-        <v>57.7</v>
+        <v>56.1</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-13.47</v>
+        <v>-140.81</v>
       </c>
       <c r="K42" t="n">
-        <v>330.74</v>
+        <v>245.45</v>
       </c>
       <c r="L42" t="n">
-        <v>331.01</v>
+        <v>282.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:37:17</t>
+          <t>06:37:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="F43" t="n">
-        <v>10.92</v>
+        <v>9.02</v>
       </c>
       <c r="G43" t="n">
-        <v>253.4</v>
+        <v>248.2</v>
       </c>
       <c r="H43" t="n">
-        <v>34.1</v>
+        <v>31.4</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-199.13</v>
+        <v>210.28</v>
       </c>
       <c r="K43" t="n">
-        <v>339.03</v>
+        <v>-160.1</v>
       </c>
       <c r="L43" t="n">
-        <v>393.19</v>
+        <v>264.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:48:07</t>
+          <t>06:48:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.37</v>
+        <v>3.74</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>12.48</v>
       </c>
       <c r="G44" t="n">
-        <v>233.4</v>
+        <v>231.1</v>
       </c>
       <c r="H44" t="n">
-        <v>55.2</v>
+        <v>32.3</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-55.92</v>
+        <v>-45.85</v>
       </c>
       <c r="K44" t="n">
-        <v>-12.63</v>
+        <v>23.77</v>
       </c>
       <c r="L44" t="n">
-        <v>57.33</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:49:05</t>
+          <t>06:49:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.7</v>
+        <v>4.16</v>
       </c>
       <c r="F45" t="n">
-        <v>8.710000000000001</v>
+        <v>14.42</v>
       </c>
       <c r="G45" t="n">
-        <v>252.6</v>
+        <v>233.1</v>
       </c>
       <c r="H45" t="n">
-        <v>52.8</v>
+        <v>19.6</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.97</v>
+        <v>73.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.31</v>
+        <v>-12.14</v>
       </c>
       <c r="L45" t="n">
-        <v>55.24</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:51:02</t>
+          <t>06:51:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.06</v>
+        <v>3.73</v>
       </c>
       <c r="F46" t="n">
-        <v>14.42</v>
+        <v>10.64</v>
       </c>
       <c r="G46" t="n">
-        <v>232.3</v>
+        <v>236.7</v>
       </c>
       <c r="H46" t="n">
-        <v>30.5</v>
+        <v>41</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-35.36</v>
+        <v>-5.06</v>
       </c>
       <c r="K46" t="n">
-        <v>-41.9</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>54.83</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:55:47</t>
+          <t>06:56:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="F47" t="n">
-        <v>13.44</v>
+        <v>14.6</v>
       </c>
       <c r="G47" t="n">
-        <v>234.2</v>
+        <v>239</v>
       </c>
       <c r="H47" t="n">
-        <v>59.3</v>
+        <v>87.7</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-56.71</v>
+        <v>5.33</v>
       </c>
       <c r="K47" t="n">
-        <v>-72.86</v>
+        <v>-86.92</v>
       </c>
       <c r="L47" t="n">
-        <v>92.33</v>
+        <v>87.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:58:23</t>
+          <t>06:57:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.71</v>
+        <v>4.49</v>
       </c>
       <c r="F48" t="n">
-        <v>12.16</v>
+        <v>14.6</v>
       </c>
       <c r="G48" t="n">
-        <v>237.4</v>
+        <v>233.6</v>
       </c>
       <c r="H48" t="n">
-        <v>60.6</v>
+        <v>50.3</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-95.78</v>
+        <v>94.2</v>
       </c>
       <c r="K48" t="n">
-        <v>12.36</v>
+        <v>45.9</v>
       </c>
       <c r="L48" t="n">
-        <v>96.58</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:00:12</t>
+          <t>06:58:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.84</v>
+        <v>4.01</v>
       </c>
       <c r="F49" t="n">
-        <v>13.33</v>
+        <v>14.52</v>
       </c>
       <c r="G49" t="n">
-        <v>229.1</v>
+        <v>231.1</v>
       </c>
       <c r="H49" t="n">
-        <v>3.4</v>
+        <v>19.8</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-75.52</v>
+        <v>-72.84999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-70.70999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="L49" t="n">
-        <v>103.46</v>
+        <v>108.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:05:56</t>
+          <t>07:04:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.11</v>
+        <v>3.63</v>
       </c>
       <c r="F50" t="n">
-        <v>12.76</v>
+        <v>12.02</v>
       </c>
       <c r="G50" t="n">
-        <v>237.4</v>
+        <v>234</v>
       </c>
       <c r="H50" t="n">
-        <v>57.5</v>
+        <v>49.4</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>-93.97</v>
+        <v>3.42</v>
       </c>
       <c r="K50" t="n">
-        <v>-94.73</v>
+        <v>114.82</v>
       </c>
       <c r="L50" t="n">
-        <v>133.43</v>
+        <v>114.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:06:56</t>
+          <t>07:06:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.48</v>
+        <v>3.38</v>
       </c>
       <c r="F51" t="n">
-        <v>14.08</v>
+        <v>12.73</v>
       </c>
       <c r="G51" t="n">
-        <v>235.5</v>
+        <v>224.3</v>
       </c>
       <c r="H51" t="n">
-        <v>47.8</v>
+        <v>52.1</v>
       </c>
       <c r="I51" t="n">
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.55</v>
+        <v>-26.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-164.82</v>
+        <v>90.97</v>
       </c>
       <c r="L51" t="n">
-        <v>165.16</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:07:51</t>
+          <t>07:07:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="F52" t="n">
-        <v>12.33</v>
+        <v>14.16</v>
       </c>
       <c r="G52" t="n">
-        <v>237.5</v>
+        <v>233.3</v>
       </c>
       <c r="H52" t="n">
-        <v>43.4</v>
+        <v>74.7</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J52" t="n">
-        <v>-129.69</v>
+        <v>-46.07</v>
       </c>
       <c r="K52" t="n">
-        <v>-129.81</v>
+        <v>105.6</v>
       </c>
       <c r="L52" t="n">
-        <v>183.5</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:12:07</t>
+          <t>07:10:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.92</v>
+        <v>3.61</v>
       </c>
       <c r="F53" t="n">
-        <v>14.6</v>
+        <v>11.32</v>
       </c>
       <c r="G53" t="n">
-        <v>230.3</v>
+        <v>239.4</v>
       </c>
       <c r="H53" t="n">
-        <v>69</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-148.92</v>
+        <v>-189.22</v>
       </c>
       <c r="K53" t="n">
-        <v>211.78</v>
+        <v>204.22</v>
       </c>
       <c r="L53" t="n">
-        <v>258.9</v>
+        <v>278.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:13:59</t>
+          <t>07:12:40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="F54" t="n">
-        <v>9.84</v>
+        <v>7.12</v>
       </c>
       <c r="G54" t="n">
-        <v>240</v>
+        <v>221.5</v>
       </c>
       <c r="H54" t="n">
-        <v>24.4</v>
+        <v>13.6</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>3.74</v>
+        <v>159.17</v>
       </c>
       <c r="K54" t="n">
-        <v>-342.26</v>
+        <v>-58.84</v>
       </c>
       <c r="L54" t="n">
-        <v>342.28</v>
+        <v>169.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:16:43</t>
+          <t>07:13:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.73</v>
+        <v>4.46</v>
       </c>
       <c r="F55" t="n">
-        <v>10.74</v>
+        <v>11.9</v>
       </c>
       <c r="G55" t="n">
-        <v>231.4</v>
+        <v>236.8</v>
       </c>
       <c r="H55" t="n">
-        <v>27.5</v>
+        <v>45</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-136.25</v>
+        <v>207.06</v>
       </c>
       <c r="K55" t="n">
-        <v>-122.01</v>
+        <v>-132.16</v>
       </c>
       <c r="L55" t="n">
-        <v>182.89</v>
+        <v>245.64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:21:10</t>
+          <t>07:17:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="F56" t="n">
-        <v>13.01</v>
+        <v>12.53</v>
       </c>
       <c r="G56" t="n">
-        <v>239</v>
+        <v>237.2</v>
       </c>
       <c r="H56" t="n">
-        <v>28.8</v>
+        <v>63.6</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>76.81</v>
+        <v>-2.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-276.77</v>
+        <v>326.31</v>
       </c>
       <c r="L56" t="n">
-        <v>287.23</v>
+        <v>326.32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:22:04</t>
+          <t>07:18:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.79</v>
+        <v>4.23</v>
       </c>
       <c r="F57" t="n">
-        <v>13.43</v>
+        <v>14.6</v>
       </c>
       <c r="G57" t="n">
-        <v>225.4</v>
+        <v>238.8</v>
       </c>
       <c r="H57" t="n">
-        <v>37.4</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-162.4</v>
+        <v>-267.49</v>
       </c>
       <c r="K57" t="n">
-        <v>-129.39</v>
+        <v>147.3</v>
       </c>
       <c r="L57" t="n">
-        <v>207.64</v>
+        <v>305.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:23:16</t>
+          <t>07:20:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.34</v>
+        <v>4.12</v>
       </c>
       <c r="F58" t="n">
-        <v>10.88</v>
+        <v>14.6</v>
       </c>
       <c r="G58" t="n">
-        <v>230.8</v>
+        <v>231.3</v>
       </c>
       <c r="H58" t="n">
-        <v>68.5</v>
+        <v>61.6</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>135.5</v>
+        <v>105.16</v>
       </c>
       <c r="K58" t="n">
-        <v>158.6</v>
+        <v>-299.9</v>
       </c>
       <c r="L58" t="n">
-        <v>208.6</v>
+        <v>317.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:32:39</t>
+          <t>07:28:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.16</v>
+        <v>3.43</v>
       </c>
       <c r="F59" t="n">
-        <v>9.220000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="G59" t="n">
-        <v>250.7</v>
+        <v>227</v>
       </c>
       <c r="H59" t="n">
-        <v>18</v>
+        <v>42.2</v>
       </c>
       <c r="I59" t="n">
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-63.08</v>
+        <v>11.87</v>
       </c>
       <c r="K59" t="n">
-        <v>24.27</v>
+        <v>65.3</v>
       </c>
       <c r="L59" t="n">
-        <v>67.59</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:33:58</t>
+          <t>07:31:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="F60" t="n">
-        <v>11.84</v>
+        <v>14.6</v>
       </c>
       <c r="G60" t="n">
-        <v>243.1</v>
+        <v>221.8</v>
       </c>
       <c r="H60" t="n">
-        <v>48.2</v>
+        <v>93.2</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-54.77</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>12.81</v>
+        <v>-36.61</v>
       </c>
       <c r="L60" t="n">
-        <v>56.24</v>
+        <v>84.97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:36:07</t>
+          <t>07:32:05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2602,31 +2602,31 @@
         <v>3.8</v>
       </c>
       <c r="F61" t="n">
-        <v>10.19</v>
+        <v>14.6</v>
       </c>
       <c r="G61" t="n">
-        <v>244.8</v>
+        <v>231.9</v>
       </c>
       <c r="H61" t="n">
-        <v>78.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.12</v>
+        <v>18.78</v>
       </c>
       <c r="K61" t="n">
-        <v>74.88</v>
+        <v>-43.75</v>
       </c>
       <c r="L61" t="n">
-        <v>74.91</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:39:33</t>
+          <t>07:35:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.25</v>
+        <v>5.06</v>
       </c>
       <c r="F62" t="n">
-        <v>14.24</v>
+        <v>14.46</v>
       </c>
       <c r="G62" t="n">
-        <v>242.7</v>
+        <v>218.3</v>
       </c>
       <c r="H62" t="n">
-        <v>52.8</v>
+        <v>58.8</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.16</v>
+        <v>-42.32</v>
       </c>
       <c r="K62" t="n">
-        <v>-81.36</v>
+        <v>102.28</v>
       </c>
       <c r="L62" t="n">
-        <v>111.44</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:41:30</t>
+          <t>07:37:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="F63" t="n">
-        <v>14.6</v>
+        <v>11.11</v>
       </c>
       <c r="G63" t="n">
-        <v>249.5</v>
+        <v>229.2</v>
       </c>
       <c r="H63" t="n">
-        <v>66.2</v>
+        <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-68.5</v>
+        <v>-49.36</v>
       </c>
       <c r="K63" t="n">
-        <v>-65.47</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>94.76000000000001</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:43:22</t>
+          <t>07:39:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.52</v>
+        <v>3.38</v>
       </c>
       <c r="F64" t="n">
-        <v>10.56</v>
+        <v>13.15</v>
       </c>
       <c r="G64" t="n">
-        <v>244.7</v>
+        <v>243.5</v>
       </c>
       <c r="H64" t="n">
-        <v>68.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>21.6</v>
+        <v>-40.2</v>
       </c>
       <c r="K64" t="n">
-        <v>-93.87</v>
+        <v>57.62</v>
       </c>
       <c r="L64" t="n">
-        <v>96.31999999999999</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:49:39</t>
+          <t>07:43:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="F65" t="n">
         <v>14.6</v>
       </c>
       <c r="G65" t="n">
-        <v>224.5</v>
+        <v>242.9</v>
       </c>
       <c r="H65" t="n">
-        <v>35.9</v>
+        <v>53.2</v>
       </c>
       <c r="I65" t="n">
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-140.23</v>
+        <v>-156.24</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.81</v>
+        <v>30.04</v>
       </c>
       <c r="L65" t="n">
-        <v>154.07</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:51:07</t>
+          <t>07:45:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="F66" t="n">
-        <v>9.140000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="G66" t="n">
-        <v>256.1</v>
+        <v>235.2</v>
       </c>
       <c r="H66" t="n">
-        <v>10.9</v>
+        <v>40.4</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-75.29000000000001</v>
+        <v>27.77</v>
       </c>
       <c r="K66" t="n">
-        <v>33.43</v>
+        <v>-124.54</v>
       </c>
       <c r="L66" t="n">
-        <v>82.38</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:52:47</t>
+          <t>07:46:12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.45</v>
+        <v>5.17</v>
       </c>
       <c r="F67" t="n">
         <v>14.6</v>
       </c>
       <c r="G67" t="n">
-        <v>251.5</v>
+        <v>232.4</v>
       </c>
       <c r="H67" t="n">
-        <v>27.4</v>
+        <v>25.3</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>-8.449999999999999</v>
+        <v>-122.29</v>
       </c>
       <c r="K67" t="n">
-        <v>-137.72</v>
+        <v>-109.5</v>
       </c>
       <c r="L67" t="n">
-        <v>137.98</v>
+        <v>164.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:56:56</t>
+          <t>07:49:39</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.07</v>
+        <v>3.96</v>
       </c>
       <c r="F68" t="n">
         <v>14.6</v>
       </c>
       <c r="G68" t="n">
-        <v>226.6</v>
+        <v>246.2</v>
       </c>
       <c r="H68" t="n">
-        <v>26.3</v>
+        <v>62.5</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>293.08</v>
+        <v>167.68</v>
       </c>
       <c r="K68" t="n">
-        <v>38.63</v>
+        <v>-4.05</v>
       </c>
       <c r="L68" t="n">
-        <v>295.61</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:58:12</t>
+          <t>07:51:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.39</v>
+        <v>4.72</v>
       </c>
       <c r="F69" t="n">
-        <v>14.6</v>
+        <v>13.89</v>
       </c>
       <c r="G69" t="n">
-        <v>228.5</v>
+        <v>248.4</v>
       </c>
       <c r="H69" t="n">
-        <v>55.2</v>
+        <v>44.5</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-212.66</v>
+        <v>-280.38</v>
       </c>
       <c r="K69" t="n">
-        <v>102.68</v>
+        <v>61.21</v>
       </c>
       <c r="L69" t="n">
-        <v>236.16</v>
+        <v>286.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:58:59</t>
+          <t>07:53:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.43</v>
+        <v>3.78</v>
       </c>
       <c r="F70" t="n">
-        <v>14.4</v>
+        <v>10.31</v>
       </c>
       <c r="G70" t="n">
-        <v>243.6</v>
+        <v>235</v>
       </c>
       <c r="H70" t="n">
-        <v>58</v>
+        <v>71.5</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-344.88</v>
+        <v>-219.92</v>
       </c>
       <c r="K70" t="n">
-        <v>44.91</v>
+        <v>-18.42</v>
       </c>
       <c r="L70" t="n">
-        <v>347.79</v>
+        <v>220.69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:03:42</t>
+          <t>07:58:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.57</v>
+        <v>4.31</v>
       </c>
       <c r="F71" t="n">
-        <v>10.59</v>
+        <v>14.02</v>
       </c>
       <c r="G71" t="n">
-        <v>218.4</v>
+        <v>240.2</v>
       </c>
       <c r="H71" t="n">
-        <v>61.7</v>
+        <v>50.9</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>-218.98</v>
+        <v>-177.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-295.57</v>
+        <v>238.43</v>
       </c>
       <c r="L71" t="n">
-        <v>367.85</v>
+        <v>297.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:05:52</t>
+          <t>08:00:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.53</v>
+        <v>4.15</v>
       </c>
       <c r="F72" t="n">
-        <v>14.32</v>
+        <v>11.09</v>
       </c>
       <c r="G72" t="n">
-        <v>234</v>
+        <v>232.7</v>
       </c>
       <c r="H72" t="n">
-        <v>64.2</v>
+        <v>24</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-145.76</v>
+        <v>-131.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-224.17</v>
+        <v>274.19</v>
       </c>
       <c r="L72" t="n">
-        <v>267.39</v>
+        <v>304.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:06:52</t>
+          <t>08:00:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="F73" t="n">
         <v>14.6</v>
       </c>
       <c r="G73" t="n">
-        <v>242.5</v>
+        <v>229.8</v>
       </c>
       <c r="H73" t="n">
-        <v>13.8</v>
+        <v>64</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-358.85</v>
+        <v>136.02</v>
       </c>
       <c r="K73" t="n">
-        <v>-93.01000000000001</v>
+        <v>220.85</v>
       </c>
       <c r="L73" t="n">
-        <v>370.71</v>
+        <v>259.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:15:26</t>
+          <t>08:10:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="F74" t="n">
-        <v>13.13</v>
+        <v>14.6</v>
       </c>
       <c r="G74" t="n">
-        <v>240.3</v>
+        <v>238.7</v>
       </c>
       <c r="H74" t="n">
-        <v>54.3</v>
+        <v>71.5</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>41.93</v>
+        <v>35.3</v>
       </c>
       <c r="K74" t="n">
-        <v>79.39</v>
+        <v>60.39</v>
       </c>
       <c r="L74" t="n">
-        <v>89.78</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:17:21</t>
+          <t>08:12:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.69</v>
+        <v>3.86</v>
       </c>
       <c r="F75" t="n">
-        <v>14.6</v>
+        <v>12.99</v>
       </c>
       <c r="G75" t="n">
-        <v>233.2</v>
+        <v>241.1</v>
       </c>
       <c r="H75" t="n">
-        <v>67.7</v>
+        <v>66.7</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.98999999999999</v>
+        <v>-30.03</v>
       </c>
       <c r="K75" t="n">
-        <v>75.97</v>
+        <v>42.18</v>
       </c>
       <c r="L75" t="n">
-        <v>99.98</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:18:53</t>
+          <t>08:14:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.97</v>
+        <v>4.4</v>
       </c>
       <c r="F76" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="G76" t="n">
-        <v>239.5</v>
+        <v>214.8</v>
       </c>
       <c r="H76" t="n">
-        <v>86.40000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>3.77</v>
+        <v>-94.68000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>64.45</v>
+        <v>22.75</v>
       </c>
       <c r="L76" t="n">
-        <v>64.56</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:22:49</t>
+          <t>08:19:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.16</v>
+        <v>4.79</v>
       </c>
       <c r="F77" t="n">
         <v>14.6</v>
       </c>
       <c r="G77" t="n">
-        <v>249.5</v>
+        <v>240.7</v>
       </c>
       <c r="H77" t="n">
-        <v>51</v>
+        <v>25.2</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>-30.51</v>
+        <v>-82.06</v>
       </c>
       <c r="K77" t="n">
-        <v>102.24</v>
+        <v>-52.29</v>
       </c>
       <c r="L77" t="n">
-        <v>106.7</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:24:24</t>
+          <t>08:21:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="F78" t="n">
-        <v>12.04</v>
+        <v>13.54</v>
       </c>
       <c r="G78" t="n">
-        <v>239.6</v>
+        <v>232.8</v>
       </c>
       <c r="H78" t="n">
-        <v>49.4</v>
+        <v>60.8</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>-102.26</v>
+        <v>-86.09999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-82.12</v>
+        <v>-32.1</v>
       </c>
       <c r="L78" t="n">
-        <v>131.15</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:26:02</t>
+          <t>08:23:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.49</v>
+        <v>4.37</v>
       </c>
       <c r="F79" t="n">
         <v>14.6</v>
       </c>
       <c r="G79" t="n">
-        <v>233.9</v>
+        <v>240.8</v>
       </c>
       <c r="H79" t="n">
-        <v>55.5</v>
+        <v>8</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-37.55</v>
+        <v>9.35</v>
       </c>
       <c r="K79" t="n">
-        <v>-100.29</v>
+        <v>66.23</v>
       </c>
       <c r="L79" t="n">
-        <v>107.09</v>
+        <v>66.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:30:19</t>
+          <t>08:28:48</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="F80" t="n">
-        <v>14.6</v>
+        <v>12.72</v>
       </c>
       <c r="G80" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H80" t="n">
-        <v>33.9</v>
+        <v>44.4</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-42.47</v>
+        <v>31.97</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.84</v>
+        <v>95.94</v>
       </c>
       <c r="L80" t="n">
-        <v>106.66</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:31:44</t>
+          <t>08:30:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.32</v>
+        <v>4.54</v>
       </c>
       <c r="F81" t="n">
-        <v>11.7</v>
+        <v>13.62</v>
       </c>
       <c r="G81" t="n">
-        <v>253.1</v>
+        <v>225</v>
       </c>
       <c r="H81" t="n">
-        <v>49.4</v>
+        <v>42.5</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-70.45</v>
+        <v>-166.03</v>
       </c>
       <c r="K81" t="n">
-        <v>136.79</v>
+        <v>143.08</v>
       </c>
       <c r="L81" t="n">
-        <v>153.86</v>
+        <v>219.17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:33:49</t>
+          <t>08:31:20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.05</v>
+        <v>4.16</v>
       </c>
       <c r="F82" t="n">
-        <v>13.38</v>
+        <v>14.52</v>
       </c>
       <c r="G82" t="n">
-        <v>242.5</v>
+        <v>220.2</v>
       </c>
       <c r="H82" t="n">
-        <v>48.7</v>
+        <v>22.1</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.31</v>
+        <v>-163.78</v>
       </c>
       <c r="K82" t="n">
-        <v>85.01000000000001</v>
+        <v>-20.17</v>
       </c>
       <c r="L82" t="n">
-        <v>120.43</v>
+        <v>165.02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:38:07</t>
+          <t>08:36:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.01</v>
+        <v>5.13</v>
       </c>
       <c r="F83" t="n">
-        <v>10.28</v>
+        <v>14.6</v>
       </c>
       <c r="G83" t="n">
-        <v>224.9</v>
+        <v>232.2</v>
       </c>
       <c r="H83" t="n">
-        <v>34.6</v>
+        <v>43</v>
       </c>
       <c r="I83" t="n">
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-45.09</v>
+        <v>269.43</v>
       </c>
       <c r="K83" t="n">
-        <v>-200.95</v>
+        <v>121.06</v>
       </c>
       <c r="L83" t="n">
-        <v>205.95</v>
+        <v>295.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:40:14</t>
+          <t>08:37:34</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.53</v>
+        <v>4.62</v>
       </c>
       <c r="F84" t="n">
-        <v>14.33</v>
+        <v>13.57</v>
       </c>
       <c r="G84" t="n">
-        <v>233.3</v>
+        <v>232.8</v>
       </c>
       <c r="H84" t="n">
-        <v>78.8</v>
+        <v>38.6</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.17</v>
+        <v>244.24</v>
       </c>
       <c r="K84" t="n">
-        <v>150.9</v>
+        <v>168.67</v>
       </c>
       <c r="L84" t="n">
-        <v>150.9</v>
+        <v>296.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:41:50</t>
+          <t>08:39:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.38</v>
+        <v>4.71</v>
       </c>
       <c r="F85" t="n">
-        <v>14.02</v>
+        <v>14.58</v>
       </c>
       <c r="G85" t="n">
-        <v>236.6</v>
+        <v>234.9</v>
       </c>
       <c r="H85" t="n">
-        <v>48.1</v>
+        <v>60.1</v>
       </c>
       <c r="I85" t="n">
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-130.2</v>
+        <v>11.02</v>
       </c>
       <c r="K85" t="n">
-        <v>-123.95</v>
+        <v>-272.26</v>
       </c>
       <c r="L85" t="n">
-        <v>179.76</v>
+        <v>272.48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:45:11</t>
+          <t>08:43:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="F86" t="n">
-        <v>14.6</v>
+        <v>13.19</v>
       </c>
       <c r="G86" t="n">
-        <v>253.1</v>
+        <v>224.9</v>
       </c>
       <c r="H86" t="n">
-        <v>57.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>-167.98</v>
+        <v>254.88</v>
       </c>
       <c r="K86" t="n">
-        <v>284.84</v>
+        <v>-225.03</v>
       </c>
       <c r="L86" t="n">
-        <v>330.69</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:47:27</t>
+          <t>08:45:01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F87" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="G87" t="n">
         <v>245.1</v>
       </c>
       <c r="H87" t="n">
-        <v>47.5</v>
+        <v>6.9</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-281.2</v>
+        <v>-194.15</v>
       </c>
       <c r="K87" t="n">
-        <v>-138.86</v>
+        <v>243.61</v>
       </c>
       <c r="L87" t="n">
-        <v>313.62</v>
+        <v>311.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:49:33</t>
+          <t>08:46:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.02</v>
+        <v>4.49</v>
       </c>
       <c r="F88" t="n">
         <v>14.6</v>
       </c>
       <c r="G88" t="n">
-        <v>239.1</v>
+        <v>241.4</v>
       </c>
       <c r="H88" t="n">
-        <v>40.4</v>
+        <v>13.5</v>
       </c>
       <c r="I88" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-368.58</v>
+        <v>-163.58</v>
       </c>
       <c r="K88" t="n">
-        <v>52.59</v>
+        <v>-284.96</v>
       </c>
       <c r="L88" t="n">
-        <v>372.31</v>
+        <v>328.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.07</v>
+        <v>-19.58</v>
       </c>
       <c r="K14" t="n">
-        <v>71.59999999999999</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>74.09999999999999</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.27</v>
+        <v>-51.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-38.33</v>
+        <v>-42.46</v>
       </c>
       <c r="L15" t="n">
-        <v>60.09</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.85</v>
+        <v>-52.38</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.04000000000001</v>
+        <v>-79.34</v>
       </c>
       <c r="L16" t="n">
-        <v>95.92</v>
+        <v>95.06999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>47.89</v>
+        <v>58.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.83</v>
+        <v>-8.31</v>
       </c>
       <c r="L17" t="n">
-        <v>48.38</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>59.67</v>
+        <v>69.78</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.71</v>
+        <v>-9.02</v>
       </c>
       <c r="L18" t="n">
-        <v>60.17</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-49.79</v>
+        <v>-57.37</v>
       </c>
       <c r="K19" t="n">
-        <v>12.77</v>
+        <v>14.71</v>
       </c>
       <c r="L19" t="n">
-        <v>51.4</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>89.16</v>
+        <v>101.32</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.23</v>
+        <v>-57.08</v>
       </c>
       <c r="L20" t="n">
-        <v>102.34</v>
+        <v>116.29</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.86</v>
+        <v>-35.45</v>
       </c>
       <c r="K21" t="n">
-        <v>76.48</v>
+        <v>93.94</v>
       </c>
       <c r="L21" t="n">
-        <v>81.73999999999999</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>10.52</v>
+        <v>13.25</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.09999999999999</v>
+        <v>-107.27</v>
       </c>
       <c r="L22" t="n">
-        <v>85.75</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>106.03</v>
+        <v>136.61</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.09</v>
+        <v>-1.4</v>
       </c>
       <c r="L23" t="n">
-        <v>106.03</v>
+        <v>136.62</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-257.72</v>
+        <v>-276.47</v>
       </c>
       <c r="L24" t="n">
-        <v>257.75</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-38.45</v>
+        <v>-43.16</v>
       </c>
       <c r="K25" t="n">
-        <v>-198.02</v>
+        <v>-222.23</v>
       </c>
       <c r="L25" t="n">
-        <v>201.72</v>
+        <v>226.38</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>214.63</v>
+        <v>271.32</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.74</v>
+        <v>-18.63</v>
       </c>
       <c r="L26" t="n">
-        <v>215.14</v>
+        <v>271.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>159.72</v>
+        <v>198.27</v>
       </c>
       <c r="K27" t="n">
-        <v>134.69</v>
+        <v>167.21</v>
       </c>
       <c r="L27" t="n">
-        <v>208.93</v>
+        <v>259.37</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-249.6</v>
+        <v>-321.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-24.77</v>
+        <v>-31.91</v>
       </c>
       <c r="L28" t="n">
-        <v>250.82</v>
+        <v>323.07</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>54.41</v>
+        <v>59.08</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.27</v>
+        <v>-31.78</v>
       </c>
       <c r="L29" t="n">
-        <v>61.78</v>
+        <v>67.08</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-67.62</v>
+        <v>-71.33</v>
       </c>
       <c r="K30" t="n">
-        <v>20.61</v>
+        <v>21.74</v>
       </c>
       <c r="L30" t="n">
-        <v>70.69</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>12.38</v>
+        <v>12.59</v>
       </c>
       <c r="K31" t="n">
-        <v>88.45999999999999</v>
+        <v>89.94</v>
       </c>
       <c r="L31" t="n">
-        <v>89.33</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>6.18</v>
+        <v>7.35</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.5</v>
+        <v>-11.31</v>
       </c>
       <c r="L32" t="n">
-        <v>11.33</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-43.59</v>
+        <v>-48.23</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.08</v>
+        <v>-52.1</v>
       </c>
       <c r="L33" t="n">
-        <v>64.16</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>75.16</v>
+        <v>81.06</v>
       </c>
       <c r="K34" t="n">
-        <v>15.13</v>
+        <v>16.32</v>
       </c>
       <c r="L34" t="n">
-        <v>76.67</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-91.26000000000001</v>
+        <v>-112.27</v>
       </c>
       <c r="K35" t="n">
-        <v>-20.02</v>
+        <v>-24.62</v>
       </c>
       <c r="L35" t="n">
-        <v>93.43000000000001</v>
+        <v>114.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>59.03</v>
+        <v>66.39</v>
       </c>
       <c r="K36" t="n">
-        <v>97.22</v>
+        <v>109.35</v>
       </c>
       <c r="L36" t="n">
-        <v>113.74</v>
+        <v>127.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-71.3</v>
+        <v>-87.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.68</v>
+        <v>-3.3</v>
       </c>
       <c r="L37" t="n">
-        <v>71.34999999999999</v>
+        <v>87.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>156.24</v>
+        <v>185.58</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.99</v>
+        <v>-5.92</v>
       </c>
       <c r="L38" t="n">
-        <v>156.32</v>
+        <v>185.67</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-96.12</v>
+        <v>-114.13</v>
       </c>
       <c r="K39" t="n">
-        <v>-93.81999999999999</v>
+        <v>-111.41</v>
       </c>
       <c r="L39" t="n">
-        <v>134.31</v>
+        <v>159.49</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-121.25</v>
+        <v>-150.34</v>
       </c>
       <c r="K40" t="n">
-        <v>11.35</v>
+        <v>14.07</v>
       </c>
       <c r="L40" t="n">
-        <v>121.78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-86.95</v>
+        <v>-114.61</v>
       </c>
       <c r="K41" t="n">
-        <v>-107.58</v>
+        <v>-141.8</v>
       </c>
       <c r="L41" t="n">
-        <v>138.32</v>
+        <v>182.32</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-72.2</v>
+        <v>-88.29000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>224.39</v>
+        <v>274.38</v>
       </c>
       <c r="L42" t="n">
-        <v>235.72</v>
+        <v>288.24</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-20.15</v>
+        <v>-26.51</v>
       </c>
       <c r="K43" t="n">
-        <v>-124.97</v>
+        <v>-164.35</v>
       </c>
       <c r="L43" t="n">
-        <v>126.58</v>
+        <v>166.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>29.56</v>
+        <v>33.45</v>
       </c>
       <c r="K44" t="n">
-        <v>44.24</v>
+        <v>50.07</v>
       </c>
       <c r="L44" t="n">
-        <v>53.2</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>36.59</v>
+        <v>39.88</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.88</v>
+        <v>-55.46</v>
       </c>
       <c r="L45" t="n">
-        <v>62.67</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>27.84</v>
+        <v>30.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.43</v>
+        <v>-56.47</v>
       </c>
       <c r="L46" t="n">
-        <v>58.48</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>102.21</v>
+        <v>106.16</v>
       </c>
       <c r="K47" t="n">
-        <v>28.82</v>
+        <v>29.94</v>
       </c>
       <c r="L47" t="n">
-        <v>106.19</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.8</v>
+        <v>-50.56</v>
       </c>
       <c r="K48" t="n">
-        <v>38.93</v>
+        <v>45.99</v>
       </c>
       <c r="L48" t="n">
-        <v>57.86</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>8.34</v>
+        <v>9.6</v>
       </c>
       <c r="K49" t="n">
-        <v>55.04</v>
+        <v>63.36</v>
       </c>
       <c r="L49" t="n">
-        <v>55.66</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-107.68</v>
+        <v>-112.5</v>
       </c>
       <c r="K50" t="n">
-        <v>107.01</v>
+        <v>111.8</v>
       </c>
       <c r="L50" t="n">
-        <v>151.81</v>
+        <v>158.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
       <c r="K51" t="n">
-        <v>176.93</v>
+        <v>186.46</v>
       </c>
       <c r="L51" t="n">
-        <v>177.1</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-140.31</v>
+        <v>-160.58</v>
       </c>
       <c r="K52" t="n">
-        <v>117.45</v>
+        <v>134.42</v>
       </c>
       <c r="L52" t="n">
-        <v>182.98</v>
+        <v>209.42</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-42.7</v>
+        <v>-56.94</v>
       </c>
       <c r="K53" t="n">
-        <v>104.95</v>
+        <v>139.95</v>
       </c>
       <c r="L53" t="n">
-        <v>113.3</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-57.04</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>104.58</v>
+        <v>131.17</v>
       </c>
       <c r="L54" t="n">
-        <v>119.13</v>
+        <v>149.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-72.77</v>
+        <v>-91.84</v>
       </c>
       <c r="K55" t="n">
-        <v>-107.94</v>
+        <v>-136.23</v>
       </c>
       <c r="L55" t="n">
-        <v>130.18</v>
+        <v>164.3</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>85.88</v>
+        <v>111.45</v>
       </c>
       <c r="K56" t="n">
-        <v>-132.14</v>
+        <v>-171.49</v>
       </c>
       <c r="L56" t="n">
-        <v>157.59</v>
+        <v>204.53</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-92.18000000000001</v>
+        <v>-126.9</v>
       </c>
       <c r="K57" t="n">
-        <v>118.89</v>
+        <v>163.68</v>
       </c>
       <c r="L57" t="n">
-        <v>150.43</v>
+        <v>207.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-295.64</v>
+        <v>-349.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-148.99</v>
+        <v>-175.97</v>
       </c>
       <c r="L58" t="n">
-        <v>331.06</v>
+        <v>391.02</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.51</v>
+        <v>-6.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.82</v>
+        <v>-54.24</v>
       </c>
       <c r="L59" t="n">
-        <v>45.15</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.37</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-16.96</v>
+        <v>-18.99</v>
       </c>
       <c r="L60" t="n">
-        <v>63.67</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>3.31</v>
+        <v>3.57</v>
       </c>
       <c r="K61" t="n">
-        <v>73.37</v>
+        <v>79.03</v>
       </c>
       <c r="L61" t="n">
-        <v>73.45</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-39.42</v>
+        <v>-41.79</v>
       </c>
       <c r="K62" t="n">
-        <v>-72.90000000000001</v>
+        <v>-77.28</v>
       </c>
       <c r="L62" t="n">
-        <v>82.88</v>
+        <v>87.84999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>4.31</v>
+        <v>5.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.11</v>
+        <v>-61.41</v>
       </c>
       <c r="L63" t="n">
-        <v>52.29</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>68.69</v>
+        <v>76.13</v>
       </c>
       <c r="K64" t="n">
-        <v>47.73</v>
+        <v>52.9</v>
       </c>
       <c r="L64" t="n">
-        <v>83.65000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>13.33</v>
+        <v>16.39</v>
       </c>
       <c r="K65" t="n">
-        <v>-81.69</v>
+        <v>-100.44</v>
       </c>
       <c r="L65" t="n">
-        <v>82.77</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>117.23</v>
+        <v>131.82</v>
       </c>
       <c r="K66" t="n">
-        <v>88.47</v>
+        <v>99.48</v>
       </c>
       <c r="L66" t="n">
-        <v>146.87</v>
+        <v>165.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-38.19</v>
+        <v>-40.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-152.8</v>
+        <v>-163.72</v>
       </c>
       <c r="L67" t="n">
-        <v>157.49</v>
+        <v>168.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.4</v>
+        <v>-119.24</v>
       </c>
       <c r="K68" t="n">
-        <v>164.6</v>
+        <v>181.05</v>
       </c>
       <c r="L68" t="n">
-        <v>197.09</v>
+        <v>216.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-151.69</v>
+        <v>-185.13</v>
       </c>
       <c r="K69" t="n">
-        <v>136.03</v>
+        <v>166.02</v>
       </c>
       <c r="L69" t="n">
-        <v>203.75</v>
+        <v>248.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-129.34</v>
+        <v>-156.32</v>
       </c>
       <c r="K70" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="L70" t="n">
-        <v>129.35</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.35</v>
+        <v>-21.97</v>
       </c>
       <c r="K71" t="n">
-        <v>182.37</v>
+        <v>261.11</v>
       </c>
       <c r="L71" t="n">
-        <v>183.01</v>
+        <v>262.03</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>31.14</v>
+        <v>38.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-186.85</v>
+        <v>-233.09</v>
       </c>
       <c r="L72" t="n">
-        <v>189.43</v>
+        <v>236.31</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-160.16</v>
+        <v>-181.9</v>
       </c>
       <c r="K73" t="n">
-        <v>-387.96</v>
+        <v>-440.62</v>
       </c>
       <c r="L73" t="n">
-        <v>419.72</v>
+        <v>476.69</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>56.85</v>
+        <v>64.66</v>
       </c>
       <c r="K74" t="n">
-        <v>12.23</v>
+        <v>13.91</v>
       </c>
       <c r="L74" t="n">
-        <v>58.15</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.42</v>
+        <v>-24.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.74</v>
+        <v>-10.35</v>
       </c>
       <c r="L75" t="n">
-        <v>22.21</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>57.83</v>
+        <v>58.82</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.93</v>
+        <v>-44.68</v>
       </c>
       <c r="L76" t="n">
-        <v>72.63</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.98999999999999</v>
+        <v>-81.31999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>19</v>
+        <v>21.77</v>
       </c>
       <c r="L77" t="n">
-        <v>73.48999999999999</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>41.7</v>
+        <v>46.42</v>
       </c>
       <c r="K78" t="n">
-        <v>-61.22</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>74.08</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-83.28</v>
+        <v>-90.38</v>
       </c>
       <c r="K79" t="n">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="L79" t="n">
-        <v>83.34999999999999</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>47.92</v>
+        <v>56.15</v>
       </c>
       <c r="K80" t="n">
-        <v>118.7</v>
+        <v>139.09</v>
       </c>
       <c r="L80" t="n">
-        <v>128.01</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>17.56</v>
+        <v>21.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-79.98999999999999</v>
+        <v>-97.58</v>
       </c>
       <c r="L81" t="n">
-        <v>81.89</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-75.83</v>
+        <v>-96.01000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="L82" t="n">
-        <v>75.83</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>178.3</v>
+        <v>209.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-23.35</v>
+        <v>-27.47</v>
       </c>
       <c r="L83" t="n">
-        <v>179.82</v>
+        <v>211.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="K84" t="n">
-        <v>-160.12</v>
+        <v>-205.32</v>
       </c>
       <c r="L84" t="n">
-        <v>160.14</v>
+        <v>205.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>203.95</v>
+        <v>239.24</v>
       </c>
       <c r="K85" t="n">
-        <v>101.07</v>
+        <v>118.56</v>
       </c>
       <c r="L85" t="n">
-        <v>227.62</v>
+        <v>267.01</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-133.61</v>
+        <v>-185.13</v>
       </c>
       <c r="K86" t="n">
-        <v>135.61</v>
+        <v>187.91</v>
       </c>
       <c r="L86" t="n">
-        <v>190.38</v>
+        <v>263.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>144.5</v>
+        <v>182.48</v>
       </c>
       <c r="K87" t="n">
-        <v>163.46</v>
+        <v>206.42</v>
       </c>
       <c r="L87" t="n">
-        <v>218.17</v>
+        <v>275.51</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-267.46</v>
+        <v>-339.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-75.59</v>
+        <v>-95.87</v>
       </c>
       <c r="L88" t="n">
-        <v>277.94</v>
+        <v>352.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-09.xlsx
+++ b/output/2025-05-09.xlsx
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-51.25</v>
+        <v>-60.18</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.46</v>
+        <v>-49.86</v>
       </c>
       <c r="L15" t="n">
-        <v>66.56</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.38</v>
+        <v>-60.5</v>
       </c>
       <c r="K16" t="n">
-        <v>-79.34</v>
+        <v>-91.64</v>
       </c>
       <c r="L16" t="n">
-        <v>95.06999999999999</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>58.28</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.31</v>
+        <v>-9.26</v>
       </c>
       <c r="L17" t="n">
-        <v>58.87</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>69.78</v>
+        <v>72.89</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.02</v>
+        <v>-9.42</v>
       </c>
       <c r="L18" t="n">
-        <v>70.36</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="19">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>59.08</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.78</v>
+        <v>-35.75</v>
       </c>
       <c r="L29" t="n">
-        <v>67.08</v>
+        <v>75.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-71.33</v>
+        <v>-84.78</v>
       </c>
       <c r="K30" t="n">
-        <v>21.74</v>
+        <v>25.85</v>
       </c>
       <c r="L30" t="n">
-        <v>74.56999999999999</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>12.59</v>
+        <v>14.81</v>
       </c>
       <c r="K31" t="n">
-        <v>89.94</v>
+        <v>105.81</v>
       </c>
       <c r="L31" t="n">
-        <v>90.81</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>7.35</v>
+        <v>8.48</v>
       </c>
       <c r="K32" t="n">
-        <v>-11.31</v>
+        <v>-13.03</v>
       </c>
       <c r="L32" t="n">
-        <v>13.49</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-48.23</v>
+        <v>-50.24</v>
       </c>
       <c r="K33" t="n">
-        <v>-52.1</v>
+        <v>-54.27</v>
       </c>
       <c r="L33" t="n">
-        <v>70.98999999999999</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>81.06</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>16.32</v>
+        <v>16.95</v>
       </c>
       <c r="L34" t="n">
-        <v>82.68000000000001</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>33.45</v>
+        <v>36.38</v>
       </c>
       <c r="K44" t="n">
-        <v>50.07</v>
+        <v>54.44</v>
       </c>
       <c r="L44" t="n">
-        <v>60.21</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>39.88</v>
+        <v>46.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-55.46</v>
+        <v>-65.25</v>
       </c>
       <c r="L45" t="n">
-        <v>68.31</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>30.56</v>
+        <v>36.11</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.47</v>
+        <v>-66.72</v>
       </c>
       <c r="L46" t="n">
-        <v>64.20999999999999</v>
+        <v>75.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>106.16</v>
+        <v>134.62</v>
       </c>
       <c r="K47" t="n">
-        <v>29.94</v>
+        <v>37.96</v>
       </c>
       <c r="L47" t="n">
-        <v>110.3</v>
+        <v>139.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-50.56</v>
+        <v>-59.81</v>
       </c>
       <c r="K48" t="n">
-        <v>45.99</v>
+        <v>54.4</v>
       </c>
       <c r="L48" t="n">
-        <v>68.34</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>9.6</v>
+        <v>10.55</v>
       </c>
       <c r="K49" t="n">
-        <v>63.36</v>
+        <v>69.64</v>
       </c>
       <c r="L49" t="n">
-        <v>64.08</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.67</v>
+        <v>-8.06</v>
       </c>
       <c r="K59" t="n">
-        <v>-54.24</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>54.65</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-68.70999999999999</v>
+        <v>-92.26000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-18.99</v>
+        <v>-25.5</v>
       </c>
       <c r="L60" t="n">
-        <v>71.28</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>3.57</v>
+        <v>4.75</v>
       </c>
       <c r="K61" t="n">
-        <v>79.03</v>
+        <v>105.27</v>
       </c>
       <c r="L61" t="n">
-        <v>79.11</v>
+        <v>105.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.79</v>
+        <v>-46.63</v>
       </c>
       <c r="K62" t="n">
-        <v>-77.28</v>
+        <v>-86.23</v>
       </c>
       <c r="L62" t="n">
-        <v>87.84999999999999</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>5.08</v>
+        <v>5.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-61.41</v>
+        <v>-68.62</v>
       </c>
       <c r="L63" t="n">
-        <v>61.62</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>76.13</v>
+        <v>98.03</v>
       </c>
       <c r="K64" t="n">
-        <v>52.9</v>
+        <v>68.12</v>
       </c>
       <c r="L64" t="n">
-        <v>92.7</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>64.66</v>
+        <v>93.23</v>
       </c>
       <c r="K74" t="n">
-        <v>13.91</v>
+        <v>20.05</v>
       </c>
       <c r="L74" t="n">
-        <v>66.14</v>
+        <v>95.36</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-24.19</v>
+        <v>-30.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.35</v>
+        <v>-12.92</v>
       </c>
       <c r="L75" t="n">
-        <v>26.31</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>58.82</v>
+        <v>67.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-44.68</v>
+        <v>-51.29</v>
       </c>
       <c r="L76" t="n">
-        <v>73.86</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-81.31999999999999</v>
+        <v>-107.14</v>
       </c>
       <c r="K77" t="n">
-        <v>21.77</v>
+        <v>28.68</v>
       </c>
       <c r="L77" t="n">
-        <v>84.18000000000001</v>
+        <v>110.91</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>46.42</v>
+        <v>56.82</v>
       </c>
       <c r="K78" t="n">
-        <v>-68.15000000000001</v>
+        <v>-83.41</v>
       </c>
       <c r="L78" t="n">
-        <v>82.45999999999999</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-90.38</v>
+        <v>-101</v>
       </c>
       <c r="K79" t="n">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="L79" t="n">
-        <v>90.45</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="80">
